--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BE76021-D73A-3643-B443-B6488BA68946}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54CB0323-5C0A-1C42-9D96-BFB5647E3EFB}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="-21100" windowWidth="27640" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Study_ID</t>
   </si>
@@ -60,6 +60,15 @@
   </si>
   <si>
     <t>NA. Thesis</t>
+  </si>
+  <si>
+    <t>Spp</t>
+  </si>
+  <si>
+    <t>Family</t>
+  </si>
+  <si>
+    <t>Leuciscidae</t>
   </si>
 </sst>
 </file>
@@ -434,39 +443,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.83203125" style="1"/>
+    <col min="1" max="3" width="10.83203125" style="1"/>
+    <col min="4" max="4" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54CB0323-5C0A-1C42-9D96-BFB5647E3EFB}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2290139F-CA7C-A048-88F3-2C0E03857F60}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="-21100" windowWidth="27640" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Study_ID</t>
   </si>
@@ -69,19 +69,49 @@
   </si>
   <si>
     <t>Leuciscidae</t>
+  </si>
+  <si>
+    <t>AMPE-1</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>doi: 10.1002/ece3.1392</t>
+  </si>
+  <si>
+    <t>Ammocrypta pellucida</t>
+  </si>
+  <si>
+    <t>Common_name</t>
+  </si>
+  <si>
+    <t>Eastern Sand Darter</t>
+  </si>
+  <si>
+    <t>Central Stoneroller</t>
+  </si>
+  <si>
+    <t>Semotilus atromaculatus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,9 +134,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -443,48 +477,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="10.83203125" style="1"/>
-    <col min="4" max="4" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="17.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="1"/>
+    <col min="5" max="5" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2290139F-CA7C-A048-88F3-2C0E03857F60}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF54F36-4523-FD49-AFBE-A9F0F0AC8105}"/>
   <bookViews>
     <workbookView xWindow="2480" yWindow="-21100" windowWidth="27640" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>Study_ID</t>
   </si>
@@ -93,6 +93,21 @@
   </si>
   <si>
     <t>Semotilus atromaculatus</t>
+  </si>
+  <si>
+    <t>AMRU-1</t>
+  </si>
+  <si>
+    <t>Nothern Rockbass</t>
+  </si>
+  <si>
+    <t>Ambloplites rupestris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Centrarchidae</t>
+  </si>
+  <si>
+    <t>NA. thesis</t>
   </si>
 </sst>
 </file>
@@ -134,15 +149,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -477,13 +489,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
     <col min="2" max="2" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="1"/>
+    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="1"/>
     <col min="7" max="7" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -496,7 +508,7 @@
       <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -519,7 +531,7 @@
       <c r="B2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -556,6 +568,29 @@
       </c>
       <c r="G3" s="1" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BF54F36-4523-FD49-AFBE-A9F0F0AC8105}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F16B5851-4C7A-7946-9984-6463974A6C6D}"/>
   <bookViews>
-    <workbookView xWindow="2480" yWindow="-21100" windowWidth="27640" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="5380" yWindow="-21100" windowWidth="27640" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
   <si>
     <t>Study_ID</t>
   </si>
@@ -108,13 +108,109 @@
   </si>
   <si>
     <t>NA. thesis</t>
+  </si>
+  <si>
+    <t>CARI-1</t>
+  </si>
+  <si>
+    <t>Klamath Smallscale Sucker</t>
+  </si>
+  <si>
+    <t>Catostomus rimiculus</t>
+  </si>
+  <si>
+    <t>Catostomidae</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-024-01651-5</t>
+  </si>
+  <si>
+    <t>ETCA-1</t>
+  </si>
+  <si>
+    <t>Rainbow Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma caeruleum</t>
+  </si>
+  <si>
+    <t>Percidae</t>
+  </si>
+  <si>
+    <t>ETCA-2</t>
+  </si>
+  <si>
+    <t>https://scholarworks.uni.edu/etd/2455</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/ece3.8422</t>
+  </si>
+  <si>
+    <t>ETNI-1</t>
+  </si>
+  <si>
+    <t>Johnny Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma nigrum</t>
+  </si>
+  <si>
+    <t>Tessellated darters</t>
+  </si>
+  <si>
+    <t>ETOL-1</t>
+  </si>
+  <si>
+    <t>Etheostoma olmstedi</t>
+  </si>
+  <si>
+    <t>Yazoo Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma Raneyi</t>
+  </si>
+  <si>
+    <t>ETRA-1</t>
+  </si>
+  <si>
+    <t>Kentucky Arrow Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma sagitta spilotum)</t>
+  </si>
+  <si>
+    <t>ETSA-1</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-019-01188-y</t>
+  </si>
+  <si>
+    <t>FUNO-1</t>
+  </si>
+  <si>
+    <t>FUOL-1</t>
+  </si>
+  <si>
+    <t>Fundulus notatus</t>
+  </si>
+  <si>
+    <t>Fundulus olivaceus</t>
+  </si>
+  <si>
+    <t>Blackstripe topminnow</t>
+  </si>
+  <si>
+    <t>Blackspotted topminnow,</t>
+  </si>
+  <si>
+    <t>Fundulidae</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -125,6 +221,21 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -146,17 +257,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -489,111 +605,308 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="1"/>
-    <col min="2" max="2" width="17.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="1"/>
-    <col min="7" max="7" width="20.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="2"/>
+    <col min="2" max="2" width="23.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="2"/>
+    <col min="7" max="7" width="38.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="1" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
     </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G5" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G7" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F16B5851-4C7A-7946-9984-6463974A6C6D}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8530CAA8-FB67-5C48-8F7A-CACBBAB85B83}"/>
   <bookViews>
-    <workbookView xWindow="5380" yWindow="-21100" windowWidth="27640" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="13340" yWindow="-21100" windowWidth="20620" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="76">
   <si>
     <t>Study_ID</t>
   </si>
@@ -200,10 +200,70 @@
     <t>Blackstripe topminnow</t>
   </si>
   <si>
-    <t>Blackspotted topminnow,</t>
-  </si>
-  <si>
     <t>Fundulidae</t>
+  </si>
+  <si>
+    <t>Blackspotted topminnow</t>
+  </si>
+  <si>
+    <t>Arroyo Chub</t>
+  </si>
+  <si>
+    <t>Gila orcuttii</t>
+  </si>
+  <si>
+    <t>GIOR-1</t>
+  </si>
+  <si>
+    <t>GIRO-1</t>
+  </si>
+  <si>
+    <t>Roundtail Chub</t>
+  </si>
+  <si>
+    <t>Gila robusta</t>
+  </si>
+  <si>
+    <t>DOI:10.1371/journal.pone.0139832</t>
+  </si>
+  <si>
+    <t>Ictalurus punctatus</t>
+  </si>
+  <si>
+    <t>ICPU-1</t>
+  </si>
+  <si>
+    <t>Channel Catfish</t>
+  </si>
+  <si>
+    <t>Ictaluridae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N </t>
+  </si>
+  <si>
+    <t>DOI: https://doi.org/10.1080/00028487.2017.1362471</t>
+  </si>
+  <si>
+    <t>LEAU-1</t>
+  </si>
+  <si>
+    <t>Redbreast Sunfish</t>
+  </si>
+  <si>
+    <t>Centrarchidae</t>
+  </si>
+  <si>
+    <t>Lepomis Auritus</t>
+  </si>
+  <si>
+    <t>Bayou Darter</t>
+  </si>
+  <si>
+    <t>NORU-1</t>
+  </si>
+  <si>
+    <t>Nothonotus rubrus</t>
   </si>
 </sst>
 </file>
@@ -605,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -614,7 +674,7 @@
     <col min="4" max="4" width="13" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="2"/>
-    <col min="7" max="7" width="38.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -873,7 +933,7 @@
         <v>51</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>12</v>
@@ -887,18 +947,124 @@
         <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8530CAA8-FB67-5C48-8F7A-CACBBAB85B83}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E902859D-3DFA-F749-949C-47800BDC5C67}"/>
   <bookViews>
     <workbookView xWindow="13340" yWindow="-21100" windowWidth="20620" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="86">
   <si>
     <t>Study_ID</t>
   </si>
@@ -264,6 +264,36 @@
   </si>
   <si>
     <t>Nothonotus rubrus</t>
+  </si>
+  <si>
+    <t>ONCL-1</t>
+  </si>
+  <si>
+    <t>Westslope Cutthroat Trout</t>
+  </si>
+  <si>
+    <t>Oncorhynchus clarkii lewisi</t>
+  </si>
+  <si>
+    <t>Salmonidae</t>
+  </si>
+  <si>
+    <t>PEFL-1</t>
+  </si>
+  <si>
+    <t>Yellow Perch</t>
+  </si>
+  <si>
+    <t>Perca flavescens</t>
+  </si>
+  <si>
+    <t>SACO-1</t>
+  </si>
+  <si>
+    <t>Bull trout</t>
+  </si>
+  <si>
+    <t>Salevlinus confluentus</t>
   </si>
 </sst>
 </file>
@@ -321,7 +351,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -329,6 +359,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -665,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -728,7 +761,7 @@
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -1065,6 +1098,66 @@
         <v>12</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E902859D-3DFA-F749-949C-47800BDC5C67}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCA00543-780F-1643-91AC-1803C0BF732A}"/>
   <bookViews>
     <workbookView xWindow="13340" yWindow="-21100" windowWidth="20620" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>Study_ID</t>
   </si>
@@ -293,7 +293,25 @@
     <t>Bull trout</t>
   </si>
   <si>
-    <t>Salevlinus confluentus</t>
+    <t>SAFO-1</t>
+  </si>
+  <si>
+    <t>Brook Trout</t>
+  </si>
+  <si>
+    <t>Salevlinus fontinalis</t>
+  </si>
+  <si>
+    <t>Salvelinus confluentus</t>
+  </si>
+  <si>
+    <t>SEAT-1</t>
+  </si>
+  <si>
+    <t>Creek Chub</t>
+  </si>
+  <si>
+    <t>Campostoma anomalum</t>
   </si>
 </sst>
 </file>
@@ -698,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -764,8 +782,8 @@
       <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
+      <c r="C3" s="4" t="s">
+        <v>91</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -1149,7 +1167,7 @@
         <v>84</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>79</v>
@@ -1158,6 +1176,46 @@
         <v>5</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCA00543-780F-1643-91AC-1803C0BF732A}"/>
+  <xr:revisionPtr revIDLastSave="187" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01DFF3F3-8919-E540-B21A-5D1EF1F580C6}"/>
   <bookViews>
-    <workbookView xWindow="13340" yWindow="-21100" windowWidth="20620" windowHeight="16180" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="13080" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="95">
   <si>
     <t>Study_ID</t>
   </si>
@@ -312,6 +312,15 @@
   </si>
   <si>
     <t>Campostoma anomalum</t>
+  </si>
+  <si>
+    <t>RHOS-1</t>
+  </si>
+  <si>
+    <t>Speckled Dace</t>
+  </si>
+  <si>
+    <t>Rhinichthys osculus</t>
   </si>
 </sst>
 </file>
@@ -716,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -1219,6 +1228,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G5" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="187" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01DFF3F3-8919-E540-B21A-5D1EF1F580C6}"/>
+  <xr:revisionPtr revIDLastSave="240" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{267668CA-7E62-5F45-A752-88E216774DBC}"/>
   <bookViews>
     <workbookView xWindow="13080" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="112">
   <si>
     <t>Study_ID</t>
   </si>
@@ -251,9 +251,6 @@
     <t>Redbreast Sunfish</t>
   </si>
   <si>
-    <t>Centrarchidae</t>
-  </si>
-  <si>
     <t>Lepomis Auritus</t>
   </si>
   <si>
@@ -299,9 +296,6 @@
     <t>Brook Trout</t>
   </si>
   <si>
-    <t>Salevlinus fontinalis</t>
-  </si>
-  <si>
     <t>Salvelinus confluentus</t>
   </si>
   <si>
@@ -321,6 +315,63 @@
   </si>
   <si>
     <t>Rhinichthys osculus</t>
+  </si>
+  <si>
+    <t>FUOL-2</t>
+  </si>
+  <si>
+    <t>ICPU-2</t>
+  </si>
+  <si>
+    <t>LARI-1</t>
+  </si>
+  <si>
+    <t>Western Brook Lamprey</t>
+  </si>
+  <si>
+    <t>Lampetra richardsoni</t>
+  </si>
+  <si>
+    <t>Petromyzontidae</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-018-1137-9</t>
+  </si>
+  <si>
+    <t>Salvelinus fontinalis</t>
+  </si>
+  <si>
+    <t>NOJE-1</t>
+  </si>
+  <si>
+    <t>Rio Grande Shiner</t>
+  </si>
+  <si>
+    <t>Notropis jemezanus</t>
+  </si>
+  <si>
+    <t>MAAE-1</t>
+  </si>
+  <si>
+    <t>Speckled Chub</t>
+  </si>
+  <si>
+    <t>Macrhybopsis aestivalis</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-020-01328-9</t>
+  </si>
+  <si>
+    <t>ONCL-2</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10980-005-5221-4</t>
+  </si>
+  <si>
+    <t>Oncorhynchus clarkii henshawi</t>
+  </si>
+  <si>
+    <t>Lahontan cutthroat trout</t>
   </si>
 </sst>
 </file>
@@ -378,7 +429,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -389,6 +440,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -725,13 +782,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
-    <col min="2" max="2" width="23.1640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="2"/>
     <col min="7" max="7" width="44.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -792,7 +849,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>10</v>
@@ -1024,16 +1081,16 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>12</v>
@@ -1044,13 +1101,13 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>10</v>
@@ -1061,190 +1118,322 @@
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="B24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="2" t="s">
+      <c r="E27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A22" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="B30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1252,6 +1441,9 @@
   <hyperlinks>
     <hyperlink ref="G5" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G7" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G19" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G21" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G22" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{267668CA-7E62-5F45-A752-88E216774DBC}"/>
+  <xr:revisionPtr revIDLastSave="250" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9436E9A4-6AA8-2E40-9CF0-A63482E03A2F}"/>
   <bookViews>
     <workbookView xWindow="13080" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="117">
   <si>
     <t>Study_ID</t>
   </si>
@@ -372,6 +372,21 @@
   </si>
   <si>
     <t>Lahontan cutthroat trout</t>
+  </si>
+  <si>
+    <t>GAAC-1</t>
+  </si>
+  <si>
+    <t>Threespine Stickleback</t>
+  </si>
+  <si>
+    <t>Gasterosteus aculeatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Gasterosteidae</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/biolinnean/blz106</t>
   </si>
 </sst>
 </file>
@@ -782,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -1099,35 +1114,38 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>10</v>
@@ -1138,36 +1156,33 @@
       <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>63</v>
@@ -1184,88 +1199,88 @@
       <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G18" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="5" t="s">
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
@@ -1274,55 +1289,58 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>78</v>
@@ -1333,45 +1351,45 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="2" t="s">
+    </row>
+    <row r="26" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
@@ -1379,19 +1397,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
@@ -1399,16 +1417,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -1419,13 +1437,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -1434,6 +1452,26 @@
         <v>12</v>
       </c>
       <c r="F30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A31" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1441,9 +1479,10 @@
   <hyperlinks>
     <hyperlink ref="G5" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G7" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G19" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G21" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G22" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G20" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G22" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G23" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G15" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="250" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9436E9A4-6AA8-2E40-9CF0-A63482E03A2F}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0555E66E-A0C0-7E42-8018-E27E879B377D}"/>
   <bookViews>
-    <workbookView xWindow="13080" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="13120" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="123">
   <si>
     <t>Study_ID</t>
   </si>
@@ -387,6 +387,24 @@
   </si>
   <si>
     <t>https://doi.org/10.1093/biolinnean/blz106</t>
+  </si>
+  <si>
+    <t>CADI-1</t>
+  </si>
+  <si>
+    <t>Bluehead Sucker</t>
+  </si>
+  <si>
+    <t>Pantosteus discobolus</t>
+  </si>
+  <si>
+    <t>FUGR-1</t>
+  </si>
+  <si>
+    <t>Gulf Killiffish</t>
+  </si>
+  <si>
+    <t>Fundulus grandis</t>
   </si>
 </sst>
 </file>
@@ -797,7 +815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -904,39 +922,36 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>118</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>26</v>
+        <v>119</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -944,13 +959,13 @@
       <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>35</v>
+      <c r="G6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>30</v>
@@ -967,19 +982,19 @@
       <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>34</v>
+      <c r="G7" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>32</v>
@@ -990,16 +1005,19 @@
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G8" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>32</v>
@@ -1013,13 +1031,13 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -1033,13 +1051,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>32</v>
@@ -1050,59 +1068,60 @@
       <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="1" t="s">
+    </row>
+    <row r="12" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>55</v>
+        <v>121</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>52</v>
+        <v>122</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>54</v>
@@ -1114,41 +1133,38 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>112</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>12</v>
@@ -1157,18 +1173,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>12</v>
@@ -1176,91 +1192,91 @@
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>62</v>
+      <c r="G17" s="5" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>99</v>
+      <c r="G20" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
@@ -1268,125 +1284,125 @@
     </row>
     <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B24" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="5" t="s">
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B25" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="5" t="s">
+      <c r="E25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A26" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
@@ -1395,38 +1411,41 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>83</v>
+        <v>108</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -1437,19 +1456,19 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
@@ -1457,32 +1476,72 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A32" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A33" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="E33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G5" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G7" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G20" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G22" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G23" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G15" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G6" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G8" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G22" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G24" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G25" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G17" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0555E66E-A0C0-7E42-8018-E27E879B377D}"/>
+  <xr:revisionPtr revIDLastSave="372" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83807E0-6954-F244-8575-1D6ED673C0C9}"/>
   <bookViews>
-    <workbookView xWindow="13120" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="13400" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="155">
   <si>
     <t>Study_ID</t>
   </si>
@@ -405,6 +405,102 @@
   </si>
   <si>
     <t>Fundulus grandis</t>
+  </si>
+  <si>
+    <t>HYPL-1</t>
+  </si>
+  <si>
+    <t>Plains Minnow</t>
+  </si>
+  <si>
+    <t>Hybognathus placitus</t>
+  </si>
+  <si>
+    <t>Emerald Shiner</t>
+  </si>
+  <si>
+    <t>Notropis atherinoides</t>
+  </si>
+  <si>
+    <t>NOAT-1</t>
+  </si>
+  <si>
+    <t>CYLU-1</t>
+  </si>
+  <si>
+    <t>Red Shiner</t>
+  </si>
+  <si>
+    <t>Cyprinella lutrensis</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/mec.12970</t>
+  </si>
+  <si>
+    <t>ONMY-1</t>
+  </si>
+  <si>
+    <t>Redband Trout</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/mec.16810</t>
+  </si>
+  <si>
+    <t>Oncorhynchus mykiss gairdneri</t>
+  </si>
+  <si>
+    <t>GINI-1</t>
+  </si>
+  <si>
+    <t>MEFU-1</t>
+  </si>
+  <si>
+    <t>TICO-1</t>
+  </si>
+  <si>
+    <t>Gila nigra</t>
+  </si>
+  <si>
+    <t>Meda fulgida</t>
+  </si>
+  <si>
+    <t>Tiaroga cobitis</t>
+  </si>
+  <si>
+    <t>Headwater chub</t>
+  </si>
+  <si>
+    <t>Spikedace</t>
+  </si>
+  <si>
+    <t>Loach minnow</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-015-0707-3</t>
+  </si>
+  <si>
+    <t>RHCA-1</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/bij.12657</t>
+  </si>
+  <si>
+    <t>Rhinichthys cataractae</t>
+  </si>
+  <si>
+    <t>Longnose Dace</t>
+  </si>
+  <si>
+    <t>SIBI-1</t>
+  </si>
+  <si>
+    <t>Siphateles bicolor</t>
+  </si>
+  <si>
+    <t>Lahontan tui chub</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-015-0697-1</t>
   </si>
 </sst>
 </file>
@@ -496,6 +592,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -815,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -965,16 +1065,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>12</v>
@@ -983,12 +1083,12 @@
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>30</v>
@@ -1005,19 +1105,19 @@
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>34</v>
+      <c r="G8" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>32</v>
@@ -1028,16 +1128,19 @@
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G9" s="3" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -1051,13 +1154,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>32</v>
@@ -1069,15 +1172,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>32</v>
@@ -1088,60 +1191,60 @@
       <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="13" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>54</v>
@@ -1155,7 +1258,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>55</v>
@@ -1173,58 +1276,58 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A18" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G17" s="5" t="s">
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>137</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>60</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>10</v>
@@ -1236,64 +1339,64 @@
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G21" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>98</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>12</v>
@@ -1301,42 +1404,45 @@
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>99</v>
+      <c r="G22" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G23" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>67</v>
@@ -1344,22 +1450,19 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
@@ -1368,21 +1471,21 @@
         <v>6</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>12</v>
@@ -1391,38 +1494,41 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G27" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>111</v>
+        <v>138</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>12</v>
@@ -1431,21 +1537,21 @@
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>109</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
@@ -1453,39 +1559,45 @@
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G29" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>12</v>
@@ -1496,52 +1608,253 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A33" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A34" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A38" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B38" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C38" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A33" s="2" t="s">
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A41" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B42" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C42" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="B45" s="6"/>
+      <c r="G45" s="5"/>
+    </row>
+    <row r="49" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G6" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G8" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G22" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G24" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G25" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G17" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G9" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G25" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G27" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G30" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G18" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G41" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F83807E0-6954-F244-8575-1D6ED673C0C9}"/>
+  <xr:revisionPtr revIDLastSave="378" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829C1685-AE3D-D249-AF1E-880316A045BC}"/>
   <bookViews>
     <workbookView xWindow="13400" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="157">
   <si>
     <t>Study_ID</t>
   </si>
@@ -501,6 +501,12 @@
   </si>
   <si>
     <t>DOI 10.1007/s10592-015-0697-1</t>
+  </si>
+  <si>
+    <t>SAFO-2</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/j.1365-294X.2011.05210.x</t>
   </si>
 </sst>
 </file>
@@ -915,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -1734,33 +1740,36 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A39" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>10</v>
@@ -1771,19 +1780,16 @@
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>10</v>
@@ -1794,19 +1800,19 @@
       <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G40" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>10</v>
@@ -1817,19 +1823,19 @@
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G41" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>10</v>
@@ -1840,12 +1846,35 @@
       <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="B45" s="6"/>
-      <c r="G45" s="5"/>
-    </row>
-    <row r="49" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="G42" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="B46" s="6"/>
+      <c r="G46" s="5"/>
+    </row>
+    <row r="50" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G6" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
@@ -1854,7 +1883,7 @@
     <hyperlink ref="G27" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
     <hyperlink ref="G30" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
     <hyperlink ref="G18" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G41" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G42" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="378" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{829C1685-AE3D-D249-AF1E-880316A045BC}"/>
+  <xr:revisionPtr revIDLastSave="413" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6256F85-EDAB-9B43-8E7D-D7CB1017A135}"/>
   <bookViews>
     <workbookView xWindow="13400" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="170">
   <si>
     <t>Study_ID</t>
   </si>
@@ -507,13 +507,52 @@
   </si>
   <si>
     <t>doi: 10.1111/j.1365-294X.2011.05210.x</t>
+  </si>
+  <si>
+    <t>doi:10.1016/j.jglr.2010.08.005</t>
+  </si>
+  <si>
+    <t>PEFL-2</t>
+  </si>
+  <si>
+    <t>SAVI-1</t>
+  </si>
+  <si>
+    <t>Walleye</t>
+  </si>
+  <si>
+    <t>Sander vitreus</t>
+  </si>
+  <si>
+    <t>SACO-2</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-009-9969-y</t>
+  </si>
+  <si>
+    <t>CYMA-1</t>
+  </si>
+  <si>
+    <t>Cyprinodon macularius</t>
+  </si>
+  <si>
+    <t>Cyprinodontidae</t>
+  </si>
+  <si>
+    <t>Desert Pupfish</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Likely Delete</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -542,6 +581,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -564,7 +610,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -582,6 +628,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -921,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -934,7 +984,7 @@
     <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -956,8 +1006,11 @@
       <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H1" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -980,7 +1033,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1003,7 +1056,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>19</v>
       </c>
@@ -1026,7 +1079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>117</v>
       </c>
@@ -1046,7 +1099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -1069,55 +1122,56 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>30</v>
@@ -1134,19 +1188,19 @@
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G9" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -1157,16 +1211,19 @@
       <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G10" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>32</v>
@@ -1178,15 +1235,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>32</v>
@@ -1198,15 +1255,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>32</v>
@@ -1217,60 +1274,60 @@
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="1" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>54</v>
@@ -1284,7 +1341,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>55</v>
@@ -1302,61 +1359,58 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="E19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>116</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>10</v>
@@ -1367,16 +1421,19 @@
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="G20" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>10</v>
@@ -1387,19 +1444,16 @@
       <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>124</v>
+        <v>60</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>10</v>
@@ -1411,35 +1465,35 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>63</v>
@@ -1456,105 +1510,105 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G24" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A26" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="5" t="s">
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26" s="2" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D27" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A27" s="2" t="s">
+      <c r="E27" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B28" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C28" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A28" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>146</v>
+      <c r="G28" s="5" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>10</v>
@@ -1566,18 +1620,18 @@
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>10</v>
@@ -1588,59 +1642,62 @@
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A31" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>107</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A31" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A33" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B33" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A33" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>78</v>
@@ -1651,68 +1708,68 @@
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>134</v>
+        <v>108</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
@@ -1720,102 +1777,102 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>78</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G39" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>153</v>
+        <v>84</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>145</v>
+        <v>85</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
@@ -1824,21 +1881,21 @@
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>12</v>
@@ -1846,19 +1903,19 @@
       <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>148</v>
+      <c r="G42" s="2" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>10</v>
@@ -1870,20 +1927,109 @@
         <v>6</v>
       </c>
     </row>
+    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A44" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A45" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
     <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="B46" s="6"/>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="50" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="A46" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="B50" s="6"/>
+      <c r="G50" s="5"/>
+    </row>
+    <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G6" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G9" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G25" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G27" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G30" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G18" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G42" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G10" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G26" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G28" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G31" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G19" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G46" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="413" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6256F85-EDAB-9B43-8E7D-D7CB1017A135}"/>
+  <xr:revisionPtr revIDLastSave="570" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D15A53C-7EDC-E441-B5BE-695E0F8482A0}"/>
   <bookViews>
-    <workbookView xWindow="13400" yWindow="-21100" windowWidth="20620" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="13380" yWindow="-21100" windowWidth="20640" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="223">
   <si>
     <t>Study_ID</t>
   </si>
@@ -59,9 +59,6 @@
     <t>JM</t>
   </si>
   <si>
-    <t>NA. Thesis</t>
-  </si>
-  <si>
     <t>Spp</t>
   </si>
   <si>
@@ -107,9 +104,6 @@
     <t xml:space="preserve">	Centrarchidae</t>
   </si>
   <si>
-    <t>NA. thesis</t>
-  </si>
-  <si>
     <t>CARI-1</t>
   </si>
   <si>
@@ -530,29 +524,194 @@
     <t>DOI 10.1007/s10592-009-9969-y</t>
   </si>
   <si>
-    <t>CYMA-1</t>
-  </si>
-  <si>
-    <t>Cyprinodon macularius</t>
-  </si>
-  <si>
     <t>Cyprinodontidae</t>
   </si>
   <si>
-    <t>Desert Pupfish</t>
-  </si>
-  <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>Likely Delete</t>
+    <t>CYSP-1</t>
+  </si>
+  <si>
+    <t>Pupfish</t>
+  </si>
+  <si>
+    <t>Cyprino spp complex</t>
+  </si>
+  <si>
+    <t>10.1007/s10592-004-1978-2</t>
+  </si>
+  <si>
+    <t>ETCA-3</t>
+  </si>
+  <si>
+    <t>doi:10.1111/j.1095-8649.2009.02414.x</t>
+  </si>
+  <si>
+    <t>ETFO-1</t>
+  </si>
+  <si>
+    <t>Etheostoma fonticola</t>
+  </si>
+  <si>
+    <t>Fountain Darter</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-016-0869-7</t>
+  </si>
+  <si>
+    <t>LEOC-1</t>
+  </si>
+  <si>
+    <t>Spotted Gar</t>
+  </si>
+  <si>
+    <t>Lepisosteus oculatus</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-015-0708-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Lepisosteidae</t>
+  </si>
+  <si>
+    <t>LOLO-1</t>
+  </si>
+  <si>
+    <t>Burbot</t>
+  </si>
+  <si>
+    <t>Lota lota</t>
+  </si>
+  <si>
+    <t>Lotidae</t>
+  </si>
+  <si>
+    <t>doi:10.1139/F08-173</t>
+  </si>
+  <si>
+    <t>MODU-1</t>
+  </si>
+  <si>
+    <t>Black Redhorse</t>
+  </si>
+  <si>
+    <t>Moxostoma duquesnei</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-007-9367-2</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/00028487.2014.982260</t>
+  </si>
+  <si>
+    <t>PEFL-3</t>
+  </si>
+  <si>
+    <t>ETNU-1</t>
+  </si>
+  <si>
+    <t>ETSW-1</t>
+  </si>
+  <si>
+    <t>Etheostoma nuchale</t>
+  </si>
+  <si>
+    <t>Etheostoma swaini</t>
+  </si>
+  <si>
+    <t>Gulf Darter</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-010-0111-y</t>
+  </si>
+  <si>
+    <t>Watercress Darter</t>
+  </si>
+  <si>
+    <t>POSP-1</t>
+  </si>
+  <si>
+    <t>Paddlefish</t>
+  </si>
+  <si>
+    <t>Polyodon spathula</t>
+  </si>
+  <si>
+    <t>DOI: 10.1577/T07-078.1</t>
+  </si>
+  <si>
+    <t>Polyodontidae</t>
+  </si>
+  <si>
+    <t>RHOS-2</t>
+  </si>
+  <si>
+    <t>Thesis.</t>
+  </si>
+  <si>
+    <t>http://dx.doi.org/10.1016/j.ympev.2014.04.027</t>
+  </si>
+  <si>
+    <t>SAVI-2</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/j.1365-294X.2009.04291.x</t>
+  </si>
+  <si>
+    <t>Arkansas Thesis</t>
+  </si>
+  <si>
+    <t>WI Thesis</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/mec.12156</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-018-1107-2</t>
+  </si>
+  <si>
+    <t>Mississippi Thesis</t>
+  </si>
+  <si>
+    <t>doi: 10.3354/meps07742</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/eff.12109</t>
+  </si>
+  <si>
+    <t>SUIE Thesis</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/00028487.2015.1121925</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/tafs.10433</t>
+  </si>
+  <si>
+    <t>GSU Thesis</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3354/esr01390</t>
+  </si>
+  <si>
+    <t>https://openfishsciencejournal.com/VOLUME/5/</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/j.1365-294X.2010.04655.x</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/ece3.4556</t>
+  </si>
+  <si>
+    <t>Purdue Thesis</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -581,13 +740,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -610,7 +762,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -628,10 +780,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -971,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
@@ -989,13 +1137,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -1007,1029 +1155,1351 @@
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>23</v>
+      <c r="G4" s="5" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8" t="s">
-        <v>169</v>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="E10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="3" t="s">
+    </row>
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
+      <c r="B13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>191</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>55</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>116</v>
+      <c r="G19" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>143</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>140</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>146</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G21" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G22" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>10</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>132</v>
+      <c r="G23" s="5" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>135</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>68</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G25" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>99</v>
+      <c r="G26" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G27" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>107</v>
+      <c r="G28" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>138</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>144</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>94</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>10</v>
+        <v>96</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>132</v>
+      <c r="G30" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>73</v>
+        <v>174</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>74</v>
+        <v>175</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>75</v>
+        <v>179</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>76</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G33" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>111</v>
+        <v>102</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>109</v>
+      <c r="G34" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>80</v>
+        <v>184</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>81</v>
+        <v>186</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G38" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>162</v>
+        <v>71</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G39" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G40" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>85</v>
+        <v>106</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G43" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>154</v>
+      <c r="G44" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A46" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" s="2" t="s">
+      <c r="B47" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B46" s="2" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A48" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A49" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A51" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A53" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A54" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="B50" s="6"/>
-      <c r="G50" s="5"/>
-    </row>
-    <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="D57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="B61" s="6"/>
+      <c r="G61" s="5"/>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G62" s="5"/>
+    </row>
+    <row r="65" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H58">
+    <sortCondition ref="A58"/>
+  </sortState>
   <hyperlinks>
     <hyperlink ref="G6" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G10" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G26" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G28" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G31" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G19" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G46" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G30" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G34" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G38" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G23" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G47" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G49" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G3" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
+    <hyperlink ref="G4" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
+    <hyperlink ref="G13" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G15" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G16" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G22" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G31" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G39" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G40" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G56" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="570" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D15A53C-7EDC-E441-B5BE-695E0F8482A0}"/>
+  <xr:revisionPtr revIDLastSave="584" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF5E8B23-BEC0-FC44-B80A-7A54C952A567}"/>
   <bookViews>
     <workbookView xWindow="13380" yWindow="-21100" windowWidth="20640" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="227">
   <si>
     <t>Study_ID</t>
   </si>
@@ -705,6 +705,18 @@
   </si>
   <si>
     <t>Purdue Thesis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITH-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siphateles t.s. </t>
+  </si>
+  <si>
+    <t>Tui chub</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-008-9529-x</t>
   </si>
 </sst>
 </file>
@@ -1119,12 +1131,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2"/>
     <col min="2" max="2" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="2"/>
@@ -2446,15 +2458,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
@@ -2466,20 +2478,47 @@
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A59" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="B61" s="6"/>
-      <c r="G61" s="5"/>
-    </row>
     <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="B62" s="6"/>
       <c r="G62" s="5"/>
     </row>
-    <row r="65" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G63" s="5"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+    </row>
+    <row r="66" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H58">
-    <sortCondition ref="A58"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H59">
+    <sortCondition ref="A59"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G6" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -808,10 +808,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="584" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF5E8B23-BEC0-FC44-B80A-7A54C952A567}"/>
+  <xr:revisionPtr revIDLastSave="725" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7970E93-7CCD-A245-A335-570EE6C5C07E}"/>
   <bookViews>
-    <workbookView xWindow="13380" yWindow="-21100" windowWidth="20640" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="14400" yWindow="-21100" windowWidth="19580" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="273">
   <si>
     <t>Study_ID</t>
   </si>
@@ -717,6 +717,144 @@
   </si>
   <si>
     <t>DOI 10.1007/s10592-008-9529-x</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/mec.16317</t>
+  </si>
+  <si>
+    <t>LEMA-1</t>
+  </si>
+  <si>
+    <t>NOAT-2</t>
+  </si>
+  <si>
+    <t>PIVI-1</t>
+  </si>
+  <si>
+    <t>ICPU-3</t>
+  </si>
+  <si>
+    <t>DOCE-1</t>
+  </si>
+  <si>
+    <t>APGR-1</t>
+  </si>
+  <si>
+    <t>Bluegill</t>
+  </si>
+  <si>
+    <t>Bullhead Minnow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gizzard Shad </t>
+  </si>
+  <si>
+    <t>Freshwater Drum</t>
+  </si>
+  <si>
+    <t>Lepomis macrochirus</t>
+  </si>
+  <si>
+    <t>Pimephales vigilax</t>
+  </si>
+  <si>
+    <t>Aplodinotus grunniens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Sciaenidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Dorosomatidae</t>
+  </si>
+  <si>
+    <t>Dorosoma cepedianum</t>
+  </si>
+  <si>
+    <t>ETLE-1</t>
+  </si>
+  <si>
+    <t>Tuxedo Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma lemniscatum</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/ece3.6064</t>
+  </si>
+  <si>
+    <t>CYGI-1</t>
+  </si>
+  <si>
+    <t>ETTA-1</t>
+  </si>
+  <si>
+    <t>Etheostoma tallapoosae</t>
+  </si>
+  <si>
+    <t>Tallapoosa Darter</t>
+  </si>
+  <si>
+    <t>Cyprinella gibbsi</t>
+  </si>
+  <si>
+    <t>Tallapoosa Shiner</t>
+  </si>
+  <si>
+    <t>CYGI-2</t>
+  </si>
+  <si>
+    <t>ETTA-2</t>
+  </si>
+  <si>
+    <t>doi:10.1111/fwb.12283</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/tafs.10296</t>
+  </si>
+  <si>
+    <t>ARIN-1</t>
+  </si>
+  <si>
+    <t>Sacromento Perch</t>
+  </si>
+  <si>
+    <t>Archoplites interruptus</t>
+  </si>
+  <si>
+    <t>Centrarchidae</t>
+  </si>
+  <si>
+    <t>Mottled Sculpin</t>
+  </si>
+  <si>
+    <t>COBA-1</t>
+  </si>
+  <si>
+    <t>Cottidae</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/j.1600-0633.2011.00525.x</t>
+  </si>
+  <si>
+    <t>Cottus bairdii</t>
+  </si>
+  <si>
+    <t>COBA-2</t>
+  </si>
+  <si>
+    <t>doi:10.1111/jfb.13101</t>
+  </si>
+  <si>
+    <t>CASA-1</t>
+  </si>
+  <si>
+    <t>Catostomus santaanae</t>
+  </si>
+  <si>
+    <t>Santa Ana Sucker</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/mec.14445</t>
   </si>
 </sst>
 </file>
@@ -1127,10 +1265,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.33203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -1212,110 +1350,110 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>87</v>
+        <v>233</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>241</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
-        <v>207</v>
+      <c r="G4" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>115</v>
+        <v>258</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>116</v>
+        <v>259</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>117</v>
+        <v>260</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>26</v>
+      <c r="G6" s="5" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
-        <v>164</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>165</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>162</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
@@ -1323,22 +1461,22 @@
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G8" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>29</v>
+        <v>269</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>11</v>
@@ -1347,67 +1485,67 @@
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>33</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>263</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>264</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G10" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>28</v>
+        <v>267</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>262</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>29</v>
+        <v>266</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>264</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G11" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>172</v>
+        <v>248</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>171</v>
+        <v>252</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
@@ -1415,22 +1553,22 @@
       <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G12" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>254</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>35</v>
+        <v>253</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>36</v>
+        <v>252</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
@@ -1438,22 +1576,22 @@
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>208</v>
+      <c r="G13" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>192</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
@@ -1462,21 +1600,21 @@
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>164</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
@@ -1484,22 +1622,22 @@
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G15" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>232</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>236</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>11</v>
@@ -1507,19 +1645,19 @@
       <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G16" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>30</v>
@@ -1530,160 +1668,160 @@
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>46</v>
+      <c r="G17" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>191</v>
+        <v>31</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>194</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A23" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>11</v>
@@ -1691,22 +1829,22 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G24" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
@@ -1714,22 +1852,22 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>215</v>
+      <c r="G25" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -1737,114 +1875,114 @@
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>60</v>
+      <c r="G26" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>121</v>
+        <v>191</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>130</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>66</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>92</v>
+        <v>255</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>61</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G30" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -1852,22 +1990,22 @@
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G31" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>174</v>
+        <v>48</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>176</v>
+        <v>53</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
@@ -1876,64 +2014,64 @@
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>179</v>
+        <v>91</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>183</v>
+      <c r="G33" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>9</v>
@@ -1948,38 +2086,38 @@
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>185</v>
+        <v>56</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>186</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>187</v>
+      <c r="G36" s="2" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>126</v>
+        <v>57</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>9</v>
@@ -1991,18 +2129,18 @@
         <v>6</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>9</v>
@@ -2013,68 +2151,68 @@
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G38" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G39" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G40" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>109</v>
+        <v>231</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>
@@ -2083,44 +2221,44 @@
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G42" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>11</v>
@@ -2128,22 +2266,22 @@
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>133</v>
+      <c r="G43" s="5" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>156</v>
+        <v>228</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>79</v>
+        <v>238</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>11</v>
@@ -2152,87 +2290,87 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>79</v>
+        <v>175</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>30</v>
+        <v>178</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>9</v>
@@ -2244,297 +2382,637 @@
         <v>6</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>89</v>
+        <v>184</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>220</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A53" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="E54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A53" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="E55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="E56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="2" t="s">
+      <c r="E57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>155</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A60" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A61" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A66" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A67" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A68" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A71" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="E74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="B62" s="6"/>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G63" s="5"/>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.15">
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-    </row>
-    <row r="66" spans="2:3" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="H79" s="2"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H59">
-    <sortCondition ref="A59"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H79">
+    <sortCondition ref="A42:A79"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="G6" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G10" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G30" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G34" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G38" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G23" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G47" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G49" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G18" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G42" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G47" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G52" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G34" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G62" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G64" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G3" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
-    <hyperlink ref="G4" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G13" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G15" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G16" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G22" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G31" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G39" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G40" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G56" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G6" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
+    <hyperlink ref="G22" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G24" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G25" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G33" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G43" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G53" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G54" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G71" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="725" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7970E93-7CCD-A245-A335-570EE6C5C07E}"/>
+  <xr:revisionPtr revIDLastSave="735" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C663533B-D286-E647-9B3E-19B64C69CA38}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="-21100" windowWidth="19580" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="3560" yWindow="-21100" windowWidth="30420" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="277">
   <si>
     <t>Study_ID</t>
   </si>
@@ -855,6 +855,18 @@
   </si>
   <si>
     <t>DOI: 10.1111/mec.14445</t>
+  </si>
+  <si>
+    <t>COGR-1</t>
+  </si>
+  <si>
+    <t>Shoshone sculpin</t>
+  </si>
+  <si>
+    <t>Cottus greenei</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/fishes8010055</t>
   </si>
 </sst>
 </file>
@@ -1534,32 +1546,32 @@
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>256</v>
+      <c r="G12" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>253</v>
@@ -1582,13 +1594,13 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>127</v>
+        <v>254</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
@@ -1600,21 +1612,21 @@
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>130</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
@@ -1623,21 +1635,21 @@
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>243</v>
+        <v>166</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>11</v>
@@ -1646,21 +1658,21 @@
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>28</v>
+        <v>236</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>29</v>
+        <v>243</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>11</v>
@@ -1669,12 +1681,12 @@
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>33</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
@@ -1691,15 +1703,15 @@
       <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C19" s="2" t="s">
@@ -1714,19 +1726,19 @@
       <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>169</v>
+      <c r="G19" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>30</v>
@@ -1738,64 +1750,64 @@
         <v>6</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>247</v>
+      <c r="G21" s="5" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G22" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>30</v>
@@ -1806,19 +1818,19 @@
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>195</v>
+      <c r="G23" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -1829,19 +1841,19 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>210</v>
+      <c r="G24" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -1853,18 +1865,18 @@
         <v>6</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -1875,59 +1887,59 @@
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>46</v>
+      <c r="G26" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>195</v>
+      <c r="G27" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>251</v>
@@ -1950,59 +1962,59 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>119</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>212</v>
+      <c r="G30" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>213</v>
+      <c r="G31" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>52</v>
@@ -2017,9 +2029,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>53</v>
@@ -2036,65 +2048,65 @@
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>214</v>
+      <c r="G33" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A35" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B35" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G34" s="5" t="s">
+      <c r="E35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A35" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>9</v>
@@ -2106,18 +2118,18 @@
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>215</v>
+        <v>144</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>9</v>
@@ -2129,18 +2141,18 @@
         <v>6</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>60</v>
+        <v>215</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>9</v>
@@ -2152,35 +2164,35 @@
         <v>6</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>63</v>
@@ -2198,12 +2210,12 @@
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>63</v>
@@ -2215,70 +2227,70 @@
         <v>64</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A42" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A42" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A44" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A44" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>21</v>
@@ -2289,68 +2301,68 @@
       <c r="F44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A45" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A45" s="2" t="s">
+    <row r="46" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A46" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" s="2" t="s">
+      <c r="E46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>65</v>
@@ -2358,82 +2370,82 @@
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G47" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G48" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A49" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A49" s="2" t="s">
+    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A50" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B50" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E50" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G49" s="5" t="s">
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A50" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>124</v>
@@ -2451,18 +2463,18 @@
         <v>6</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>9</v>
@@ -2473,22 +2485,22 @@
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>105</v>
+      <c r="G52" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -2497,41 +2509,41 @@
         <v>6</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>218</v>
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>76</v>
@@ -2542,48 +2554,48 @@
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G55" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>6</v>
@@ -2594,7 +2606,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>78</v>
@@ -2612,12 +2624,12 @@
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>78</v>
@@ -2629,93 +2641,93 @@
         <v>30</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="2" t="s">
+      <c r="E62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>9</v>
@@ -2726,13 +2738,13 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G63" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>89</v>
@@ -2749,36 +2761,36 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="5" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>81</v>
@@ -2796,35 +2808,35 @@
         <v>6</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>221</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>83</v>
@@ -2842,21 +2854,21 @@
         <v>6</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -2865,12 +2877,12 @@
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>158</v>
@@ -2888,41 +2900,41 @@
         <v>6</v>
       </c>
       <c r="G70" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A71" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A71" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>151</v>
+        <v>85</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>9</v>
@@ -2934,18 +2946,18 @@
         <v>6</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>224</v>
+        <v>151</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>9</v>
@@ -2956,19 +2968,19 @@
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G73" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>9</v>
@@ -2980,39 +2992,64 @@
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G77" s="5"/>
+    </row>
     <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="H79" s="2"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H79">
-    <sortCondition ref="A42:A79"/>
+    <sortCondition ref="A64:A79"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G18" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G42" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G47" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G52" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G34" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G62" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G64" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G19" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G43" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G48" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G53" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G35" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G63" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G65" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G3" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G6" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G22" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G24" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G25" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G33" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G43" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G53" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G54" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G71" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G23" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G25" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G26" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G34" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G44" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G54" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G55" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G72" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G12" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="735" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C663533B-D286-E647-9B3E-19B64C69CA38}"/>
+  <xr:revisionPtr revIDLastSave="787" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{119D430D-51DA-0A43-BAFB-0297F218EC46}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="-21100" windowWidth="30420" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-3540" yWindow="-21100" windowWidth="37520" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="293">
   <si>
     <t>Study_ID</t>
   </si>
@@ -867,6 +867,54 @@
   </si>
   <si>
     <t>https://doi.org/10.3390/fishes8010055</t>
+  </si>
+  <si>
+    <t>MIDO-1</t>
+  </si>
+  <si>
+    <t>Smallmouth Bass</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/tafs.10238</t>
+  </si>
+  <si>
+    <t>Micropterus dolomieu</t>
+  </si>
+  <si>
+    <t>ONMY-3</t>
+  </si>
+  <si>
+    <t>California Golden Trout</t>
+  </si>
+  <si>
+    <t>Oncorhynchus mykiss aguabonita</t>
+  </si>
+  <si>
+    <t>DOI: 10.1577/T05-120.1</t>
+  </si>
+  <si>
+    <t>SEAT-2</t>
+  </si>
+  <si>
+    <t>DOI: 10.1577/T07-060.1</t>
+  </si>
+  <si>
+    <t>ONCL-3</t>
+  </si>
+  <si>
+    <t>Cutthroat Trout</t>
+  </si>
+  <si>
+    <t>Oncorhynchus clarkii</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1577/1548-8659(2002)131&lt;0376:PGSILC&gt;2.0.CO;2</t>
+  </si>
+  <si>
+    <t>SACO-3</t>
+  </si>
+  <si>
+    <t>DOI: 10.1577/T05-166.1</t>
   </si>
 </sst>
 </file>
@@ -1277,16 +1325,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="2"/>
-    <col min="7" max="7" width="44.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="58.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -2397,7 +2445,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>136</v>
       </c>
@@ -2420,55 +2468,55 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A51" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B51" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="5" t="s">
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A52" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>124</v>
@@ -2486,18 +2534,18 @@
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>9</v>
@@ -2508,65 +2556,65 @@
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G53" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A54" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
+    <row r="55" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D55" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="5" t="s">
+      <c r="E55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>76</v>
@@ -2577,180 +2625,181 @@
       <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G56" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A59" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A60" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H60" s="2"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A61" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D61" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="E61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="E62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A60" s="2" t="s">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="F63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>9</v>
@@ -2762,283 +2811,390 @@
         <v>6</v>
       </c>
       <c r="G64" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A66" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A67" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
+    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A68" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B68" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="5" t="s">
+      <c r="E68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A66" s="2" t="s">
+    <row r="69" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A67" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A68" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A71" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="2" t="s">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="2" t="s">
+      <c r="E74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A71" s="2" t="s">
+    <row r="75" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="2" t="s">
+      <c r="E75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="2" t="s">
+    <row r="76" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A76" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B76" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D76" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="5" t="s">
+      <c r="E76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A77" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B78" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="5" t="s">
+      <c r="E78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G78" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
+    <row r="79" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A79" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B79" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C79" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="2" t="s">
+      <c r="E79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A80" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C75" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D75" s="2" t="s">
+      <c r="D80" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G75" s="2" t="s">
+      <c r="E80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G77" s="5"/>
-    </row>
-    <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="H79" s="2"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H79">
-    <sortCondition ref="A64:A79"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H82">
+    <sortCondition ref="A39:A82"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G8" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G19" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
     <hyperlink ref="G43" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
     <hyperlink ref="G48" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G53" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G54" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
     <hyperlink ref="G35" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G63" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G65" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G66" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G68" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G3" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G6" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
     <hyperlink ref="G23" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
@@ -3046,10 +3202,11 @@
     <hyperlink ref="G26" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
     <hyperlink ref="G34" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
     <hyperlink ref="G44" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G54" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G55" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G72" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G55" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G56" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G76" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G12" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G58" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="787" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{119D430D-51DA-0A43-BAFB-0297F218EC46}"/>
+  <xr:revisionPtr revIDLastSave="796" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E386C3B2-62E2-8B42-AC07-36AE5365744D}"/>
   <bookViews>
-    <workbookView xWindow="-3540" yWindow="-21100" windowWidth="37520" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="9680" yWindow="-21100" windowWidth="24240" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="295">
   <si>
     <t>Study_ID</t>
   </si>
@@ -915,6 +915,12 @@
   </si>
   <si>
     <t>DOI: 10.1577/T05-166.1</t>
+  </si>
+  <si>
+    <t>SACO-4</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-024-01649-z</t>
   </si>
 </sst>
 </file>
@@ -1006,6 +1012,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1325,7 +1335,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -2943,7 +2953,7 @@
         <v>76</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>6</v>
@@ -2966,7 +2976,7 @@
         <v>76</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>6</v>
@@ -3180,6 +3190,29 @@
       </c>
       <c r="G80" s="2" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A81" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -3207,6 +3240,7 @@
     <hyperlink ref="G76" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G12" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
     <hyperlink ref="G58" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G81" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="796" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E386C3B2-62E2-8B42-AC07-36AE5365744D}"/>
+  <xr:revisionPtr revIDLastSave="797" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B64BA96C-D781-414C-ADB6-24C100D0D56B}"/>
   <bookViews>
-    <workbookView xWindow="9680" yWindow="-21100" windowWidth="24240" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="9680" yWindow="-21100" windowWidth="24240" windowHeight="21100" activeTab="1" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
@@ -1012,10 +1013,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3244,4 +3241,13 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10412BD-3C21-D945-B559-C622027104B5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="797" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B64BA96C-D781-414C-ADB6-24C100D0D56B}"/>
+  <xr:revisionPtr revIDLastSave="839" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51754661-AD78-C84F-A5FA-57937B85B0AD}"/>
   <bookViews>
     <workbookView xWindow="9680" yWindow="-21100" windowWidth="24240" windowHeight="21100" activeTab="1" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="processed_data" sheetId="1" r:id="rId1"/>
+    <sheet name="data_to_add" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029" concurrentCalc="0"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="315">
   <si>
     <t>Study_ID</t>
   </si>
@@ -922,6 +922,66 @@
   </si>
   <si>
     <t>https://doi.org/10.1007/s10592-024-01649-z</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/mec.13517</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/j.1365-294X.2008.03710.x</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/tafs.10388</t>
+  </si>
+  <si>
+    <t>RHOS-3</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-008-9652-8</t>
+  </si>
+  <si>
+    <t>ONCL-4</t>
+  </si>
+  <si>
+    <t>SAFO</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/tafafs/vnaf045</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/tafs.10260</t>
+  </si>
+  <si>
+    <t>POSP-2</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/tafs.10419</t>
+  </si>
+  <si>
+    <t>ICBU-1</t>
+  </si>
+  <si>
+    <t>PERI</t>
+  </si>
+  <si>
+    <t>doi:10.1111/fwb.12190</t>
+  </si>
+  <si>
+    <t>NOHU</t>
+  </si>
+  <si>
+    <t>ONMY</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3955/046.085.0305</t>
+  </si>
+  <si>
+    <t>SACO</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/nafm.10618</t>
+  </si>
+  <si>
+    <t>SITH</t>
   </si>
 </sst>
 </file>
@@ -979,7 +1039,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -996,6 +1056,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3245,9 +3311,131 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10412BD-3C21-D945-B559-C622027104B5}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="7"/>
+    <col min="2" max="2" width="38" style="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{270CE535-C8D5-5748-AC78-B94307888FFC}"/>
+    <hyperlink ref="B7" r:id="rId2" xr:uid="{7EC1CDF4-A767-7849-8534-85910A46FFAF}"/>
+    <hyperlink ref="B12" r:id="rId3" xr:uid="{6AA1709D-7D14-2F47-99CE-E6DE53104C77}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="839" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51754661-AD78-C84F-A5FA-57937B85B0AD}"/>
   <bookViews>
-    <workbookView xWindow="9680" yWindow="-21100" windowWidth="24240" windowHeight="21100" activeTab="1" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="9680" yWindow="-21100" windowWidth="24240" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="839" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51754661-AD78-C84F-A5FA-57937B85B0AD}"/>
+  <xr:revisionPtr revIDLastSave="918" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1370D5F-246E-9542-91B6-E5EC1087BC1A}"/>
   <bookViews>
-    <workbookView xWindow="9680" yWindow="-21100" windowWidth="24240" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-2040" yWindow="-21100" windowWidth="35960" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="333">
   <si>
     <t>Study_ID</t>
   </si>
@@ -982,6 +982,60 @@
   </si>
   <si>
     <t>SITH</t>
+  </si>
+  <si>
+    <t>MIDO-2</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/mec.14079</t>
+  </si>
+  <si>
+    <t>Agosia chrysogaster</t>
+  </si>
+  <si>
+    <t>AGCH-1</t>
+  </si>
+  <si>
+    <t>Longfin dace</t>
+  </si>
+  <si>
+    <t>Yellow Bullhead</t>
+  </si>
+  <si>
+    <t>Ameiurus natalis</t>
+  </si>
+  <si>
+    <t>CAIN-1</t>
+  </si>
+  <si>
+    <t>Catostomus insignis</t>
+  </si>
+  <si>
+    <t>Sonora sucker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Catostomidae</t>
+  </si>
+  <si>
+    <t>GINI-2</t>
+  </si>
+  <si>
+    <t>MEFU-2</t>
+  </si>
+  <si>
+    <t>PACL-1</t>
+  </si>
+  <si>
+    <t>Pantosteus clarkii</t>
+  </si>
+  <si>
+    <t>Desert Sucker</t>
+  </si>
+  <si>
+    <t>TICO-2</t>
+  </si>
+  <si>
+    <t>AMNA-1</t>
   </si>
 </sst>
 </file>
@@ -1079,6 +1133,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1398,7 +1456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -1439,13 +1497,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>318</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>319</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>13</v>
+        <v>317</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -1457,21 +1515,21 @@
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>332</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>320</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -1479,160 +1537,160 @@
       <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>208</v>
+      <c r="G3" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C9" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>270</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>272</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>263</v>
+        <v>322</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>264</v>
+        <v>325</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>65</v>
@@ -1641,136 +1699,136 @@
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>265</v>
+        <v>316</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>267</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>262</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>266</v>
+        <v>24</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>264</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G11" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>275</v>
+        <v>269</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>264</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>276</v>
+      <c r="G12" s="2" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>127</v>
+        <v>273</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>128</v>
+        <v>274</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>129</v>
+        <v>275</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>130</v>
+      <c r="G15" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>164</v>
+        <v>248</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>165</v>
+        <v>253</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>11</v>
@@ -1779,21 +1837,21 @@
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>167</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>242</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>11</v>
@@ -1802,21 +1860,21 @@
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>227</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>127</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -1825,21 +1883,21 @@
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
@@ -1847,22 +1905,22 @@
       <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>32</v>
+      <c r="G19" s="2" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>28</v>
+        <v>232</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>236</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>29</v>
+        <v>243</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -1870,19 +1928,19 @@
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>169</v>
+      <c r="G20" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>172</v>
+        <v>27</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>30</v>
@@ -1893,42 +1951,42 @@
       <c r="F21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>173</v>
+      <c r="G21" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>244</v>
+        <v>31</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>245</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>246</v>
+        <v>29</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>247</v>
+      <c r="G22" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>35</v>
+        <v>168</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>30</v>
@@ -1940,18 +1998,18 @@
         <v>6</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>208</v>
+        <v>169</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>196</v>
+        <v>170</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -1962,42 +2020,42 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G24" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>38</v>
+        <v>244</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>39</v>
+        <v>246</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>210</v>
+      <c r="G25" s="2" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -2009,18 +2067,18 @@
         <v>6</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>190</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>43</v>
+        <v>196</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>44</v>
+        <v>192</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
@@ -2031,42 +2089,42 @@
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G27" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>191</v>
+        <v>38</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>194</v>
+        <v>37</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>193</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G28" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>249</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>251</v>
+        <v>40</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>250</v>
+        <v>41</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -2077,19 +2135,19 @@
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>256</v>
+      <c r="G29" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>255</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>251</v>
+        <v>43</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2100,22 +2158,22 @@
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>256</v>
+      <c r="G30" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>119</v>
+        <v>194</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>120</v>
+        <v>193</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>65</v>
@@ -2123,22 +2181,22 @@
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>212</v>
+      <c r="G31" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>47</v>
+        <v>249</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>51</v>
+        <v>251</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>49</v>
+        <v>250</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
@@ -2147,21 +2205,21 @@
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>48</v>
+        <v>255</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>53</v>
+        <v>251</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
@@ -2170,44 +2228,44 @@
         <v>6</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G34" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
@@ -2215,22 +2273,22 @@
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>114</v>
+      <c r="G35" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>135</v>
+        <v>48</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -2239,21 +2297,21 @@
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>11</v>
@@ -2261,22 +2319,22 @@
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>215</v>
+      <c r="G37" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>57</v>
+        <v>110</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
@@ -2284,19 +2342,19 @@
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>60</v>
+      <c r="G38" s="5" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>122</v>
+        <v>141</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>9</v>
@@ -2308,228 +2366,228 @@
         <v>6</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>62</v>
+        <v>326</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>66</v>
+        <v>316</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>231</v>
+        <v>57</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A43" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A44" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A43" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="5" t="s">
-        <v>217</v>
+      <c r="G44" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>234</v>
+        <v>63</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>238</v>
+        <v>61</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A46" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>180</v>
+        <v>94</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>181</v>
+        <v>95</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>182</v>
+        <v>96</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>183</v>
+      <c r="G47" s="5" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>102</v>
+        <v>67</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>103</v>
+        <v>68</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>136</v>
+        <v>228</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>142</v>
+        <v>234</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>139</v>
+        <v>238</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>11</v>
@@ -2538,21 +2596,21 @@
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>277</v>
+        <v>174</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>280</v>
+        <v>175</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>261</v>
+        <v>178</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
@@ -2561,21 +2619,21 @@
         <v>6</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>185</v>
+        <v>179</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>180</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>65</v>
@@ -2583,42 +2641,42 @@
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G51" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G52" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>229</v>
+        <v>136</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>9</v>
@@ -2630,18 +2688,18 @@
         <v>6</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>99</v>
+        <v>327</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>9</v>
@@ -2652,158 +2710,157 @@
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A59" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A60" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
+    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A61" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C61" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A60" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H60" s="2"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>30</v>
@@ -2814,341 +2871,342 @@
       <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A66" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H66" s="2"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A67" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A68" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D69" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="2" t="s">
+      <c r="E69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
+    <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B70" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C70" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D70" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E70" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="2" t="s">
+      <c r="F70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A71" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D71" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="E71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
+    <row r="72" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="2" t="s">
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A66" s="2" t="s">
+    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D66" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="5" t="s">
+      <c r="E73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A67" s="2" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D67" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="2" t="s">
+      <c r="E74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A68" s="2" t="s">
+    <row r="75" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D68" s="2" t="s">
+      <c r="D75" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="5" t="s">
+      <c r="E75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="5" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A71" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>85</v>
+        <v>298</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>9</v>
@@ -3159,45 +3217,45 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G76" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>285</v>
+        <v>80</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>151</v>
+        <v>160</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -3205,22 +3263,22 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G78" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>224</v>
+        <v>291</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -3229,21 +3287,21 @@
         <v>6</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>137</v>
+        <v>293</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -3251,19 +3309,19 @@
       <c r="F80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G80" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>76</v>
@@ -3274,36 +3332,243 @@
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="5" t="s">
-        <v>294</v>
+      <c r="G81" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A82" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A83" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A84" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A85" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A87" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A88" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A89" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A90" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H82">
-    <sortCondition ref="A39:A82"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H90">
+    <sortCondition ref="A54:A90"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G19" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G43" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G48" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G54" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G35" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G66" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G68" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
-    <hyperlink ref="G3" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
-    <hyperlink ref="G6" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G23" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G25" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G26" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G34" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G44" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G55" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G56" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G76" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G12" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G58" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G81" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G22" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G47" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G52" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G60" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G38" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G73" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G75" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
+    <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
+    <hyperlink ref="G26" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G28" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G29" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G37" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G48" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G61" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G62" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G85" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G64" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G80" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="918" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1370D5F-246E-9542-91B6-E5EC1087BC1A}"/>
+  <xr:revisionPtr revIDLastSave="924" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3564E6D-02BF-7746-A8C9-2FC92058C7C8}"/>
   <bookViews>
     <workbookView xWindow="-2040" yWindow="-21100" windowWidth="35960" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="335">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1036,6 +1036,12 @@
   </si>
   <si>
     <t>AMNA-1</t>
+  </si>
+  <si>
+    <t>ETCA-4</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-014-0649-1</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -3541,6 +3547,29 @@
       </c>
       <c r="G90" s="2" t="s">
         <v>316</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A99" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="924" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3564E6D-02BF-7746-A8C9-2FC92058C7C8}"/>
+  <xr:revisionPtr revIDLastSave="933" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAD683E5-A604-4D4C-9467-FD50428BEFCC}"/>
   <bookViews>
     <workbookView xWindow="-2040" yWindow="-21100" windowWidth="35960" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="339">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1042,6 +1042,18 @@
   </si>
   <si>
     <t>DOI 10.1007/s10592-014-0649-1</t>
+  </si>
+  <si>
+    <t>MICA-1</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/nafm.10048</t>
+  </si>
+  <si>
+    <t>Shoal bass</t>
+  </si>
+  <si>
+    <t>Micropterus cataractae</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -2007,15 +2019,15 @@
         <v>169</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>170</v>
+        <v>333</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -2026,65 +2038,65 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G24" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G25" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G26" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
@@ -2095,19 +2107,19 @@
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G27" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
@@ -2118,19 +2130,19 @@
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>210</v>
+      <c r="G28" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -2142,18 +2154,18 @@
         <v>6</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2164,59 +2176,59 @@
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>46</v>
+      <c r="G30" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>195</v>
+      <c r="G31" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>251</v>
@@ -2239,59 +2251,59 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>119</v>
+        <v>251</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>212</v>
+      <c r="G34" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>213</v>
+      <c r="G35" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>52</v>
@@ -2306,9 +2318,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>53</v>
@@ -2325,59 +2337,59 @@
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="2" t="s">
+    <row r="39" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B39" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C39" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G38" s="5" t="s">
+      <c r="E39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A39" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>326</v>
+        <v>135</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>141</v>
@@ -2395,18 +2407,18 @@
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>9</v>
@@ -2418,18 +2430,18 @@
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>9</v>
@@ -2441,18 +2453,18 @@
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>60</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>9</v>
@@ -2464,35 +2476,35 @@
         <v>6</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>63</v>
@@ -2510,12 +2522,12 @@
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>63</v>
@@ -2527,70 +2539,70 @@
         <v>64</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G46" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G47" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A49" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G48" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A49" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>21</v>
@@ -2601,68 +2613,68 @@
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="2" t="s">
+      <c r="G49" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A50" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A50" s="2" t="s">
+    <row r="51" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A51" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="E51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A52" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>65</v>
@@ -2670,36 +2682,36 @@
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G52" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>144</v>
+      <c r="G53" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>327</v>
+        <v>136</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>142</v>
@@ -2717,21 +2729,21 @@
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>11</v>
@@ -2740,12 +2752,12 @@
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>278</v>
@@ -2763,58 +2775,58 @@
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
+    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B58" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="5" t="s">
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>124</v>
@@ -2832,18 +2844,18 @@
         <v>6</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>9</v>
@@ -2854,22 +2866,22 @@
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>105</v>
+      <c r="G60" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -2878,41 +2890,41 @@
         <v>6</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>218</v>
+        <v>105</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>76</v>
@@ -2923,19 +2935,19 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G63" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>288</v>
+        <v>106</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>289</v>
+        <v>108</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>76</v>
@@ -2946,69 +2958,68 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G64" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>132</v>
+        <v>288</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>133</v>
+      <c r="G65" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H66" s="2"/>
+        <v>133</v>
+      </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -3017,35 +3028,36 @@
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>316</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H67" s="2"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>78</v>
@@ -3063,12 +3075,12 @@
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>78</v>
@@ -3080,93 +3092,93 @@
         <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="2" t="s">
+      <c r="F71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A71" s="2" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A72" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B72" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D71" s="2" t="s">
+      <c r="D72" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="2" t="s">
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="2" t="s">
+    <row r="73" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B73" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D73" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="2" t="s">
+      <c r="E73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
+    <row r="74" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>9</v>
@@ -3177,13 +3189,13 @@
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G74" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>89</v>
@@ -3200,13 +3212,13 @@
       <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>204</v>
+      <c r="G75" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>89</v>
@@ -3223,36 +3235,36 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G76" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A77" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A78" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -3264,18 +3276,18 @@
         <v>76</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>291</v>
+        <v>160</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>81</v>
@@ -3293,12 +3305,12 @@
         <v>6</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>81</v>
@@ -3315,19 +3327,19 @@
       <c r="F80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G80" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>76</v>
@@ -3338,13 +3350,13 @@
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>221</v>
+      <c r="G81" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>83</v>
@@ -3362,21 +3374,21 @@
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -3385,12 +3397,12 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>158</v>
@@ -3408,35 +3420,35 @@
         <v>6</v>
       </c>
       <c r="G84" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A85" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A85" s="2" t="s">
+    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A86" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>86</v>
@@ -3453,19 +3465,19 @@
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G86" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>151</v>
+        <v>285</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>9</v>
@@ -3476,19 +3488,19 @@
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G87" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>224</v>
+        <v>151</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>9</v>
@@ -3499,19 +3511,19 @@
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G88" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
@@ -3523,12 +3535,12 @@
         <v>6</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>143</v>
@@ -3546,58 +3558,84 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A99" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B99" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>334</v>
-      </c>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A92" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="B100" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H90">
-    <sortCondition ref="A54:A90"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H91">
+    <sortCondition ref="A55:A91"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G22" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G47" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G52" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G60" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G38" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G73" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G75" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G48" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G53" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G61" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G39" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G74" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G76" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G26" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G28" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G29" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G37" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G48" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G61" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G62" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G85" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G27" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G29" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G30" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G38" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G49" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G62" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G63" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G86" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G64" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G80" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G65" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G81" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="933" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAD683E5-A604-4D4C-9467-FD50428BEFCC}"/>
+  <xr:revisionPtr revIDLastSave="934" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0CDDDE4-154F-DE45-AAF7-70F0D400473C}"/>
   <bookViews>
     <workbookView xWindow="-2040" yWindow="-21100" windowWidth="35960" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -2757,13 +2757,13 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>261</v>
@@ -2775,12 +2775,12 @@
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>278</v>
@@ -2798,58 +2798,58 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
+    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A59" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B59" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E59" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="5" t="s">
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>124</v>
@@ -2867,18 +2867,18 @@
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>9</v>
@@ -2889,22 +2889,22 @@
       <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>105</v>
+      <c r="G61" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -2913,41 +2913,41 @@
         <v>6</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>218</v>
+        <v>105</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>76</v>
@@ -2958,19 +2958,19 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G64" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>288</v>
+        <v>106</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>289</v>
+        <v>108</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>76</v>
@@ -2981,69 +2981,68 @@
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G65" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>132</v>
+        <v>288</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>133</v>
+      <c r="G66" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H67" s="2"/>
+        <v>133</v>
+      </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -3052,21 +3051,22 @@
         <v>6</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>316</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H68" s="2"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -3075,12 +3075,12 @@
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>133</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>78</v>
@@ -3098,12 +3098,12 @@
         <v>6</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>78</v>
@@ -3115,93 +3115,93 @@
         <v>30</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="D73" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="2" t="s">
+      <c r="E74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
+    <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A75" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>9</v>
@@ -3212,13 +3212,13 @@
       <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>203</v>
+      <c r="G75" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>89</v>
@@ -3235,13 +3235,13 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>204</v>
+      <c r="G76" s="2" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>89</v>
@@ -3258,36 +3258,36 @@
       <c r="F77" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>316</v>
+      <c r="G77" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>220</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>81</v>
@@ -3299,18 +3299,18 @@
         <v>76</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>291</v>
+        <v>160</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>81</v>
@@ -3328,12 +3328,12 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>81</v>
@@ -3350,19 +3350,19 @@
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G81" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>76</v>
@@ -3373,13 +3373,13 @@
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>221</v>
+      <c r="G82" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>83</v>
@@ -3397,21 +3397,21 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -3420,12 +3420,12 @@
         <v>6</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>158</v>
@@ -3443,35 +3443,35 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A86" s="2" t="s">
+    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A87" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A87" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>86</v>
@@ -3488,19 +3488,19 @@
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G87" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>151</v>
+        <v>285</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>9</v>
@@ -3511,19 +3511,19 @@
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G88" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>224</v>
+        <v>151</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
@@ -3534,19 +3534,19 @@
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G89" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>9</v>
@@ -3558,12 +3558,12 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>143</v>
@@ -3581,21 +3581,21 @@
         <v>6</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>337</v>
+        <v>143</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>338</v>
+        <v>140</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -3604,25 +3604,25 @@
         <v>6</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
     </row>
     <row r="100" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B100" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H91">
-    <sortCondition ref="A55:A91"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
+    <sortCondition ref="A58:A100"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G22" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
     <hyperlink ref="G48" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
     <hyperlink ref="G53" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G61" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G62" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
     <hyperlink ref="G39" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G74" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G76" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G75" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G77" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
     <hyperlink ref="G27" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
@@ -3630,12 +3630,12 @@
     <hyperlink ref="G30" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
     <hyperlink ref="G38" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
     <hyperlink ref="G49" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G62" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G63" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G86" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G63" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G64" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G87" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G65" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G81" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G66" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G82" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="934" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0CDDDE4-154F-DE45-AAF7-70F0D400473C}"/>
+  <xr:revisionPtr revIDLastSave="951" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2CB30C5-2ADB-CE40-BA13-BDFA40707FAF}"/>
   <bookViews>
-    <workbookView xWindow="-2040" yWindow="-21100" windowWidth="35960" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4340" yWindow="-21100" windowWidth="38260" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
     <sheet name="data_to_add" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="673" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="346">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1054,6 +1054,27 @@
   </si>
   <si>
     <t>Micropterus cataractae</t>
+  </si>
+  <si>
+    <t>ETOO-1</t>
+  </si>
+  <si>
+    <t>Etheostoma cf. oophylax</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-020-01300-7</t>
+  </si>
+  <si>
+    <t>Clarks Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma chienense</t>
+  </si>
+  <si>
+    <t>Relict Darter</t>
+  </si>
+  <si>
+    <t>ETCH-1</t>
   </si>
 </sst>
 </file>
@@ -2044,13 +2065,13 @@
     </row>
     <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>172</v>
+        <v>345</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>171</v>
+        <v>343</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -2062,64 +2083,64 @@
         <v>6</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G26" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G27" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
@@ -2130,19 +2151,19 @@
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G28" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -2153,19 +2174,19 @@
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>210</v>
+      <c r="G29" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2177,18 +2198,18 @@
         <v>6</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>45</v>
+        <v>339</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>342</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
+        <v>340</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2199,42 +2220,42 @@
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G31" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>191</v>
+        <v>42</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>193</v>
+        <v>41</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>195</v>
+      <c r="G32" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>249</v>
+        <v>45</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>251</v>
+        <v>43</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -2245,68 +2266,68 @@
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>256</v>
+      <c r="G33" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>118</v>
+        <v>249</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>119</v>
+        <v>251</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>212</v>
+      <c r="G35" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>47</v>
+        <v>255</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>51</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>49</v>
+        <v>250</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -2315,41 +2336,41 @@
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>213</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G37" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>52</v>
@@ -2360,88 +2381,88 @@
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>214</v>
+      <c r="G38" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A41" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="5" t="s">
+      <c r="E41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A40" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A41" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>9</v>
@@ -2453,18 +2474,18 @@
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>215</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>9</v>
@@ -2476,18 +2497,18 @@
         <v>6</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>60</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>9</v>
@@ -2499,58 +2520,58 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>130</v>
+        <v>215</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>216</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>63</v>
@@ -2562,211 +2583,211 @@
         <v>64</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G47" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A48" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A49" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A48" s="2" t="s">
+    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A50" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D50" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G48" s="5" t="s">
+      <c r="E50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A49" s="2" t="s">
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A51" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C51" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G49" s="5" t="s">
+      <c r="E51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A50" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>104</v>
+        <v>175</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>105</v>
+      <c r="G53" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>327</v>
+        <v>102</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>316</v>
+      <c r="G55" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>335</v>
+        <v>136</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>337</v>
+        <v>142</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>338</v>
+        <v>139</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
@@ -2775,21 +2796,21 @@
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>336</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -2798,18 +2819,18 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>261</v>
@@ -2821,87 +2842,87 @@
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>185</v>
+        <v>277</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>187</v>
+      <c r="G59" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A61" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>9</v>
@@ -2912,22 +2933,22 @@
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G62" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>71</v>
+        <v>229</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -2935,22 +2956,22 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>218</v>
+      <c r="G63" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
@@ -2959,21 +2980,21 @@
         <v>6</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -2981,19 +3002,19 @@
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>107</v>
+      <c r="G65" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>76</v>
@@ -3005,41 +3026,41 @@
         <v>6</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>76</v>
@@ -3050,46 +3071,45 @@
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H68" s="2"/>
+      <c r="G68" s="5" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>328</v>
+        <v>131</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>330</v>
+        <v>132</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>329</v>
+        <v>134</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>316</v>
+        <v>133</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -3098,21 +3118,22 @@
         <v>6</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H70" s="2"/>
     </row>
     <row r="71" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>156</v>
+        <v>328</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -3121,12 +3142,12 @@
         <v>6</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>155</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>78</v>
@@ -3138,27 +3159,27 @@
         <v>30</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -3167,41 +3188,41 @@
         <v>6</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>9</v>
@@ -3212,22 +3233,22 @@
       <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G75" s="5" t="s">
-        <v>146</v>
+      <c r="G75" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3236,18 +3257,18 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>9</v>
@@ -3259,12 +3280,12 @@
         <v>6</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>298</v>
+        <v>88</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>89</v>
@@ -3282,44 +3303,44 @@
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>316</v>
+        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>220</v>
+      <c r="G79" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>160</v>
+        <v>298</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -3328,12 +3349,12 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>161</v>
+        <v>316</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>81</v>
@@ -3345,18 +3366,18 @@
         <v>76</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>293</v>
+        <v>160</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>81</v>
@@ -3373,19 +3394,19 @@
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>294</v>
+      <c r="G82" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>76</v>
@@ -3397,18 +3418,18 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>153</v>
+        <v>293</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>76</v>
@@ -3419,22 +3440,22 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>154</v>
+      <c r="G84" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -3443,67 +3464,67 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>155</v>
+        <v>221</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A87" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C87" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D86" s="2" t="s">
+      <c r="D87" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A87" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>222</v>
+      <c r="G87" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -3512,18 +3533,18 @@
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>286</v>
+        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>151</v>
+        <v>85</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
@@ -3535,18 +3556,18 @@
         <v>6</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>9</v>
@@ -3558,18 +3579,18 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>9</v>
@@ -3580,19 +3601,19 @@
       <c r="F91" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G91" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>9</v>
@@ -3604,38 +3625,92 @@
         <v>6</v>
       </c>
       <c r="G92" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A93" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A94" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G96" s="5"/>
+    </row>
+    <row r="97" spans="2:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G97" s="5"/>
+    </row>
+    <row r="100" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B100" s="6"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
-    <sortCondition ref="A58:A100"/>
+    <sortCondition ref="A67:A100"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G22" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G48" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G53" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G62" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G39" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G75" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G77" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G50" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G55" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G64" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G41" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G77" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G79" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G27" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G29" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G30" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G38" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G49" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G63" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G64" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G87" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G28" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G30" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G32" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G40" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G51" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G65" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G66" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G89" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G66" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G82" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G68" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G84" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G25" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G31" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="951" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2CB30C5-2ADB-CE40-BA13-BDFA40707FAF}"/>
+  <xr:revisionPtr revIDLastSave="977" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52DE8E8C-F8BD-194A-B516-EB26BB7238F0}"/>
   <bookViews>
-    <workbookView xWindow="-4340" yWindow="-21100" windowWidth="38260" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16680" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="356">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1075,6 +1075,36 @@
   </si>
   <si>
     <t>ETCH-1</t>
+  </si>
+  <si>
+    <t>Etheostoma boschungi</t>
+  </si>
+  <si>
+    <t>Etheostoma tuscumbia</t>
+  </si>
+  <si>
+    <t>ETBO-1</t>
+  </si>
+  <si>
+    <t>ETTU-1</t>
+  </si>
+  <si>
+    <t>Slackwater Darter</t>
+  </si>
+  <si>
+    <t>Tuscumbia Darter</t>
+  </si>
+  <si>
+    <t>doi:10.1111/evo.12505</t>
+  </si>
+  <si>
+    <t>ONMY-2</t>
+  </si>
+  <si>
+    <t>Oncorhynchus mykiss</t>
+  </si>
+  <si>
+    <t>Steelhead Trout</t>
   </si>
 </sst>
 </file>
@@ -1495,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -1973,13 +2003,13 @@
     </row>
     <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>29</v>
+        <v>346</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>30</v>
@@ -1991,12 +2021,12 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>28</v>
@@ -2013,15 +2043,15 @@
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B23" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2036,13 +2066,13 @@
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G23" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>333</v>
+        <v>168</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>28</v>
@@ -2059,19 +2089,19 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>334</v>
+      <c r="G24" s="5" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>344</v>
+        <v>333</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>343</v>
+        <v>29</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -2082,19 +2112,19 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>341</v>
+      <c r="G25" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>172</v>
+        <v>345</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>171</v>
+        <v>343</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -2106,64 +2136,64 @@
         <v>6</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G27" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G28" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -2174,19 +2204,19 @@
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G29" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2197,19 +2227,19 @@
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>210</v>
+      <c r="G30" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>339</v>
+        <v>38</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>342</v>
+        <v>37</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2221,18 +2251,18 @@
         <v>6</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>42</v>
+        <v>339</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>40</v>
+        <v>342</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>41</v>
+        <v>340</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
@@ -2244,18 +2274,18 @@
         <v>6</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -2266,59 +2296,59 @@
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>46</v>
+      <c r="G33" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>195</v>
+      <c r="G34" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>251</v>
@@ -2341,39 +2371,39 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>119</v>
+        <v>251</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G37" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>51</v>
+        <v>349</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>351</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>49</v>
+        <v>347</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
@@ -2382,41 +2412,41 @@
         <v>6</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>213</v>
+        <v>352</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G39" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>52</v>
@@ -2427,88 +2457,88 @@
       <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A41" s="2" t="s">
+    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A43" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B43" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G41" s="5" t="s">
+      <c r="E43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A42" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A43" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>9</v>
@@ -2520,18 +2550,18 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>215</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>9</v>
@@ -2543,18 +2573,18 @@
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>60</v>
+        <v>316</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>9</v>
@@ -2566,58 +2596,58 @@
         <v>6</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>130</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>216</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>63</v>
@@ -2629,211 +2659,211 @@
         <v>64</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A50" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A51" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A50" s="2" t="s">
+    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A52" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B52" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C52" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D52" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="5" t="s">
+      <c r="E52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A53" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B53" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D53" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="5" t="s">
+      <c r="E53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="5" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A53" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>104</v>
+        <v>175</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>105</v>
+      <c r="G55" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>327</v>
+        <v>102</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>316</v>
+      <c r="G57" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>335</v>
+        <v>136</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>337</v>
+        <v>142</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>338</v>
+        <v>139</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -2842,21 +2872,21 @@
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>336</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -2865,18 +2895,18 @@
         <v>6</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>261</v>
@@ -2888,87 +2918,87 @@
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>185</v>
+        <v>277</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>187</v>
+      <c r="G61" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B64" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>9</v>
@@ -2979,22 +3009,22 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G64" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>71</v>
+        <v>229</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -3002,22 +3032,22 @@
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>218</v>
+      <c r="G65" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -3026,21 +3056,21 @@
         <v>6</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -3048,19 +3078,19 @@
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>107</v>
+      <c r="G67" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>76</v>
@@ -3072,41 +3102,41 @@
         <v>6</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>132</v>
+        <v>106</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>76</v>
@@ -3117,46 +3147,45 @@
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H70" s="2"/>
+      <c r="G70" s="5" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="71" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>328</v>
+        <v>131</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>330</v>
+        <v>132</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>329</v>
+        <v>134</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>316</v>
+        <v>133</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -3165,21 +3194,22 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>133</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H72" s="2"/>
     </row>
     <row r="73" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>156</v>
+        <v>328</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -3188,12 +3218,12 @@
         <v>6</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>155</v>
+        <v>316</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>78</v>
@@ -3205,27 +3235,27 @@
         <v>30</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>188</v>
+        <v>133</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -3234,41 +3264,41 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>9</v>
@@ -3279,22 +3309,22 @@
       <c r="F77" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="5" t="s">
-        <v>146</v>
+      <c r="G77" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -3303,18 +3333,18 @@
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>9</v>
@@ -3326,12 +3356,12 @@
         <v>6</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>298</v>
+        <v>88</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>89</v>
@@ -3349,44 +3379,44 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>220</v>
+      <c r="G81" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>160</v>
+        <v>298</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -3395,12 +3425,12 @@
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>161</v>
+        <v>316</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>81</v>
@@ -3412,18 +3442,18 @@
         <v>76</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>293</v>
+        <v>160</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>81</v>
@@ -3440,19 +3470,19 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>294</v>
+      <c r="G84" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>76</v>
@@ -3464,18 +3494,18 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>153</v>
+        <v>293</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>76</v>
@@ -3486,22 +3516,22 @@
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>154</v>
+      <c r="G86" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -3510,67 +3540,67 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>155</v>
+        <v>221</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A89" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C89" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D89" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A89" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>222</v>
+      <c r="G89" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -3579,18 +3609,18 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>286</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>151</v>
+        <v>85</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>9</v>
@@ -3602,18 +3632,18 @@
         <v>6</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B92" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>9</v>
@@ -3625,18 +3655,18 @@
         <v>6</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>9</v>
@@ -3647,19 +3677,19 @@
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G93" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>9</v>
@@ -3671,48 +3701,115 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A95" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A96" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G96" s="5"/>
-    </row>
-    <row r="97" spans="2:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G97" s="5"/>
     </row>
-    <row r="100" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B100" s="6"/>
+    </row>
+    <row r="104" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A104" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>295</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
-    <sortCondition ref="A67:A100"/>
+    <sortCondition ref="A66:A100"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G22" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G50" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G55" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G64" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G41" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G77" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G79" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G23" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G52" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G57" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G66" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G43" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G79" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G81" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G28" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G30" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G32" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G40" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G51" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G65" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G66" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G89" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G29" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G31" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G33" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G42" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G53" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G67" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G68" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G91" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G68" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G84" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G25" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G31" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G70" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G86" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G26" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G32" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="977" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52DE8E8C-F8BD-194A-B516-EB26BB7238F0}"/>
+  <xr:revisionPtr revIDLastSave="1000" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F706BBE4-8E20-ED4A-8701-02576E5520CF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16680" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="10420" yWindow="-21100" windowWidth="23500" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="359">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1105,6 +1105,15 @@
   </si>
   <si>
     <t>Steelhead Trout</t>
+  </si>
+  <si>
+    <t>Ictiobus bubalus</t>
+  </si>
+  <si>
+    <t>Smallmouth Buffalo</t>
+  </si>
+  <si>
+    <t>SAFO-3</t>
   </si>
 </sst>
 </file>
@@ -1202,10 +1211,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2647,30 +2652,30 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>62</v>
+        <v>306</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>63</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>66</v>
+        <v>305</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>63</v>
@@ -2688,12 +2693,12 @@
         <v>6</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>63</v>
@@ -2705,70 +2710,70 @@
         <v>64</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G51" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A52" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G52" s="2" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A52" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A54" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B54" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C54" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>21</v>
@@ -2779,68 +2784,68 @@
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
+    <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C56" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="2" t="s">
+      <c r="E56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>65</v>
@@ -2848,36 +2853,36 @@
       <c r="F57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G57" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>144</v>
+      <c r="G58" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>327</v>
+        <v>136</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>142</v>
@@ -2895,21 +2900,21 @@
         <v>6</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>337</v>
+        <v>142</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>338</v>
+        <v>139</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -2918,18 +2923,18 @@
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>261</v>
@@ -2941,12 +2946,12 @@
         <v>6</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>278</v>
@@ -2964,58 +2969,58 @@
         <v>6</v>
       </c>
       <c r="G62" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B64" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C64" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D63" s="2" t="s">
+      <c r="D64" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G63" s="5" t="s">
+      <c r="F64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="5" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>124</v>
@@ -3033,18 +3038,18 @@
         <v>6</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>9</v>
@@ -3055,22 +3060,22 @@
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="5" t="s">
-        <v>105</v>
+      <c r="G66" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -3079,41 +3084,41 @@
         <v>6</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>218</v>
+        <v>105</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>76</v>
@@ -3124,19 +3129,19 @@
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>107</v>
+      <c r="G69" s="5" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>288</v>
+        <v>106</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>289</v>
+        <v>108</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>76</v>
@@ -3147,69 +3152,68 @@
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>290</v>
+      <c r="G70" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>132</v>
+        <v>288</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>133</v>
+      <c r="G71" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H72" s="2"/>
+        <v>133</v>
+      </c>
     </row>
     <row r="73" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>328</v>
+        <v>281</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>330</v>
+        <v>282</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>329</v>
+        <v>283</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -3218,21 +3222,22 @@
         <v>6</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>316</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H73" s="2"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>77</v>
+        <v>328</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3241,12 +3246,12 @@
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>133</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>78</v>
@@ -3264,12 +3269,12 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>78</v>
@@ -3281,50 +3286,50 @@
         <v>30</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>201</v>
+        <v>9</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -3333,21 +3338,21 @@
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>147</v>
+        <v>199</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -3355,22 +3360,22 @@
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>146</v>
+      <c r="G79" s="2" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>88</v>
+        <v>304</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -3379,18 +3384,18 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>203</v>
+        <v>305</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>9</v>
@@ -3402,12 +3407,12 @@
         <v>6</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>298</v>
+        <v>88</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>89</v>
@@ -3425,44 +3430,44 @@
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>220</v>
+      <c r="G83" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>160</v>
+        <v>298</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -3471,12 +3476,12 @@
         <v>6</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>161</v>
+        <v>316</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>81</v>
@@ -3488,18 +3493,18 @@
         <v>76</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>293</v>
+        <v>160</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>81</v>
@@ -3516,19 +3521,19 @@
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>294</v>
+      <c r="G86" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>76</v>
@@ -3540,18 +3545,18 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>153</v>
+        <v>293</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>76</v>
@@ -3562,22 +3567,22 @@
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>154</v>
+      <c r="G88" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -3586,67 +3591,67 @@
         <v>6</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>155</v>
+        <v>221</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C91" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D90" s="2" t="s">
+      <c r="D91" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>222</v>
+      <c r="G91" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -3655,18 +3660,18 @@
         <v>6</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>286</v>
+        <v>206</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B93" s="6" t="s">
-        <v>151</v>
+        <v>85</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>9</v>
@@ -3678,18 +3683,18 @@
         <v>6</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>9</v>
@@ -3701,18 +3706,18 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>9</v>
@@ -3723,19 +3728,19 @@
       <c r="F95" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G95" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G95" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>9</v>
@@ -3747,14 +3752,80 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A97" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A98" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G97" s="5"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="B100" s="6"/>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A103" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>313</v>
+      </c>
     </row>
     <row r="104" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
@@ -3780,31 +3851,31 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
-    <sortCondition ref="A66:A100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H98">
+    <sortCondition ref="A2:A98"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G23" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G52" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G57" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G66" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G53" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G58" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G67" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
     <hyperlink ref="G43" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G79" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G81" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G81" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G83" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
     <hyperlink ref="G29" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
     <hyperlink ref="G31" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
     <hyperlink ref="G33" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
     <hyperlink ref="G42" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G53" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G67" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G68" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G91" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G54" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G68" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G69" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G93" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G70" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G86" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G71" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G88" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
     <hyperlink ref="G26" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
     <hyperlink ref="G32" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
   </hyperlinks>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1000" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F706BBE4-8E20-ED4A-8701-02576E5520CF}"/>
+  <xr:revisionPtr revIDLastSave="1017" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96EE4AF7-9F3F-CE41-899B-86EAC4A6CE7A}"/>
   <bookViews>
     <workbookView xWindow="10420" yWindow="-21100" windowWidth="23500" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="361">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1114,6 +1114,12 @@
   </si>
   <si>
     <t>SAFO-3</t>
+  </si>
+  <si>
+    <t>Rio Grande Cutthroat Trout</t>
+  </si>
+  <si>
+    <t>Oncorhynchus clarkii virginalis</t>
   </si>
 </sst>
 </file>
@@ -1530,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -3179,102 +3185,102 @@
         <v>290</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>132</v>
+        <v>300</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>359</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>134</v>
+        <v>360</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G73" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="H73" s="2"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>316</v>
-      </c>
+      <c r="H74" s="2"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A76" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>78</v>
@@ -3292,12 +3298,12 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>78</v>
@@ -3309,64 +3315,64 @@
         <v>30</v>
       </c>
       <c r="E77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A78" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" s="2" t="s">
+      <c r="F78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A78" s="2" t="s">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A79" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="2" t="s">
+      <c r="E79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="2" t="s">
+    <row r="80" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A80" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>198</v>
@@ -3384,41 +3390,41 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A81" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A81" s="2" t="s">
+    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A82" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C82" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A82" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>9</v>
@@ -3429,13 +3435,13 @@
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G82" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>89</v>
@@ -3452,13 +3458,13 @@
       <c r="F83" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G83" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G83" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>89</v>
@@ -3475,36 +3481,36 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>316</v>
+      <c r="G84" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>80</v>
+        <v>298</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>220</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>81</v>
@@ -3516,18 +3522,18 @@
         <v>76</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>291</v>
+        <v>160</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>81</v>
@@ -3545,12 +3551,12 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>81</v>
@@ -3567,19 +3573,19 @@
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G88" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>76</v>
@@ -3590,13 +3596,13 @@
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>221</v>
+      <c r="G89" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>83</v>
@@ -3614,90 +3620,90 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="2" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>205</v>
+        <v>358</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A93" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D92" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A93" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>222</v>
+      <c r="G93" s="2" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>86</v>
+        <v>158</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -3706,18 +3712,18 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>286</v>
+        <v>206</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>151</v>
+        <v>85</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>9</v>
@@ -3729,18 +3735,18 @@
         <v>6</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>224</v>
+        <v>285</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>9</v>
@@ -3752,18 +3758,18 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>9</v>
@@ -3774,19 +3780,19 @@
       <c r="F97" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G97" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G97" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>9</v>
@@ -3798,61 +3804,87 @@
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A99" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A100" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B100" s="6"/>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A103" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D103" s="2" t="s">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="B102" s="6"/>
+    </row>
+    <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B105" s="6"/>
+    </row>
+    <row r="106" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A106" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A104" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G104" s="2" t="s">
+      <c r="E106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="2" t="s">
         <v>295</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H98">
-    <sortCondition ref="A2:A98"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
+    <sortCondition ref="A2:A100"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
@@ -3861,8 +3893,8 @@
     <hyperlink ref="G58" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
     <hyperlink ref="G67" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
     <hyperlink ref="G43" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G81" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G83" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G82" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G84" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
     <hyperlink ref="G29" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
@@ -3872,10 +3904,10 @@
     <hyperlink ref="G54" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
     <hyperlink ref="G68" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
     <hyperlink ref="G69" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G93" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G95" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
     <hyperlink ref="G71" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G88" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G89" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
     <hyperlink ref="G26" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
     <hyperlink ref="G32" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
   </hyperlinks>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1017" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96EE4AF7-9F3F-CE41-899B-86EAC4A6CE7A}"/>
+  <xr:revisionPtr revIDLastSave="1068" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27C136E9-0E05-634C-8298-E7BA0AFC8DFE}"/>
   <bookViews>
-    <workbookView xWindow="10420" yWindow="-21100" windowWidth="23500" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="2720" yWindow="-21100" windowWidth="31200" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="373">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1120,6 +1120,42 @@
   </si>
   <si>
     <t>Oncorhynchus clarkii virginalis</t>
+  </si>
+  <si>
+    <t>SAFO-4</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/nafm.11033</t>
+  </si>
+  <si>
+    <t>RHOS-4</t>
+  </si>
+  <si>
+    <t>ETAK-1</t>
+  </si>
+  <si>
+    <t>NOHU-1</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/mec.15947</t>
+  </si>
+  <si>
+    <t>Bluemask Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma akatulo</t>
+  </si>
+  <si>
+    <t>Olympic Mudminnow</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-014-0627-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Esocidae</t>
+  </si>
+  <si>
+    <t>Novumbra hubbsi</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H106"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -2014,13 +2050,13 @@
     </row>
     <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>30</v>
@@ -2032,18 +2068,18 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>29</v>
+        <v>346</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>30</v>
@@ -2055,12 +2091,12 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>28</v>
@@ -2077,15 +2113,15 @@
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B24" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
@@ -2100,13 +2136,13 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>169</v>
+      <c r="G24" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>333</v>
+        <v>168</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>28</v>
@@ -2123,19 +2159,19 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G25" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>344</v>
+        <v>333</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>343</v>
+        <v>29</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>30</v>
@@ -2146,19 +2182,19 @@
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>341</v>
+      <c r="G26" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>172</v>
+        <v>345</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>171</v>
+        <v>343</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
@@ -2170,64 +2206,64 @@
         <v>6</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G28" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G29" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2238,19 +2274,19 @@
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G30" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2261,19 +2297,19 @@
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>210</v>
+      <c r="G31" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>339</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>342</v>
+        <v>37</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
@@ -2285,18 +2321,18 @@
         <v>6</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>42</v>
+        <v>339</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>40</v>
+        <v>342</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>41</v>
+        <v>340</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -2308,18 +2344,18 @@
         <v>6</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -2330,59 +2366,59 @@
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>46</v>
+      <c r="G34" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>195</v>
+      <c r="G35" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>251</v>
@@ -2403,15 +2439,15 @@
         <v>256</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>351</v>
+        <v>255</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>347</v>
+        <v>250</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>30</v>
@@ -2423,64 +2459,64 @@
         <v>6</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>352</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>119</v>
+        <v>349</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>351</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>120</v>
+        <v>347</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>212</v>
+      <c r="G39" s="2" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>213</v>
+      <c r="G40" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>52</v>
@@ -2495,9 +2531,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>53</v>
@@ -2514,59 +2550,59 @@
       <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>214</v>
+      <c r="G42" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A44" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B44" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G43" s="5" t="s">
+      <c r="E44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A44" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>326</v>
+        <v>135</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>141</v>
@@ -2584,18 +2620,18 @@
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>9</v>
@@ -2607,18 +2643,18 @@
         <v>6</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
@@ -2630,18 +2666,18 @@
         <v>6</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>60</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>9</v>
@@ -2653,21 +2689,21 @@
         <v>6</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>306</v>
+        <v>121</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>357</v>
+        <v>122</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>356</v>
+        <v>123</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>11</v>
@@ -2676,35 +2712,35 @@
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>305</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>62</v>
+        <v>306</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>63</v>
+        <v>357</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>66</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>63</v>
@@ -2722,12 +2758,12 @@
         <v>6</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>63</v>
@@ -2739,70 +2775,70 @@
         <v>64</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A53" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A53" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G53" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B55" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C55" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>21</v>
@@ -2813,68 +2849,68 @@
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
+    <row r="57" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C57" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="E57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>65</v>
@@ -2882,36 +2918,36 @@
       <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G58" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>144</v>
+      <c r="G59" s="5" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>327</v>
+        <v>136</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>142</v>
@@ -2929,21 +2965,21 @@
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>337</v>
+        <v>142</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>338</v>
+        <v>139</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -2952,18 +2988,18 @@
         <v>6</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>277</v>
+        <v>335</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>261</v>
@@ -2975,12 +3011,12 @@
         <v>6</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>279</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>315</v>
+        <v>277</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>278</v>
@@ -2998,58 +3034,58 @@
         <v>6</v>
       </c>
       <c r="G63" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B65" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="5" t="s">
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="5" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>124</v>
@@ -3067,18 +3103,18 @@
         <v>6</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>9</v>
@@ -3089,22 +3125,22 @@
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G67" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>71</v>
+        <v>365</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>70</v>
+        <v>369</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>72</v>
+        <v>372</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>30</v>
+        <v>371</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -3112,22 +3148,22 @@
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>218</v>
+      <c r="G68" s="2" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -3136,21 +3172,21 @@
         <v>6</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>219</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -3158,19 +3194,19 @@
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="2" t="s">
-        <v>107</v>
+      <c r="G70" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>76</v>
@@ -3182,18 +3218,18 @@
         <v>6</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>290</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>300</v>
+        <v>106</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>359</v>
+        <v>109</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>360</v>
+        <v>108</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>76</v>
@@ -3205,41 +3241,41 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>132</v>
+        <v>288</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>133</v>
+      <c r="G73" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>282</v>
+        <v>300</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>359</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>283</v>
+        <v>360</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>76</v>
@@ -3251,45 +3287,44 @@
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H74" s="2"/>
+        <v>299</v>
+      </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>328</v>
+        <v>131</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>330</v>
+        <v>132</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>329</v>
+        <v>134</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>78</v>
+        <v>353</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>355</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3298,21 +3333,21 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>133</v>
+        <v>295</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>156</v>
+        <v>281</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -3321,44 +3356,45 @@
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H77" s="2"/>
     </row>
     <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>189</v>
+        <v>328</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>188</v>
+        <v>316</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -3367,21 +3403,21 @@
         <v>6</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -3390,41 +3426,41 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>304</v>
+        <v>189</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>9</v>
@@ -3435,22 +3471,22 @@
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>146</v>
+      <c r="G82" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -3459,21 +3495,21 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>202</v>
+        <v>304</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -3481,19 +3517,19 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G84" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>298</v>
+        <v>145</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>9</v>
@@ -3504,45 +3540,45 @@
       <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>316</v>
+      <c r="G85" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -3550,22 +3586,22 @@
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>161</v>
+      <c r="G87" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -3574,21 +3610,21 @@
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>293</v>
+        <v>363</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -3596,42 +3632,42 @@
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>294</v>
+      <c r="G89" s="2" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>76</v>
@@ -3643,18 +3679,18 @@
         <v>6</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>358</v>
+        <v>291</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>76</v>
@@ -3666,21 +3702,21 @@
         <v>6</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>157</v>
+        <v>293</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>158</v>
+        <v>81</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -3688,22 +3724,22 @@
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>155</v>
+      <c r="G93" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -3712,21 +3748,21 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>85</v>
+        <v>153</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -3734,22 +3770,22 @@
       <c r="F95" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G95" s="5" t="s">
-        <v>222</v>
+      <c r="G95" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>285</v>
+        <v>358</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -3758,21 +3794,21 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>151</v>
+        <v>361</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -3780,22 +3816,22 @@
       <c r="F97" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G97" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G97" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>224</v>
+        <v>157</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -3804,21 +3840,21 @@
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>226</v>
+        <v>155</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -3827,18 +3863,18 @@
         <v>6</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>331</v>
+        <v>85</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>9</v>
@@ -3849,67 +3885,159 @@
       <c r="F100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="2" t="s">
+      <c r="G100" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A101" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A102" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A103" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A104" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A105" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G105" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B102" s="6"/>
-    </row>
-    <row r="105" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B105" s="6"/>
-    </row>
-    <row r="106" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A106" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>295</v>
-      </c>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="B108" s="6"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="B112" s="6"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H100">
-    <sortCondition ref="A2:A100"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H105">
+    <sortCondition ref="A105"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G23" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G53" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G58" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G67" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G43" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G82" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G84" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G24" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G54" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G59" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G69" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G44" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G85" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G87" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G29" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G31" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G33" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G42" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G54" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G68" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G69" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G95" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G30" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G32" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G34" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G43" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G55" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G70" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G71" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G100" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G71" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G89" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G26" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G32" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G73" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G93" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G27" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G33" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1068" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27C136E9-0E05-634C-8298-E7BA0AFC8DFE}"/>
+  <xr:revisionPtr revIDLastSave="1113" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC7EB0C4-E6C3-C54A-AA2A-3CAED52C112F}"/>
   <bookViews>
-    <workbookView xWindow="2720" yWindow="-21100" windowWidth="31200" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4320" yWindow="-21100" windowWidth="31400" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="387">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1122,6 +1122,9 @@
     <t>Oncorhynchus clarkii virginalis</t>
   </si>
   <si>
+    <t>SAFO-5</t>
+  </si>
+  <si>
     <t>SAFO-4</t>
   </si>
   <si>
@@ -1137,6 +1140,9 @@
     <t>NOHU-1</t>
   </si>
   <si>
+    <t>COAS-1</t>
+  </si>
+  <si>
     <t>DOI: 10.1111/mec.15947</t>
   </si>
   <si>
@@ -1156,6 +1162,42 @@
   </si>
   <si>
     <t>Novumbra hubbsi</t>
+  </si>
+  <si>
+    <t>Cottus asper</t>
+  </si>
+  <si>
+    <t>Prickly Sculpin</t>
+  </si>
+  <si>
+    <t>doi:10.1093/jhered/esw045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Cottidae</t>
+  </si>
+  <si>
+    <t>NOGI-1</t>
+  </si>
+  <si>
+    <t>Arkansas River Chub</t>
+  </si>
+  <si>
+    <t>Notropis girardi</t>
+  </si>
+  <si>
+    <t>Peppered Chub</t>
+  </si>
+  <si>
+    <t>Macrhybopsis tetranema</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-021-01374-x</t>
+  </si>
+  <si>
+    <t>MATE-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Leuciscidae</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -1866,30 +1908,30 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>263</v>
+        <v>367</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>262</v>
+        <v>376</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>266</v>
+        <v>375</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>264</v>
+        <v>378</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>265</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>262</v>
@@ -1907,18 +1949,18 @@
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>264</v>
@@ -1929,36 +1971,36 @@
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>253</v>
@@ -1981,13 +2023,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>127</v>
+        <v>254</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
@@ -1999,21 +2041,21 @@
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>130</v>
+        <v>256</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
@@ -2022,21 +2064,21 @@
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>167</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>232</v>
+        <v>164</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>236</v>
+        <v>165</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>243</v>
+        <v>166</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -2045,21 +2087,21 @@
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>227</v>
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>364</v>
+        <v>232</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>367</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>368</v>
+        <v>243</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>11</v>
@@ -2068,18 +2110,18 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>366</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>350</v>
+        <v>369</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>30</v>
@@ -2091,18 +2133,18 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>348</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>29</v>
+        <v>346</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>30</v>
@@ -2114,12 +2156,12 @@
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>28</v>
@@ -2136,15 +2178,15 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>32</v>
+      <c r="G24" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -2159,13 +2201,13 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G25" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>333</v>
+        <v>168</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>28</v>
@@ -2182,19 +2224,19 @@
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G26" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>344</v>
+        <v>333</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>343</v>
+        <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>30</v>
@@ -2205,19 +2247,19 @@
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>341</v>
+      <c r="G27" s="2" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>172</v>
+        <v>345</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>171</v>
+        <v>343</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
@@ -2229,64 +2271,64 @@
         <v>6</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G29" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G30" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2297,19 +2339,19 @@
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G31" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
@@ -2320,19 +2362,19 @@
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>210</v>
+      <c r="G32" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>339</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>342</v>
+        <v>37</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -2344,18 +2386,18 @@
         <v>6</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>339</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>40</v>
+        <v>342</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>41</v>
+        <v>340</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -2367,18 +2409,18 @@
         <v>6</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -2389,59 +2431,59 @@
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>46</v>
+      <c r="G35" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>191</v>
+        <v>45</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>194</v>
+        <v>43</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>193</v>
+        <v>44</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G36" s="2" t="s">
-        <v>195</v>
+      <c r="G36" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>249</v>
+        <v>191</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>256</v>
+        <v>195</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>251</v>
@@ -2464,13 +2506,13 @@
     </row>
     <row r="39" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>351</v>
+        <v>255</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>347</v>
+        <v>250</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>30</v>
@@ -2482,64 +2524,64 @@
         <v>6</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>352</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A40" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>49</v>
+        <v>120</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>213</v>
+      <c r="G41" s="4" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>52</v>
@@ -2554,9 +2596,9 @@
         <v>213</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>53</v>
@@ -2573,59 +2615,59 @@
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>214</v>
+      <c r="G43" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A45" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B45" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G44" s="5" t="s">
+      <c r="E45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A45" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>326</v>
+        <v>135</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>141</v>
@@ -2643,18 +2685,18 @@
         <v>6</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>316</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>326</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
@@ -2666,18 +2708,18 @@
         <v>6</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>9</v>
@@ -2689,18 +2731,18 @@
         <v>6</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>60</v>
+        <v>215</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
@@ -2712,21 +2754,21 @@
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>306</v>
+        <v>121</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>357</v>
+        <v>122</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>356</v>
+        <v>123</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
@@ -2735,58 +2777,58 @@
         <v>6</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>64</v>
+        <v>386</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>66</v>
+      <c r="G51" s="5" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>92</v>
+        <v>306</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>63</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>216</v>
+        <v>305</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>63</v>
@@ -2798,211 +2840,211 @@
         <v>64</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G53" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A55" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G55" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A54" s="2" t="s">
+    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B56" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C56" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G54" s="5" t="s">
+      <c r="E56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A55" s="2" t="s">
+    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B57" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C57" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="D57" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G55" s="5" t="s">
+      <c r="E57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>104</v>
+        <v>175</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>9</v>
+        <v>178</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>105</v>
+      <c r="G59" s="2" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>9</v>
+        <v>182</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>327</v>
+        <v>102</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G61" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>337</v>
+        <v>382</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -3010,22 +3052,22 @@
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>336</v>
+      <c r="G62" s="5" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>277</v>
+        <v>136</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -3034,21 +3076,21 @@
         <v>6</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>279</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>11</v>
@@ -3060,107 +3102,107 @@
         <v>316</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A66" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A67" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A68" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B68" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C68" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="D65" s="2" t="s">
+      <c r="D68" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="E68" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="5" t="s">
+      <c r="F68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A66" s="2" t="s">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B69" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C69" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A67" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A68" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>9</v>
@@ -3171,157 +3213,157 @@
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A70" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A71" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A72" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="2" t="s">
+    <row r="74" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D70" s="2" t="s">
+      <c r="D74" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="5" t="s">
+      <c r="E74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G74" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="2" t="s">
+    <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A75" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B75" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A72" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B74" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A75" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G75" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>353</v>
+        <v>106</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>355</v>
+        <v>109</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>354</v>
+        <v>108</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>76</v>
@@ -3333,18 +3375,18 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>76</v>
@@ -3355,23 +3397,22 @@
       <c r="F77" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H77" s="2"/>
-    </row>
-    <row r="78" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G77" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>330</v>
+        <v>300</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>359</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>329</v>
+        <v>360</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -3380,24 +3421,24 @@
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>6</v>
@@ -3406,153 +3447,154 @@
         <v>133</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A81" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H81" s="2"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A82" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A83" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A84" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C80" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D80" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G80" s="2" t="s">
+      <c r="E84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A81" s="2" t="s">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A85" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B85" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C81" s="2" t="s">
+      <c r="C85" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="D85" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G81" s="2" t="s">
+      <c r="F85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A82" s="2" t="s">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A83" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A84" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A85" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A86" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>9</v>
@@ -3564,21 +3606,21 @@
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -3586,22 +3628,22 @@
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G87" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -3610,18 +3652,18 @@
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>363</v>
+        <v>145</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
@@ -3632,134 +3674,134 @@
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A90" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A92" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A93" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A94" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B94" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C94" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A92" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A93" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A94" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>76</v>
@@ -3771,18 +3813,18 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>358</v>
+        <v>291</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>76</v>
@@ -3794,18 +3836,18 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>361</v>
+        <v>293</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>76</v>
@@ -3816,22 +3858,22 @@
       <c r="F97" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G97" s="2" t="s">
-        <v>362</v>
+      <c r="G97" s="5" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -3840,21 +3882,21 @@
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>205</v>
+        <v>153</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -3863,21 +3905,21 @@
         <v>6</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>85</v>
+        <v>358</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -3885,22 +3927,22 @@
       <c r="F100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G100" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>285</v>
+        <v>362</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -3909,21 +3951,21 @@
         <v>6</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>286</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>151</v>
+        <v>361</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -3932,21 +3974,21 @@
         <v>6</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B103" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>224</v>
+        <v>157</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -3955,21 +3997,21 @@
         <v>6</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>226</v>
+        <v>155</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>140</v>
+        <v>159</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -3978,18 +4020,18 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>331</v>
+        <v>85</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>9</v>
@@ -4000,44 +4042,169 @@
       <c r="F105" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G105" s="2" t="s">
+      <c r="G105" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A106" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A107" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A109" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A110" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G110" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B108" s="6"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="B112" s="6"/>
+    <row r="113" spans="7:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G113" s="5"/>
+    </row>
+    <row r="117" spans="7:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G117" s="5"/>
+    </row>
+    <row r="118" spans="7:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G118" s="5"/>
+    </row>
+    <row r="119" spans="7:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G119" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H105">
-    <sortCondition ref="A105"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H119">
+    <sortCondition ref="A15:A119"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G24" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G54" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G59" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G69" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G44" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G85" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G87" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G25" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G56" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G61" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G73" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G45" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G89" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G91" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G30" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G32" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G34" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G43" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G55" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G70" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G71" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G100" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G15" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G73" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G93" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G27" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G33" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G31" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G33" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G35" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G44" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G57" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G74" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G75" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G105" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G16" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G77" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G97" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G28" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G34" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G102" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G71" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G62" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G51" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1113" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC7EB0C4-E6C3-C54A-AA2A-3CAED52C112F}"/>
+  <xr:revisionPtr revIDLastSave="1137" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8111A67-AE61-E447-B152-99BB7A1B7B9C}"/>
   <bookViews>
     <workbookView xWindow="-4320" yWindow="-21100" windowWidth="31400" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="397">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1198,6 +1198,36 @@
   </si>
   <si>
     <t xml:space="preserve">	Leuciscidae</t>
+  </si>
+  <si>
+    <t>CAMI-1</t>
+  </si>
+  <si>
+    <t>CAOC-1</t>
+  </si>
+  <si>
+    <t>Modoc Sucker</t>
+  </si>
+  <si>
+    <t>Sacramento Sucker</t>
+  </si>
+  <si>
+    <t>Catostomus occidentalis</t>
+  </si>
+  <si>
+    <t>Catostomus microps</t>
+  </si>
+  <si>
+    <t>doi:10.3996/022010-JFWM-003</t>
+  </si>
+  <si>
+    <t>ONCL-5</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-022-01455-5</t>
+  </si>
+  <si>
+    <t>HYPL-2</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -1862,13 +1892,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>387</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>389</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>392</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
@@ -1879,19 +1909,19 @@
       <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G11" s="2" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>270</v>
+        <v>388</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>391</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>25</v>
@@ -1903,21 +1933,21 @@
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>272</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>367</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>376</v>
+        <v>23</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>375</v>
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>378</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
@@ -1925,65 +1955,65 @@
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G13" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>264</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>267</v>
+        <v>367</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>264</v>
@@ -1994,65 +2024,65 @@
       <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>276</v>
+      <c r="G16" s="2" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>256</v>
+      <c r="G18" s="5" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>9</v>
@@ -2064,21 +2094,21 @@
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>130</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>164</v>
+        <v>254</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>165</v>
+        <v>253</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>162</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -2087,21 +2117,21 @@
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>167</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>232</v>
+        <v>127</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>236</v>
+        <v>128</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>243</v>
+        <v>129</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>242</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>11</v>
@@ -2110,21 +2140,21 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>227</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>365</v>
+        <v>164</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>369</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>370</v>
+        <v>166</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>162</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
@@ -2133,21 +2163,21 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>368</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>348</v>
+        <v>232</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>350</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>346</v>
+        <v>243</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>11</v>
@@ -2156,18 +2186,18 @@
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>352</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>27</v>
+        <v>365</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>369</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>29</v>
+        <v>370</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -2179,18 +2209,18 @@
         <v>6</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>368</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>31</v>
+        <v>348</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>350</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>29</v>
+        <v>346</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -2201,15 +2231,15 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G25" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
@@ -2224,15 +2254,15 @@
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G26" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="B27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C27" s="2" t="s">
@@ -2247,19 +2277,19 @@
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>334</v>
+      <c r="G27" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>344</v>
+        <v>168</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>343</v>
+        <v>29</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>30</v>
@@ -2271,18 +2301,18 @@
         <v>6</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>170</v>
+        <v>333</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>172</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>171</v>
+        <v>29</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>30</v>
@@ -2293,42 +2323,42 @@
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G29" s="2" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>244</v>
+        <v>345</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>245</v>
+        <v>344</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>246</v>
+        <v>343</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>247</v>
+      <c r="G30" s="5" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>35</v>
+        <v>170</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>36</v>
+        <v>171</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2340,41 +2370,41 @@
         <v>6</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>196</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>192</v>
+        <v>246</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>195</v>
+        <v>247</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -2386,18 +2416,18 @@
         <v>6</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>339</v>
+        <v>190</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>342</v>
+        <v>196</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>340</v>
+        <v>192</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -2408,19 +2438,19 @@
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>341</v>
+      <c r="G34" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -2432,18 +2462,18 @@
         <v>6</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>339</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>43</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>44</v>
+        <v>340</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
@@ -2454,42 +2484,42 @@
       <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G36" s="5" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>191</v>
+        <v>42</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>193</v>
+        <v>41</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>195</v>
+      <c r="G37" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>249</v>
+        <v>45</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>251</v>
+        <v>43</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>250</v>
+        <v>44</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>30</v>
@@ -2500,42 +2530,42 @@
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>256</v>
+      <c r="G38" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>251</v>
+        <v>194</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>351</v>
+        <v>249</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>347</v>
+        <v>250</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>30</v>
@@ -2547,44 +2577,44 @@
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>352</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>119</v>
+        <v>251</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G41" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>51</v>
+        <v>349</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>351</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>49</v>
+        <v>347</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
@@ -2593,41 +2623,41 @@
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>213</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>52</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G43" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G43" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>52</v>
@@ -2638,88 +2668,88 @@
       <c r="F44" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A45" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G46" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A45" s="2" t="s">
+    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A47" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G45" s="5" t="s">
+      <c r="E47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A46" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A47" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>56</v>
+        <v>135</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>55</v>
+        <v>138</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>9</v>
@@ -2731,18 +2761,18 @@
         <v>6</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>215</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>57</v>
+        <v>326</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>58</v>
+        <v>141</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
@@ -2754,18 +2784,18 @@
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>60</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>9</v>
@@ -2777,21 +2807,21 @@
         <v>6</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>121</v>
+        <v>57</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>122</v>
+        <v>58</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>386</v>
+        <v>9</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>11</v>
@@ -2799,22 +2829,22 @@
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>384</v>
+      <c r="G51" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>306</v>
+        <v>121</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>357</v>
+        <v>122</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>356</v>
+        <v>123</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
@@ -2823,58 +2853,58 @@
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>62</v>
+        <v>396</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>64</v>
+        <v>386</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>66</v>
+      <c r="G53" s="5" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>92</v>
+        <v>306</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>357</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>216</v>
+        <v>305</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>231</v>
+        <v>62</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
@@ -2886,208 +2916,208 @@
         <v>64</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A57" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G57" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A56" s="2" t="s">
+    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A58" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B58" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C58" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="D58" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="5" t="s">
+      <c r="E58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A57" s="2" t="s">
+    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A59" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G57" s="5" t="s">
+      <c r="E59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>217</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A58" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A59" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A61" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B62" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C62" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="D62" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E62" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="F62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G62" s="2" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A63" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B63" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C63" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A63" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G63" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>327</v>
+        <v>385</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>142</v>
+        <v>382</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>139</v>
+        <v>383</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>9</v>
@@ -3098,22 +3128,22 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>316</v>
+      <c r="G64" s="5" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>335</v>
+        <v>136</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>337</v>
+        <v>142</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>338</v>
+        <v>139</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -3122,21 +3152,21 @@
         <v>6</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>336</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>277</v>
+        <v>327</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -3145,18 +3175,18 @@
         <v>6</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>279</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>278</v>
+        <v>337</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>280</v>
+        <v>338</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>261</v>
@@ -3168,44 +3198,44 @@
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>185</v>
+        <v>277</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>278</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>186</v>
+        <v>280</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="5" t="s">
-        <v>187</v>
+      <c r="G68" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>126</v>
+        <v>315</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>124</v>
+        <v>278</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -3214,41 +3244,41 @@
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>130</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>124</v>
+        <v>184</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>125</v>
+        <v>186</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="2" t="s">
-        <v>227</v>
+      <c r="G70" s="5" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>379</v>
+        <v>126</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>380</v>
+        <v>124</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>381</v>
+        <v>125</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>9</v>
@@ -3259,22 +3289,22 @@
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>384</v>
+      <c r="G71" s="2" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>366</v>
+        <v>229</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>371</v>
+        <v>124</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>374</v>
+        <v>125</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -3283,18 +3313,18 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>372</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>99</v>
+        <v>379</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>9</v>
@@ -3306,21 +3336,21 @@
         <v>6</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>105</v>
+        <v>384</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>71</v>
+        <v>366</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>70</v>
+        <v>371</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>72</v>
+        <v>374</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>30</v>
+        <v>373</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3328,22 +3358,22 @@
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>218</v>
+      <c r="G74" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -3352,21 +3382,21 @@
         <v>6</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3374,19 +3404,19 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>107</v>
+      <c r="G76" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>287</v>
+        <v>73</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>288</v>
+        <v>74</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>76</v>
@@ -3398,18 +3428,18 @@
         <v>6</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>290</v>
+        <v>219</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>300</v>
+        <v>106</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>359</v>
+        <v>109</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>360</v>
+        <v>108</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>76</v>
@@ -3421,41 +3451,41 @@
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>132</v>
+        <v>288</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>133</v>
+      <c r="G79" s="5" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>353</v>
+        <v>300</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>76</v>
@@ -3467,18 +3497,18 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>281</v>
+        <v>394</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>76</v>
@@ -3489,46 +3519,45 @@
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H81" s="2"/>
+      <c r="G81" s="5" t="s">
+        <v>395</v>
+      </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>328</v>
+        <v>131</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>330</v>
+        <v>132</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>329</v>
+        <v>134</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>325</v>
+        <v>76</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.15">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>78</v>
+        <v>353</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>355</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -3537,21 +3566,21 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>133</v>
+        <v>295</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>156</v>
+        <v>281</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -3560,44 +3589,45 @@
         <v>6</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>155</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H84" s="2"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>189</v>
+        <v>328</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>78</v>
+        <v>330</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>30</v>
+        <v>325</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>188</v>
+        <v>316</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -3606,21 +3636,21 @@
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -3629,41 +3659,41 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>304</v>
+        <v>189</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
@@ -3674,22 +3704,22 @@
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>146</v>
+      <c r="G89" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -3698,21 +3728,21 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>202</v>
+        <v>304</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -3720,19 +3750,19 @@
       <c r="F91" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G91" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>298</v>
+        <v>145</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>9</v>
@@ -3743,13 +3773,13 @@
       <c r="F92" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>316</v>
+      <c r="G92" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>364</v>
+        <v>88</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>89</v>
@@ -3767,81 +3797,81 @@
         <v>6</v>
       </c>
       <c r="G93" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A94" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A95" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A96" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G96" s="2" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A94" s="2" t="s">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A97" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A96" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A97" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>81</v>
@@ -3853,24 +3883,24 @@
         <v>76</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G97" s="5" t="s">
-        <v>294</v>
+      <c r="G97" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>76</v>
@@ -3882,18 +3912,18 @@
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>76</v>
@@ -3905,18 +3935,18 @@
         <v>6</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>358</v>
+        <v>293</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>76</v>
@@ -3927,13 +3957,13 @@
       <c r="F100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G100" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>83</v>
@@ -3951,12 +3981,12 @@
         <v>6</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>361</v>
+        <v>153</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>83</v>
@@ -3973,22 +4003,22 @@
       <c r="F102" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G102" s="5" t="s">
-        <v>302</v>
+      <c r="G102" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>157</v>
+        <v>358</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -3997,21 +4027,21 @@
         <v>6</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>155</v>
+        <v>313</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>205</v>
+        <v>362</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -4020,21 +4050,21 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>206</v>
+        <v>363</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>85</v>
+        <v>361</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -4043,64 +4073,64 @@
         <v>6</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>222</v>
+        <v>302</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>285</v>
+        <v>157</v>
       </c>
       <c r="B106" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A107" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A107" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A108" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>9</v>
@@ -4111,19 +4141,19 @@
       <c r="F108" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G108" s="2" t="s">
-        <v>226</v>
+      <c r="G108" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>9</v>
@@ -4135,18 +4165,18 @@
         <v>6</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>9</v>
@@ -4157,54 +4187,127 @@
       <c r="F110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="G110" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A111" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A112" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A113" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="113" spans="7:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G113" s="5"/>
-    </row>
-    <row r="117" spans="7:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G117" s="5"/>
-    </row>
-    <row r="118" spans="7:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G114" s="5"/>
+    </row>
+    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G118" s="5"/>
     </row>
-    <row r="119" spans="7:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G119" s="5"/>
     </row>
+    <row r="120" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G120" s="5"/>
+    </row>
+    <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G122" s="5"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H119">
-    <sortCondition ref="A15:A119"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H120">
+    <sortCondition ref="A93:A120"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="G11" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G25" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G56" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G61" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G73" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G45" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G89" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G91" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G27" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G58" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G63" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G75" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G47" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G92" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G94" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G31" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G33" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G35" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G44" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G57" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G74" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G75" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G105" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G16" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G77" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G97" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G28" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G34" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G102" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G71" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G62" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G51" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G33" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G35" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G37" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G46" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G59" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G76" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G77" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G108" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G18" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G79" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G100" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G30" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G36" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G105" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G73" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G64" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G53" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G81" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1137" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8111A67-AE61-E447-B152-99BB7A1B7B9C}"/>
+  <xr:revisionPtr revIDLastSave="1139" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ABCF093-4D94-9346-9EC4-BFBDDF23792C}"/>
   <bookViews>
     <workbookView xWindow="-4320" yWindow="-21100" windowWidth="31400" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="398">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1228,6 +1228,9 @@
   </si>
   <si>
     <t>HYPL-2</t>
+  </si>
+  <si>
+    <t>SACO-</t>
   </si>
 </sst>
 </file>
@@ -4272,6 +4275,11 @@
     <row r="120" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G120" s="5"/>
     </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A121" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
     <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G122" s="5"/>
     </row>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1139" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ABCF093-4D94-9346-9EC4-BFBDDF23792C}"/>
+  <xr:revisionPtr revIDLastSave="1153" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF042101-767C-1347-91A7-9FA5B1648A31}"/>
   <bookViews>
-    <workbookView xWindow="-4320" yWindow="-21100" windowWidth="31400" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4320" yWindow="-21100" windowWidth="38300" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="401">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1230,7 +1230,16 @@
     <t>HYPL-2</t>
   </si>
   <si>
-    <t>SACO-</t>
+    <t>SACO-5</t>
+  </si>
+  <si>
+    <t>Bull Trout</t>
+  </si>
+  <si>
+    <t>Coastal-Puget</t>
+  </si>
+  <si>
+    <t>http://www.bioone.org/doi/full/10.3955/046.085.0305</t>
   </si>
 </sst>
 </file>
@@ -1328,6 +1337,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1709,18 +1722,18 @@
         <v>316</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>332</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>320</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>321</v>
+        <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -1728,54 +1741,54 @@
       <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>316</v>
+      <c r="G3" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -1849,16 +1862,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>322</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>116</v>
+        <v>324</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>117</v>
+        <v>323</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
@@ -1867,41 +1880,41 @@
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>209</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>322</v>
+        <v>387</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>324</v>
+        <v>389</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>323</v>
+        <v>392</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>316</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
@@ -1918,13 +1931,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>388</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>390</v>
+        <v>23</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>391</v>
+        <v>24</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>25</v>
@@ -1935,19 +1948,19 @@
       <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G12" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>269</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>270</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>25</v>
@@ -1958,22 +1971,22 @@
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G13" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>270</v>
+        <v>397</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
@@ -1981,8 +1994,8 @@
       <c r="F14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>272</v>
+      <c r="G14" s="5" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
@@ -2332,13 +2345,13 @@
     </row>
     <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2355,13 +2368,13 @@
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>172</v>
+        <v>345</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>171</v>
+        <v>343</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2373,64 +2386,64 @@
         <v>6</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>245</v>
+        <v>170</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>246</v>
+        <v>171</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G32" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>244</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>35</v>
+        <v>245</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G33" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -2441,19 +2454,19 @@
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G34" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>37</v>
+        <v>196</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>39</v>
+        <v>192</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -2464,19 +2477,19 @@
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>210</v>
+      <c r="G35" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>339</v>
+        <v>38</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>342</v>
+        <v>37</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>340</v>
+        <v>39</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
@@ -2488,7 +2501,7 @@
         <v>6</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>341</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -2884,30 +2897,30 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>306</v>
+        <v>62</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>357</v>
+        <v>63</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>356</v>
+        <v>61</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>305</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
@@ -2925,12 +2938,12 @@
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>66</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>92</v>
+        <v>231</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>63</v>
@@ -2942,27 +2955,27 @@
         <v>64</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>231</v>
+        <v>306</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>63</v>
+        <v>357</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>61</v>
+        <v>356</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -2971,7 +2984,7 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>227</v>
+        <v>305</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -2997,38 +3010,38 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A60" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B60" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C60" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G59" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A60" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>21</v>
@@ -3039,31 +3052,31 @@
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A61" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A61" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.15">
@@ -3275,16 +3288,16 @@
     </row>
     <row r="71" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>126</v>
+        <v>71</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -3292,13 +3305,13 @@
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>130</v>
+      <c r="G71" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>229</v>
+        <v>126</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>124</v>
@@ -3316,18 +3329,18 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>379</v>
+        <v>229</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>380</v>
+        <v>124</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>381</v>
+        <v>125</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>9</v>
@@ -3338,22 +3351,22 @@
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>384</v>
+      <c r="G73" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3361,8 +3374,8 @@
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>372</v>
+      <c r="G74" s="5" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -3388,18 +3401,18 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>71</v>
+        <v>366</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>70</v>
+        <v>371</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>72</v>
+        <v>374</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>30</v>
+        <v>373</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3407,19 +3420,19 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>218</v>
+      <c r="G76" s="2" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>73</v>
+        <v>287</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>74</v>
+        <v>288</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>75</v>
+        <v>289</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>76</v>
@@ -3431,18 +3444,18 @@
         <v>6</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>219</v>
+        <v>290</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>109</v>
+        <v>394</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>108</v>
+        <v>289</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>76</v>
@@ -3453,19 +3466,19 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G78" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>288</v>
+        <v>106</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>289</v>
+        <v>108</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>76</v>
@@ -3476,19 +3489,19 @@
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>290</v>
+      <c r="G79" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>359</v>
+        <v>73</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>360</v>
+        <v>75</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>76</v>
@@ -3499,19 +3512,19 @@
       <c r="F80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G80" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>359</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>289</v>
+        <v>360</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>76</v>
@@ -3522,42 +3535,42 @@
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G81" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>132</v>
+        <v>353</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>355</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>134</v>
+        <v>354</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>355</v>
+        <v>281</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>354</v>
+        <v>283</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>76</v>
@@ -3569,32 +3582,32 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>295</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H83" s="2"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>281</v>
+        <v>131</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>283</v>
+        <v>134</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H84" s="2"/>
+        <v>133</v>
+      </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
@@ -3621,30 +3634,30 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>133</v>
+        <v>209</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>78</v>
@@ -3662,12 +3675,12 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>78</v>
@@ -3679,50 +3692,50 @@
         <v>30</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>230</v>
+        <v>189</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>227</v>
+        <v>188</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>201</v>
+        <v>9</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -3731,12 +3744,12 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>304</v>
+        <v>197</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>198</v>
@@ -3754,41 +3767,41 @@
         <v>6</v>
       </c>
       <c r="G91" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A92" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A92" s="2" t="s">
+    <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A93" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B93" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A93" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>9</v>
@@ -3799,13 +3812,13 @@
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G93" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>202</v>
+        <v>88</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>89</v>
@@ -3822,13 +3835,13 @@
       <c r="F94" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G94" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G94" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>89</v>
@@ -3845,13 +3858,13 @@
       <c r="F95" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G95" s="2" t="s">
-        <v>316</v>
+      <c r="G95" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>89</v>
@@ -3869,35 +3882,35 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>80</v>
+        <v>364</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>220</v>
+        <v>297</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>81</v>
@@ -3909,18 +3922,18 @@
         <v>76</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>291</v>
+        <v>160</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>81</v>
@@ -3938,12 +3951,12 @@
         <v>6</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>292</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>81</v>
@@ -3960,19 +3973,19 @@
       <c r="F100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G100" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>76</v>
@@ -3983,13 +3996,13 @@
       <c r="F101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G101" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>83</v>
@@ -4007,12 +4020,12 @@
         <v>6</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>358</v>
+        <v>153</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>83</v>
@@ -4030,12 +4043,12 @@
         <v>6</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>313</v>
+        <v>154</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>83</v>
@@ -4053,12 +4066,12 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>83</v>
@@ -4075,36 +4088,36 @@
       <c r="F105" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G105" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A106" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="5" t="s">
         <v>302</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A106" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>205</v>
+        <v>157</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>158</v>
@@ -4122,35 +4135,35 @@
         <v>6</v>
       </c>
       <c r="G107" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A108" s="2" t="s">
+    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A109" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A109" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>86</v>
@@ -4167,19 +4180,19 @@
       <c r="F109" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G109" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>151</v>
+        <v>285</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>9</v>
@@ -4190,19 +4203,19 @@
       <c r="F110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G110" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G110" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>224</v>
+        <v>151</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>9</v>
@@ -4213,19 +4226,19 @@
       <c r="F111" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G111" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>140</v>
+        <v>223</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>224</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>9</v>
@@ -4237,12 +4250,12 @@
         <v>6</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>144</v>
+        <v>226</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>143</v>
@@ -4260,14 +4273,34 @@
         <v>6</v>
       </c>
       <c r="G113" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A114" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="2" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G114" s="5"/>
-    </row>
-    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G118" s="5"/>
+    <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G115" s="5"/>
     </row>
     <row r="119" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G119" s="5"/>
@@ -4275,47 +4308,46 @@
     <row r="120" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G120" s="5"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A121" s="2" t="s">
-        <v>397</v>
-      </c>
+    <row r="121" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G121" s="5"/>
     </row>
     <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G122" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H120">
-    <sortCondition ref="A93:A120"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H122">
+    <sortCondition ref="C14:C122"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G12" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G27" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
     <hyperlink ref="G58" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
     <hyperlink ref="G63" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
     <hyperlink ref="G75" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
     <hyperlink ref="G47" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G92" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G94" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
-    <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
+    <hyperlink ref="G93" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G95" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G3" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G33" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G35" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G34" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G36" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
     <hyperlink ref="G37" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
     <hyperlink ref="G46" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G59" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G76" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G77" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G108" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G60" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G71" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G80" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G109" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G18" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G79" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G100" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G30" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G36" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G105" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G73" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G77" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G101" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G31" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G30" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G106" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G74" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
     <hyperlink ref="G64" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
     <hyperlink ref="G53" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G81" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G78" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G14" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1153" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF042101-767C-1347-91A7-9FA5B1648A31}"/>
+  <xr:revisionPtr revIDLastSave="1180" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9386E2E5-3F30-5D40-AE34-2E4A8047DAD0}"/>
   <bookViews>
-    <workbookView xWindow="-4320" yWindow="-21100" windowWidth="38300" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4280" yWindow="-21100" windowWidth="38300" windowHeight="21100" activeTab="1" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
-    <sheet name="data_to_add" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="410">
   <si>
     <t>Study_ID</t>
   </si>
@@ -927,9 +927,6 @@
     <t>doi: 10.1111/mec.13517</t>
   </si>
   <si>
-    <t>doi: 10.1111/j.1365-294X.2008.03710.x</t>
-  </si>
-  <si>
     <t>DOI: 10.1002/tafs.10388</t>
   </si>
   <si>
@@ -942,15 +939,9 @@
     <t>ONCL-4</t>
   </si>
   <si>
-    <t>SAFO</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1093/tafafs/vnaf045</t>
   </si>
   <si>
-    <t>DOI: 10.1002/tafs.10260</t>
-  </si>
-  <si>
     <t>POSP-2</t>
   </si>
   <si>
@@ -960,30 +951,9 @@
     <t>ICBU-1</t>
   </si>
   <si>
-    <t>PERI</t>
-  </si>
-  <si>
-    <t>doi:10.1111/fwb.12190</t>
-  </si>
-  <si>
-    <t>NOHU</t>
-  </si>
-  <si>
-    <t>ONMY</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3955/046.085.0305</t>
-  </si>
-  <si>
-    <t>SACO</t>
-  </si>
-  <si>
     <t>DOI: 10.1002/nafm.10618</t>
   </si>
   <si>
-    <t>SITH</t>
-  </si>
-  <si>
     <t>MIDO-2</t>
   </si>
   <si>
@@ -1240,6 +1210,63 @@
   </si>
   <si>
     <t>http://www.bioone.org/doi/full/10.3955/046.085.0305</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/ddi.13759</t>
+  </si>
+  <si>
+    <t>doi:10.3390/fishes5030024</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.11646/zootaxa.5154.5.1</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/evolut/qpaf249</t>
+  </si>
+  <si>
+    <t>https://scispace.com/pdf/population-genetic-structure-and-temporal-stability-at-the-2kj9rf8mqa.pdf</t>
+  </si>
+  <si>
+    <t>https://scholarsjunction.msstate.edu/td/6714/</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/aqc.3510</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-023-01572-9</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-016-0845-2</t>
+  </si>
+  <si>
+    <t>https://scholarworks.uni.edu/etd/1204/</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/eva.12990</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s12862-023-02191-1</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/eva.12454</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/00028487.2017.1285351</t>
+  </si>
+  <si>
+    <t>DOI: 10.1002/ece3.5237</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://doi.org/10.1002/eap.2147</t>
+  </si>
+  <si>
+    <t>doi: 10.1111/mec.17558</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/jfb.15999</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3354/esr00986</t>
   </si>
 </sst>
 </file>
@@ -1297,7 +1324,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1315,12 +1342,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1701,13 +1723,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -1719,7 +1741,7 @@
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.15">
@@ -1747,13 +1769,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>64</v>
@@ -1765,7 +1787,7 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
@@ -1862,16 +1884,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
@@ -1880,18 +1902,18 @@
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>25</v>
@@ -1903,18 +1925,18 @@
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
@@ -1926,7 +1948,7 @@
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
@@ -1977,13 +1999,13 @@
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>76</v>
@@ -1995,30 +2017,30 @@
         <v>6</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -2207,13 +2229,13 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>30</v>
@@ -2225,18 +2247,18 @@
         <v>6</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>30</v>
@@ -2248,7 +2270,7 @@
         <v>6</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
@@ -2322,7 +2344,7 @@
     </row>
     <row r="29" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>28</v>
@@ -2340,18 +2362,18 @@
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2363,18 +2385,18 @@
         <v>6</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2386,7 +2408,7 @@
         <v>6</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -2621,13 +2643,13 @@
     </row>
     <row r="42" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
@@ -2639,7 +2661,7 @@
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
@@ -2782,7 +2804,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>141</v>
@@ -2800,7 +2822,7 @@
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
@@ -2874,7 +2896,7 @@
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>122</v>
@@ -2883,7 +2905,7 @@
         <v>123</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -2892,7 +2914,7 @@
         <v>6</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
@@ -2966,13 +2988,13 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>25</v>
@@ -2984,7 +3006,7 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -3127,13 +3149,13 @@
     </row>
     <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>9</v>
@@ -3145,7 +3167,7 @@
         <v>6</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.15">
@@ -3173,7 +3195,7 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>142</v>
@@ -3191,18 +3213,18 @@
         <v>6</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>261</v>
@@ -3214,7 +3236,7 @@
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.15">
@@ -3242,7 +3264,7 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>278</v>
@@ -3260,7 +3282,7 @@
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
@@ -3357,13 +3379,13 @@
     </row>
     <row r="74" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>9</v>
@@ -3375,7 +3397,7 @@
         <v>6</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -3403,16 +3425,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3421,7 +3443,7 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
@@ -3449,7 +3471,7 @@
     </row>
     <row r="78" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>288</v>
@@ -3467,7 +3489,7 @@
         <v>6</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="14" x14ac:dyDescent="0.15">
@@ -3516,15 +3538,15 @@
         <v>219</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:8" ht="28" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>76</v>
@@ -3536,18 +3558,18 @@
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>76</v>
@@ -3611,16 +3633,16 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -3629,7 +3651,7 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.15">
@@ -3772,7 +3794,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>198</v>
@@ -3790,7 +3812,7 @@
         <v>6</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.15">
@@ -3864,7 +3886,7 @@
     </row>
     <row r="96" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>89</v>
@@ -3882,12 +3904,12 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>89</v>
@@ -3905,7 +3927,7 @@
         <v>6</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
@@ -4048,7 +4070,7 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>83</v>
@@ -4066,12 +4088,12 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>83</v>
@@ -4089,12 +4111,12 @@
         <v>6</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>83</v>
@@ -4112,7 +4134,7 @@
         <v>6</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.15">
@@ -4278,7 +4300,7 @@
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>143</v>
@@ -4296,7 +4318,7 @@
         <v>6</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -4355,131 +4377,125 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10412BD-3C21-D945-B559-C622027104B5}">
-  <dimension ref="A1:B14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D2BF60-27FC-AE44-BE48-175A6AFC76C6}">
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.83203125" style="7"/>
-    <col min="2" max="2" width="38" style="7" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>226</v>
+        <v>402</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
+        <v>409</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{270CE535-C8D5-5748-AC78-B94307888FFC}"/>
-    <hyperlink ref="B7" r:id="rId2" xr:uid="{7EC1CDF4-A767-7849-8534-85910A46FFAF}"/>
-    <hyperlink ref="B12" r:id="rId3" xr:uid="{6AA1709D-7D14-2F47-99CE-E6DE53104C77}"/>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{D9D17451-9130-AB4E-B96E-5E9D8890900A}"/>
+    <hyperlink ref="A5" r:id="rId2" xr:uid="{D7B39A72-5A83-8845-876E-755A6FE0F199}"/>
+    <hyperlink ref="A6" r:id="rId3" xr:uid="{5BB4B890-A333-7446-AB88-D2B3CC3685FD}"/>
+    <hyperlink ref="A7" r:id="rId4" xr:uid="{468A1DEE-C6C6-7C4C-A701-301937A047DF}"/>
+    <hyperlink ref="A9" r:id="rId5" xr:uid="{B095DED7-3261-3C4B-95BF-879B19908C6F}"/>
+    <hyperlink ref="A11" r:id="rId6" xr:uid="{AC321152-D02E-514C-81C1-6E9C3AE50660}"/>
+    <hyperlink ref="A13" r:id="rId7" xr:uid="{8EA87D1C-C36E-B44F-8CED-C439FBD142A9}"/>
+    <hyperlink ref="A21" r:id="rId8" xr:uid="{082A3BE1-8E40-C940-B27B-ED3626DC70EF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1180" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9386E2E5-3F30-5D40-AE34-2E4A8047DAD0}"/>
+  <xr:revisionPtr revIDLastSave="1232" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCB8598C-601A-DE4B-B43F-E6A42BD55B14}"/>
   <bookViews>
-    <workbookView xWindow="-4280" yWindow="-21100" windowWidth="38300" windowHeight="21100" activeTab="1" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4280" yWindow="-21100" windowWidth="34600" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="423">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1267,6 +1267,45 @@
   </si>
   <si>
     <t>https://doi.org/10.3354/esr00986</t>
+  </si>
+  <si>
+    <t>MAVE-1</t>
+  </si>
+  <si>
+    <t>LRBA-1</t>
+  </si>
+  <si>
+    <t>OUBA-1</t>
+  </si>
+  <si>
+    <t>Micropterus velox</t>
+  </si>
+  <si>
+    <t>Neosho Bass</t>
+  </si>
+  <si>
+    <t>Ouachita Bass</t>
+  </si>
+  <si>
+    <t>Little River Bass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micropterus cf. dolomieu </t>
+  </si>
+  <si>
+    <t>Micropterus cf. dolomieu</t>
+  </si>
+  <si>
+    <t>MOSA-1</t>
+  </si>
+  <si>
+    <t>Striped Bass</t>
+  </si>
+  <si>
+    <t>Morone saxatilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Moronidae</t>
   </si>
 </sst>
 </file>
@@ -1682,7 +1721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -1744,18 +1783,18 @@
         <v>306</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>322</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>19</v>
+        <v>310</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -1763,22 +1802,22 @@
       <c r="F3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>208</v>
+      <c r="G3" s="2" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
-        <v>322</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>310</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>311</v>
+        <v>13</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>11</v>
@@ -1787,21 +1826,21 @@
         <v>6</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>11</v>
@@ -1809,8 +1848,8 @@
       <c r="F5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
+      <c r="G5" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -1884,16 +1923,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>312</v>
+        <v>115</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>314</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>117</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>315</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
@@ -1902,41 +1941,41 @@
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>306</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>377</v>
+        <v>312</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>379</v>
+        <v>314</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>382</v>
+        <v>313</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>315</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>383</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
@@ -1953,13 +1992,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>22</v>
+        <v>378</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>380</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>381</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>25</v>
@@ -1970,19 +2009,19 @@
       <c r="F12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G12" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>270</v>
+        <v>22</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>25</v>
@@ -1993,31 +2032,31 @@
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>272</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
@@ -2135,7 +2174,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>254</v>
       </c>
@@ -2158,7 +2197,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
@@ -2181,7 +2220,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>164</v>
       </c>
@@ -2250,7 +2289,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>338</v>
       </c>
@@ -2367,13 +2406,13 @@
     </row>
     <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>30</v>
@@ -2390,13 +2429,13 @@
     </row>
     <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>334</v>
+        <v>170</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>333</v>
+        <v>171</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>30</v>
@@ -2408,64 +2447,64 @@
         <v>6</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>172</v>
+        <v>244</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>171</v>
+        <v>246</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G32" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>244</v>
+        <v>34</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>245</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>246</v>
+        <v>36</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G33" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>34</v>
+        <v>190</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>35</v>
+        <v>196</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -2476,19 +2515,19 @@
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G34" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -2499,19 +2538,19 @@
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="2" t="s">
-        <v>195</v>
+      <c r="G35" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>38</v>
+        <v>329</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>37</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>39</v>
+        <v>330</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
@@ -2523,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>210</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -2572,7 +2611,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>191</v>
       </c>
@@ -2919,30 +2958,30 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>62</v>
+        <v>303</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>347</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>61</v>
+        <v>346</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>66</v>
+        <v>302</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>63</v>
@@ -2960,12 +2999,12 @@
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>216</v>
+        <v>66</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>63</v>
@@ -2977,27 +3016,27 @@
         <v>64</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>347</v>
+        <v>63</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>346</v>
+        <v>61</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -3006,7 +3045,7 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>302</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -3032,18 +3071,18 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>176</v>
+        <v>68</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -3051,19 +3090,19 @@
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G59" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>67</v>
+        <v>228</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>68</v>
+        <v>234</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>69</v>
+        <v>238</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>21</v>
@@ -3074,22 +3113,22 @@
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G60" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>238</v>
+        <v>175</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>21</v>
+        <v>178</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -3098,7 +3137,7 @@
         <v>6</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.15">
@@ -3126,59 +3165,59 @@
     </row>
     <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>102</v>
+        <v>411</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>103</v>
+        <v>416</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>104</v>
+        <v>417</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>105</v>
+        <v>391</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>375</v>
+        <v>102</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>372</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>373</v>
+        <v>104</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>136</v>
+        <v>375</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>142</v>
+        <v>372</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>139</v>
+        <v>373</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>9</v>
@@ -3189,22 +3228,22 @@
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G65" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>317</v>
+        <v>410</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>142</v>
+        <v>414</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>139</v>
+        <v>413</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -3212,19 +3251,19 @@
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G66" s="5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>325</v>
+        <v>410</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>327</v>
+        <v>414</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>328</v>
+        <v>413</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>261</v>
@@ -3235,22 +3274,22 @@
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>326</v>
+      <c r="G67" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>277</v>
+        <v>136</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -3259,21 +3298,21 @@
         <v>6</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>279</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>280</v>
+        <v>139</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -3285,41 +3324,41 @@
         <v>306</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>185</v>
+        <v>325</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>186</v>
+        <v>328</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>25</v>
+        <v>261</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G70" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>71</v>
+        <v>277</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>30</v>
+        <v>261</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -3327,65 +3366,65 @@
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>218</v>
+      <c r="G71" s="2" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A74" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B74" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>9</v>
@@ -3396,19 +3435,19 @@
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G74" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>99</v>
+        <v>229</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>9</v>
@@ -3419,91 +3458,91 @@
       <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G75" s="5" t="s">
+      <c r="G75" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A76" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A77" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A78" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G78" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A76" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -3511,11 +3550,11 @@
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G79" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
         <v>73</v>
       </c>
@@ -3538,15 +3577,15 @@
         <v>219</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="28" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>299</v>
+        <v>106</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>350</v>
+        <v>108</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>76</v>
@@ -3558,18 +3597,18 @@
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>345</v>
+        <v>287</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>344</v>
+        <v>289</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>76</v>
@@ -3580,19 +3619,19 @@
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G82" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>282</v>
+        <v>299</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>349</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>283</v>
+        <v>350</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>76</v>
@@ -3604,91 +3643,90 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H83" s="2"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.15">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>131</v>
+        <v>384</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>132</v>
+        <v>288</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>134</v>
+        <v>289</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>76</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>133</v>
+      <c r="G84" s="5" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>318</v>
+        <v>131</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>320</v>
+        <v>132</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>319</v>
+        <v>134</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>315</v>
+        <v>76</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.15">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>116</v>
+        <v>343</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>345</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>117</v>
+        <v>344</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>209</v>
+        <v>295</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>77</v>
+        <v>281</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>78</v>
+        <v>282</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>79</v>
+        <v>283</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -3697,21 +3735,22 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.15">
+        <v>284</v>
+      </c>
+      <c r="H87" s="2"/>
+    </row>
+    <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>156</v>
+        <v>412</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>78</v>
+        <v>415</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>79</v>
+        <v>418</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>30</v>
+        <v>261</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -3719,45 +3758,45 @@
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>155</v>
+      <c r="G88" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>78</v>
+        <v>320</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>30</v>
+        <v>315</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>188</v>
+        <v>306</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>239</v>
+        <v>79</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -3766,21 +3805,21 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>227</v>
+        <v>133</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -3789,41 +3828,41 @@
         <v>6</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>301</v>
+        <v>189</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>145</v>
+        <v>230</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>148</v>
+        <v>235</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>9</v>
@@ -3834,22 +3873,22 @@
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>146</v>
+      <c r="G93" s="2" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -3858,21 +3897,21 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>202</v>
+        <v>301</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>90</v>
+        <v>199</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -3880,19 +3919,19 @@
       <c r="F95" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G95" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G95" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>297</v>
+        <v>145</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>9</v>
@@ -3903,13 +3942,13 @@
       <c r="F96" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>306</v>
+      <c r="G96" s="5" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>354</v>
+        <v>88</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>89</v>
@@ -3927,81 +3966,81 @@
         <v>6</v>
       </c>
       <c r="G97" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A98" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A99" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A100" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G100" s="2" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A98" s="2" t="s">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A101" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A100" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A101" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>81</v>
@@ -4013,24 +4052,24 @@
         <v>76</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G101" s="5" t="s">
-        <v>294</v>
+      <c r="G101" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>76</v>
@@ -4042,18 +4081,18 @@
         <v>6</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>153</v>
+        <v>291</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>76</v>
@@ -4065,18 +4104,18 @@
         <v>6</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>348</v>
+        <v>293</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>76</v>
@@ -4087,19 +4126,19 @@
       <c r="F104" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G104" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G104" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>352</v>
+        <v>387</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>98</v>
+        <v>389</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>76</v>
@@ -4110,13 +4149,13 @@
       <c r="F105" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G105" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G105" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>83</v>
@@ -4133,22 +4172,22 @@
       <c r="F106" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G106" s="5" t="s">
-        <v>300</v>
+      <c r="G106" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -4157,133 +4196,133 @@
         <v>6</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A109" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A110" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G110" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A111" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A112" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="D112" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="2" t="s">
+      <c r="E112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="2" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A109" s="2" t="s">
+    <row r="113" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A113" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B113" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C109" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A110" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A111" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A112" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A113" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>9</v>
@@ -4294,19 +4333,19 @@
       <c r="F113" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>144</v>
+      <c r="G113" s="5" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>140</v>
+        <v>17</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>9</v>
@@ -4318,11 +4357,100 @@
         <v>6</v>
       </c>
       <c r="G114" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A115" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A116" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A117" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A118" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G115" s="5"/>
     </row>
     <row r="119" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G119" s="5"/>
@@ -4336,40 +4464,66 @@
     <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G122" s="5"/>
     </row>
+    <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G123" s="5"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A127" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H122">
-    <sortCondition ref="C14:C122"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H123">
+    <sortCondition ref="A1:A123"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="G12" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G13" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G27" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
     <hyperlink ref="G58" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G63" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G75" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G64" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G78" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
     <hyperlink ref="G47" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G93" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G95" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
-    <hyperlink ref="G3" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
+    <hyperlink ref="G96" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G98" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G34" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G36" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G33" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G35" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
     <hyperlink ref="G37" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
     <hyperlink ref="G46" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G60" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G71" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G59" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G79" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
     <hyperlink ref="G80" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G109" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G113" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G18" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G77" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G101" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G31" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G30" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G106" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G74" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G64" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G82" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G104" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G30" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G36" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G110" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G76" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G65" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
     <hyperlink ref="G53" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G78" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G14" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G84" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G105" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1232" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCB8598C-601A-DE4B-B43F-E6A42BD55B14}"/>
+  <xr:revisionPtr revIDLastSave="1470" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF4E9E7-8986-1343-BCDA-4C8018B38202}"/>
   <bookViews>
-    <workbookView xWindow="-4280" yWindow="-21100" windowWidth="34600" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="5060" yWindow="-21100" windowWidth="28940" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="521">
   <si>
     <t>Study_ID</t>
   </si>
@@ -234,9 +234,6 @@
     <t>Ictaluridae</t>
   </si>
   <si>
-    <t xml:space="preserve">N </t>
-  </si>
-  <si>
     <t>DOI: https://doi.org/10.1080/00028487.2017.1362471</t>
   </si>
   <si>
@@ -1306,13 +1303,310 @@
   </si>
   <si>
     <t xml:space="preserve">	Moronidae</t>
+  </si>
+  <si>
+    <t>RHKL-1</t>
+  </si>
+  <si>
+    <t>Western Speckled Dace</t>
+  </si>
+  <si>
+    <t>Rhinichthys klamathensis</t>
+  </si>
+  <si>
+    <t>GIPA-1</t>
+  </si>
+  <si>
+    <t>Gila pandora</t>
+  </si>
+  <si>
+    <t>Rio Grande Chub</t>
+  </si>
+  <si>
+    <t>ONMY-4</t>
+  </si>
+  <si>
+    <t>Rainbow Trout</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/mec.15367</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/mec.16806</t>
+  </si>
+  <si>
+    <t>Atherinopsidae</t>
+  </si>
+  <si>
+    <t>Poeciliidae</t>
+  </si>
+  <si>
+    <t>LASI-1</t>
+  </si>
+  <si>
+    <t>LEME-1</t>
+  </si>
+  <si>
+    <t>MISA-1</t>
+  </si>
+  <si>
+    <t>COCA-1</t>
+  </si>
+  <si>
+    <t>COHY-1</t>
+  </si>
+  <si>
+    <t>FUCA-1</t>
+  </si>
+  <si>
+    <t>CAOL-1</t>
+  </si>
+  <si>
+    <t>CHER-1</t>
+  </si>
+  <si>
+    <t>CYGA-1</t>
+  </si>
+  <si>
+    <t>CYWH-1</t>
+  </si>
+  <si>
+    <t>LUCH-1</t>
+  </si>
+  <si>
+    <t>LUPI-1</t>
+  </si>
+  <si>
+    <t>LUZO-1</t>
+  </si>
+  <si>
+    <t>LYUM-1</t>
+  </si>
+  <si>
+    <t>NOBO-1</t>
+  </si>
+  <si>
+    <t>NONU-1</t>
+  </si>
+  <si>
+    <t>NOPE-1</t>
+  </si>
+  <si>
+    <t>NOTE-1</t>
+  </si>
+  <si>
+    <t>PINO-1</t>
+  </si>
+  <si>
+    <t>SEAT-3</t>
+  </si>
+  <si>
+    <t>ETBL-1</t>
+  </si>
+  <si>
+    <t>ETCA-5</t>
+  </si>
+  <si>
+    <t>ETFL-1</t>
+  </si>
+  <si>
+    <t>ETJU-1</t>
+  </si>
+  <si>
+    <t>ETSP-1</t>
+  </si>
+  <si>
+    <t>ETZO-1</t>
+  </si>
+  <si>
+    <t>GAAF-1</t>
+  </si>
+  <si>
+    <t>Etheostoma flabellare</t>
+  </si>
+  <si>
+    <t>Cottus hypselurus</t>
+  </si>
+  <si>
+    <t>Chrosomus erythrogaster</t>
+  </si>
+  <si>
+    <t>Cottus carolinae</t>
+  </si>
+  <si>
+    <t>CAAN-2</t>
+  </si>
+  <si>
+    <t>Etheostoma blennioides</t>
+  </si>
+  <si>
+    <t>Pimephales notatus</t>
+  </si>
+  <si>
+    <t>Etheostoma juliae</t>
+  </si>
+  <si>
+    <t>Lythrurus umbratilis</t>
+  </si>
+  <si>
+    <t>Etheostoma spectabile</t>
+  </si>
+  <si>
+    <t>Fundulus catenatus</t>
+  </si>
+  <si>
+    <t>Labidesthes sicculus</t>
+  </si>
+  <si>
+    <t>Brook Silverside</t>
+  </si>
+  <si>
+    <t>Notropis telescopus</t>
+  </si>
+  <si>
+    <t>Etheostoma zonale</t>
+  </si>
+  <si>
+    <t>Luxilus chrysocephalus</t>
+  </si>
+  <si>
+    <t>Lepomis megalotis</t>
+  </si>
+  <si>
+    <t>Gambusia affinis</t>
+  </si>
+  <si>
+    <t>Cyprinella whipplei</t>
+  </si>
+  <si>
+    <t>Micropterus salmoides</t>
+  </si>
+  <si>
+    <t>Luxilus zonatus</t>
+  </si>
+  <si>
+    <t>MIDO-3</t>
+  </si>
+  <si>
+    <t>Notropis boops</t>
+  </si>
+  <si>
+    <t>Notropis nubilus</t>
+  </si>
+  <si>
+    <t>Campostoma oligolepis</t>
+  </si>
+  <si>
+    <t>Cyprinella galactura</t>
+  </si>
+  <si>
+    <t>Notropis percobromus</t>
+  </si>
+  <si>
+    <t>Luxilus pilsbryi</t>
+  </si>
+  <si>
+    <t>FUOL-3</t>
+  </si>
+  <si>
+    <t>Longear sunfish</t>
+  </si>
+  <si>
+    <t>Largemouth Bass</t>
+  </si>
+  <si>
+    <t>Banded Sculpin</t>
+  </si>
+  <si>
+    <t>Ozark Sculpin</t>
+  </si>
+  <si>
+    <t>Northern Studfish</t>
+  </si>
+  <si>
+    <t>Blackspotted Topminnow</t>
+  </si>
+  <si>
+    <t>Largescale Stoneroller</t>
+  </si>
+  <si>
+    <t>Southern Redbelly Dace</t>
+  </si>
+  <si>
+    <t>Whitetail Shiner</t>
+  </si>
+  <si>
+    <t>Steelcolor Shiner</t>
+  </si>
+  <si>
+    <t>Striped Shiner</t>
+  </si>
+  <si>
+    <t>Duskystripe Shiner</t>
+  </si>
+  <si>
+    <t>Bleeding Shiner</t>
+  </si>
+  <si>
+    <t>Redfin Shiner</t>
+  </si>
+  <si>
+    <t>Bigeye shiner</t>
+  </si>
+  <si>
+    <t>Ozark Minnow</t>
+  </si>
+  <si>
+    <t>Carmine Shiner</t>
+  </si>
+  <si>
+    <t>Telescope Shiner</t>
+  </si>
+  <si>
+    <t>Bluntnose Minnow</t>
+  </si>
+  <si>
+    <t>Greenside Darter</t>
+  </si>
+  <si>
+    <t>Fantail Darter</t>
+  </si>
+  <si>
+    <t>Yoke darter</t>
+  </si>
+  <si>
+    <t>Orangethroat Darter</t>
+  </si>
+  <si>
+    <t>Banded Darter</t>
+  </si>
+  <si>
+    <t>Western Mosquitofish</t>
+  </si>
+  <si>
+    <t>LEMA-2</t>
+  </si>
+  <si>
+    <t>SAFO-6</t>
+  </si>
+  <si>
+    <t>Riffle Sculpin</t>
+  </si>
+  <si>
+    <t>Cottus gulosus</t>
+  </si>
+  <si>
+    <t>COAS-2</t>
+  </si>
+  <si>
+    <t>COGU-1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1340,6 +1634,12 @@
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1398,10 +1698,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1721,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -1757,18 +2053,18 @@
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>309</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -1780,18 +2076,18 @@
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>64</v>
@@ -1803,7 +2099,7 @@
         <v>6</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
@@ -1849,22 +2145,22 @@
         <v>6</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
@@ -1872,22 +2168,22 @@
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
@@ -1895,7 +2191,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.15">
@@ -1906,7 +2202,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
@@ -1918,67 +2214,67 @@
         <v>6</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
-        <v>115</v>
+        <v>465</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>116</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>209</v>
+        <v>431</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>312</v>
+        <v>114</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>314</v>
+        <v>115</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>313</v>
+        <v>116</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>315</v>
+        <v>25</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>306</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>377</v>
+        <v>311</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>379</v>
+        <v>313</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>314</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -1987,15 +2283,15 @@
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>383</v>
+        <v>305</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>381</v>
@@ -2010,18 +2306,18 @@
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>22</v>
+        <v>377</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>23</v>
+        <v>379</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>380</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>25</v>
@@ -2032,22 +2328,22 @@
       <c r="F13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G13" s="2" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>270</v>
+        <v>440</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>485</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
@@ -2056,21 +2352,21 @@
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>272</v>
+        <v>431</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>357</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>366</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>365</v>
+        <v>24</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>368</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
@@ -2078,91 +2374,91 @@
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G15" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>269</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>264</v>
+        <v>25</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>267</v>
+        <v>441</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>262</v>
+        <v>497</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>266</v>
+        <v>463</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>264</v>
+        <v>9</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>273</v>
+        <v>356</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>274</v>
+        <v>365</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>275</v>
+        <v>364</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>264</v>
+        <v>367</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G18" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>248</v>
+        <v>519</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>253</v>
+        <v>365</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>252</v>
+        <v>364</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>9</v>
+        <v>367</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>11</v>
@@ -2170,22 +2466,22 @@
       <c r="F19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G19" s="2" t="s">
-        <v>256</v>
+      <c r="G19" s="5" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -2194,21 +2490,21 @@
         <v>6</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>127</v>
+        <v>266</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>128</v>
+        <v>261</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>129</v>
+        <v>265</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>9</v>
+        <v>263</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>11</v>
@@ -2217,21 +2513,21 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>130</v>
+        <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>164</v>
+        <v>437</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>492</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>166</v>
+        <v>464</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>263</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
@@ -2240,21 +2536,21 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>236</v>
+        <v>273</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>243</v>
+        <v>274</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>11</v>
@@ -2262,22 +2558,22 @@
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G23" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>355</v>
+        <v>520</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>359</v>
+        <v>517</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>360</v>
+        <v>518</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>30</v>
+        <v>367</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>11</v>
@@ -2285,22 +2581,22 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="2" t="s">
-        <v>358</v>
+      <c r="G24" s="5" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
-        <v>338</v>
+        <v>438</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>340</v>
+        <v>493</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>336</v>
+        <v>462</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
@@ -2309,21 +2605,21 @@
         <v>6</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>342</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>27</v>
+        <v>442</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>498</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>29</v>
+        <v>486</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -2332,21 +2628,21 @@
         <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>33</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>31</v>
+        <v>247</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>29</v>
+        <v>251</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
@@ -2354,22 +2650,22 @@
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G27" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>28</v>
+        <v>253</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>29</v>
+        <v>251</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>11</v>
@@ -2377,22 +2673,22 @@
       <c r="F28" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G28" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>28</v>
+        <v>126</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -2401,21 +2697,21 @@
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>335</v>
+        <v>163</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>334</v>
+        <v>164</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>333</v>
+        <v>165</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
@@ -2423,22 +2719,22 @@
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G30" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>172</v>
+        <v>443</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>499</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>171</v>
+        <v>479</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -2446,42 +2742,42 @@
       <c r="F31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>173</v>
+      <c r="G31" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>30</v>
+        <v>241</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>354</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>35</v>
+        <v>358</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>36</v>
+        <v>359</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>30</v>
@@ -2492,19 +2788,19 @@
       <c r="F33" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>208</v>
+      <c r="G33" s="2" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>190</v>
+        <v>454</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>196</v>
+        <v>509</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>192</v>
+        <v>466</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -2516,18 +2812,18 @@
         <v>6</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>337</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>37</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>39</v>
+        <v>335</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -2538,19 +2834,19 @@
       <c r="F35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G35" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G35" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>329</v>
+        <v>27</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>332</v>
+        <v>28</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>330</v>
+        <v>29</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
@@ -2561,19 +2857,19 @@
       <c r="F36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G36" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G36" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>30</v>
@@ -2584,19 +2880,19 @@
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G37" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>43</v>
+        <v>167</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>30</v>
@@ -2607,42 +2903,42 @@
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G38" s="5" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>194</v>
+        <v>322</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>193</v>
+        <v>29</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>195</v>
+        <v>323</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>249</v>
+        <v>455</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>251</v>
+        <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>250</v>
+        <v>29</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>30</v>
@@ -2654,18 +2950,18 @@
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>255</v>
+        <v>334</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>251</v>
+        <v>333</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>30</v>
@@ -2676,19 +2972,19 @@
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G41" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>341</v>
+        <v>456</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>510</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>337</v>
+        <v>461</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
@@ -2700,44 +2996,44 @@
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>119</v>
+        <v>169</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>212</v>
+      <c r="G43" s="5" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>47</v>
+        <v>457</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>51</v>
+        <v>511</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>49</v>
+        <v>468</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>11</v>
@@ -2746,21 +3042,21 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>213</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>48</v>
+        <v>243</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>53</v>
+        <v>244</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>50</v>
+        <v>245</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>11</v>
@@ -2769,21 +3065,21 @@
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>213</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>11</v>
@@ -2792,21 +3088,21 @@
         <v>6</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>110</v>
+        <v>189</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>112</v>
+        <v>191</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>113</v>
+        <v>30</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>11</v>
@@ -2814,22 +3110,22 @@
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G47" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>11</v>
@@ -2837,22 +3133,22 @@
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G48" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>141</v>
+        <v>331</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>138</v>
+        <v>329</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>11</v>
@@ -2860,22 +3156,22 @@
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G49" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>11</v>
@@ -2883,22 +3179,22 @@
       <c r="F50" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>215</v>
+      <c r="G50" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>11</v>
@@ -2906,22 +3202,22 @@
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>60</v>
+      <c r="G51" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>121</v>
+        <v>458</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>122</v>
+        <v>512</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>123</v>
+        <v>470</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>11</v>
@@ -2930,21 +3226,21 @@
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>386</v>
+        <v>190</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>376</v>
+        <v>30</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>11</v>
@@ -2952,22 +3248,22 @@
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>374</v>
+      <c r="G53" s="2" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>347</v>
+        <v>250</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>346</v>
+        <v>249</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>11</v>
@@ -2976,67 +3272,67 @@
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>302</v>
+        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>62</v>
+        <v>254</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>63</v>
+        <v>250</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>61</v>
+        <v>249</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>63</v>
+        <v>338</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>340</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>61</v>
+        <v>336</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>216</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>231</v>
+        <v>459</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>63</v>
+        <v>513</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>61</v>
+        <v>475</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>11</v>
@@ -3045,21 +3341,21 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>93</v>
+        <v>439</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>94</v>
+        <v>494</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>95</v>
+        <v>471</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -3067,22 +3363,22 @@
       <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G58" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -3090,22 +3386,22 @@
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>217</v>
+      <c r="G59" s="4" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>228</v>
+        <v>47</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>234</v>
+        <v>51</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>238</v>
+        <v>49</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -3114,21 +3410,21 @@
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>174</v>
+        <v>48</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>176</v>
+        <v>53</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>178</v>
+        <v>52</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -3137,44 +3433,44 @@
         <v>6</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>180</v>
+        <v>53</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>181</v>
+        <v>50</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G62" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>411</v>
+        <v>489</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>416</v>
+        <v>495</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>417</v>
+        <v>50</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>261</v>
+        <v>52</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -3182,111 +3478,111 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>391</v>
+      <c r="G63" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="E66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A67" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A66" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A67" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>391</v>
+      <c r="G67" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>9</v>
@@ -3298,18 +3594,18 @@
         <v>6</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>139</v>
+        <v>425</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>9</v>
@@ -3320,22 +3616,22 @@
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>306</v>
+      <c r="G69" s="5" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>325</v>
+        <v>57</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>327</v>
+        <v>58</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>328</v>
+        <v>59</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -3344,21 +3640,21 @@
         <v>6</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>326</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>277</v>
+        <v>120</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>280</v>
+        <v>122</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -3367,21 +3663,21 @@
         <v>6</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>305</v>
+        <v>385</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>280</v>
+        <v>122</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>261</v>
+        <v>375</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -3389,45 +3685,45 @@
       <c r="F72" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G72" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>185</v>
+        <v>302</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>186</v>
+        <v>345</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>187</v>
+      <c r="G73" s="2" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>126</v>
+        <v>62</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3436,21 +3732,21 @@
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>229</v>
+        <v>91</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -3459,21 +3755,21 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>369</v>
+        <v>230</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>370</v>
+        <v>63</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>371</v>
+        <v>61</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3481,22 +3777,22 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G76" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>356</v>
+        <v>92</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>361</v>
+        <v>93</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>364</v>
+        <v>94</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>363</v>
+        <v>95</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -3504,22 +3800,22 @@
       <c r="F77" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G77" s="2" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G77" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>99</v>
+        <v>434</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>100</v>
+        <v>473</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>101</v>
+        <v>472</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>432</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -3527,22 +3823,22 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>105</v>
+      <c r="G78" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -3551,21 +3847,21 @@
         <v>6</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>74</v>
+        <v>233</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -3573,22 +3869,22 @@
       <c r="F80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G80" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>109</v>
+        <v>515</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>233</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>108</v>
+        <v>237</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -3597,21 +3893,21 @@
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>287</v>
+        <v>435</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>288</v>
+        <v>490</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>289</v>
+        <v>477</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -3619,22 +3915,22 @@
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G82" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>350</v>
+        <v>173</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -3643,21 +3939,21 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>384</v>
+        <v>178</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>288</v>
+        <v>179</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>289</v>
+        <v>180</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -3665,45 +3961,45 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G84" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>131</v>
+        <v>410</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>132</v>
+        <v>415</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>134</v>
+        <v>416</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>76</v>
+        <v>260</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G85" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G85" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>345</v>
+        <v>444</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>500</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>344</v>
+        <v>476</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -3712,21 +4008,21 @@
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>281</v>
+        <v>445</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>282</v>
+        <v>501</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>283</v>
+        <v>488</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -3735,161 +4031,160 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="H87" s="2"/>
-    </row>
-    <row r="88" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A89" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A90" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A92" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A89" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A92" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="D92" s="2" t="s">
-        <v>30</v>
+        <v>260</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G92" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>230</v>
+        <v>409</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>235</v>
+        <v>413</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>239</v>
+        <v>412</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A94" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A94" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
       </c>
@@ -3897,21 +4192,21 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.15">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>198</v>
+        <v>141</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>199</v>
+        <v>138</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>201</v>
+        <v>9</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -3920,21 +4215,21 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>145</v>
+        <v>324</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>148</v>
+        <v>326</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>147</v>
+        <v>327</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -3942,22 +4237,22 @@
       <c r="F96" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>146</v>
+      <c r="G96" s="2" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>88</v>
+        <v>276</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -3966,21 +4261,21 @@
         <v>6</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>202</v>
+        <v>304</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -3988,22 +4283,22 @@
       <c r="F98" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G98" s="5" t="s">
-        <v>204</v>
+      <c r="G98" s="2" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>297</v>
+        <v>482</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>89</v>
+        <v>277</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>90</v>
+        <v>279</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -4012,21 +4307,21 @@
         <v>6</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>306</v>
+        <v>431</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>354</v>
+        <v>436</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>89</v>
+        <v>491</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>90</v>
+        <v>480</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -4035,44 +4330,44 @@
         <v>6</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>81</v>
+        <v>183</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>220</v>
+      <c r="G101" s="5" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>160</v>
+        <v>418</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>81</v>
+        <v>419</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>84</v>
+        <v>420</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>76</v>
+        <v>421</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -4081,21 +4376,21 @@
         <v>6</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>161</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>291</v>
+        <v>125</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -4104,21 +4399,21 @@
         <v>6</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>293</v>
+        <v>228</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -4126,22 +4421,22 @@
       <c r="F104" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G104" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G104" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>387</v>
+        <v>448</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>388</v>
+        <v>504</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>389</v>
+        <v>483</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -4149,22 +4444,22 @@
       <c r="F105" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G105" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G105" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>83</v>
+        <v>369</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>98</v>
+        <v>370</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -4172,45 +4467,45 @@
       <c r="F106" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G106" s="2" t="s">
-        <v>221</v>
+      <c r="G106" s="5" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>153</v>
+        <v>355</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>83</v>
+        <v>360</v>
       </c>
       <c r="C107" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A108" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="B108" s="2" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -4218,22 +4513,22 @@
       <c r="F108" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G108" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G108" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>352</v>
+        <v>449</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>98</v>
+        <v>484</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -4242,21 +4537,21 @@
         <v>6</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>351</v>
+        <v>450</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>83</v>
+        <v>506</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>98</v>
+        <v>487</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -4264,19 +4559,19 @@
       <c r="F110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G110" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G110" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>157</v>
+        <v>70</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>159</v>
+        <v>71</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>30</v>
@@ -4287,243 +4582,1090 @@
       <c r="F111" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>155</v>
+      <c r="G111" s="5" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A113" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A114" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A115" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="28" x14ac:dyDescent="0.15">
+      <c r="A116" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A117" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A118" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A119" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A120" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H120" s="2"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A121" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A122" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A123" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A124" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A125" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A126" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A127" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A128" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A129" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A130" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A131" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A132" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A133" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A134" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A135" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A136" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A137" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A138" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A139" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A140" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A141" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A142" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A143" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A144" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A145" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A146" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A147" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A148" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A113" s="2" t="s">
+    </row>
+    <row r="149" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A149" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C113" s="2" t="s">
+      <c r="C149" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D113" s="2" t="s">
+      <c r="D149" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E113" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G113" s="5" t="s">
+      <c r="E149" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A150" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A151" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A152" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A153" s="2" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A114" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D114" s="2" t="s">
+      <c r="B153" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A115" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="C115" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D115" s="2" t="s">
+      <c r="E153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A154" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D154" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G115" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A116" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="D116" s="2" t="s">
+      <c r="E154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A155" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A117" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A118" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G119" s="5"/>
-    </row>
-    <row r="120" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G120" s="5"/>
-    </row>
-    <row r="121" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G121" s="5"/>
-    </row>
-    <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G122" s="5"/>
-    </row>
-    <row r="123" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G123" s="5"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A127" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>392</v>
+      <c r="E155" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G159" s="5"/>
+    </row>
+    <row r="160" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G160" s="5"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A165" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H123">
-    <sortCondition ref="A1:A123"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H155">
+    <sortCondition ref="A155"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G13" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G27" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G58" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G64" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G78" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G47" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G96" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G98" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G15" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G37" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G77" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G90" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G108" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G64" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G131" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G134" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G33" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G35" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G37" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G46" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G59" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G79" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G80" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G113" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G18" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G82" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G104" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G30" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G36" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G110" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G76" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G65" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G53" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G84" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G105" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G46" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G48" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G50" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G62" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G79" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G111" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G113" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G149" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G23" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G115" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G140" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G41" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G49" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G146" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G106" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G91" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G72" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G117" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G141" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G132" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
+    <hyperlink ref="G19" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
+    <hyperlink ref="G24" r:id="rId32" xr:uid="{96BB9605-0761-7B42-9979-49FF10E1A826}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -4542,102 +5684,102 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1470" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF4E9E7-8986-1343-BCDA-4C8018B38202}"/>
+  <xr:revisionPtr revIDLastSave="1472" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C6D707-394C-824E-BDEF-FC4EC63002EA}"/>
   <bookViews>
     <workbookView xWindow="5060" yWindow="-21100" windowWidth="28940" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -5047,7 +5047,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
         <v>422</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
         <v>386</v>
       </c>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1472" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4C6D707-394C-824E-BDEF-FC4EC63002EA}"/>
+  <xr:revisionPtr revIDLastSave="1502" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF4C9D2-3411-2041-A0AD-82C0A2803A3B}"/>
   <bookViews>
-    <workbookView xWindow="5060" yWindow="-21100" windowWidth="28940" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4380" yWindow="-21100" windowWidth="28940" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="527">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1587,19 +1587,37 @@
     <t>LEMA-2</t>
   </si>
   <si>
+    <t>Riffle Sculpin</t>
+  </si>
+  <si>
+    <t>Cottus gulosus</t>
+  </si>
+  <si>
+    <t>COAS-2</t>
+  </si>
+  <si>
+    <t>COGU-1</t>
+  </si>
+  <si>
+    <t>ETTR-1</t>
+  </si>
+  <si>
+    <t>Trispot Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma trisella</t>
+  </si>
+  <si>
+    <t>SAVI-3</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/mec.17558</t>
+  </si>
+  <si>
     <t>SAFO-6</t>
   </si>
   <si>
-    <t>Riffle Sculpin</t>
-  </si>
-  <si>
-    <t>Cottus gulosus</t>
-  </si>
-  <si>
-    <t>COAS-2</t>
-  </si>
-  <si>
-    <t>COGU-1</t>
+    <t>SAFO-7</t>
   </si>
 </sst>
 </file>
@@ -2017,7 +2035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H165"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -2449,7 +2467,7 @@
     </row>
     <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>365</v>
@@ -2562,15 +2580,15 @@
         <v>275</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>367</v>
@@ -2581,7 +2599,7 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" t="s">
         <v>392</v>
       </c>
     </row>
@@ -3298,15 +3316,15 @@
         <v>255</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>340</v>
+        <v>520</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>521</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>336</v>
+        <v>522</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
@@ -3317,19 +3335,19 @@
       <c r="F56" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G56" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G56" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>513</v>
+        <v>338</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>340</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>475</v>
+        <v>336</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
@@ -3341,21 +3359,21 @@
         <v>6</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>431</v>
+        <v>341</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>11</v>
@@ -3369,13 +3387,13 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>117</v>
+        <v>439</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>118</v>
+        <v>494</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>119</v>
+        <v>471</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>52</v>
@@ -3386,19 +3404,19 @@
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>211</v>
+      <c r="G59" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>51</v>
+        <v>118</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>52</v>
@@ -3409,19 +3427,19 @@
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>212</v>
+      <c r="G60" s="4" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>52</v>
@@ -3436,9 +3454,9 @@
         <v>212</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>53</v>
@@ -3455,16 +3473,16 @@
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G62" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>489</v>
+        <v>90</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>495</v>
+        <v>53</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>50</v>
@@ -3478,68 +3496,68 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="G63" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="2" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B65" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C65" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D64" s="2" t="s">
+      <c r="D65" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="5" t="s">
+      <c r="E65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G65" s="5" t="s">
         <v>113</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>134</v>
+        <v>460</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>140</v>
+        <v>514</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>137</v>
+        <v>478</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>9</v>
+        <v>433</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -3548,12 +3566,12 @@
         <v>6</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>143</v>
+        <v>431</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>315</v>
+        <v>134</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>140</v>
@@ -3571,18 +3589,18 @@
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>305</v>
+        <v>143</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>56</v>
+        <v>315</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>9</v>
@@ -3594,18 +3612,18 @@
         <v>6</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>426</v>
+        <v>56</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>9</v>
@@ -3616,19 +3634,19 @@
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G69" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>59</v>
+        <v>425</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>426</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>9</v>
@@ -3639,19 +3657,19 @@
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="2" t="s">
-        <v>60</v>
+      <c r="G70" s="5" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>9</v>
@@ -3663,12 +3681,12 @@
         <v>6</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>385</v>
+        <v>120</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>121</v>
@@ -3677,53 +3695,53 @@
         <v>122</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="5" t="s">
+      <c r="E73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>373</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>62</v>
+        <v>302</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>63</v>
+        <v>346</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>61</v>
+        <v>345</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3732,12 +3750,12 @@
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>65</v>
+        <v>301</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>63</v>
@@ -3755,12 +3773,12 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>230</v>
+        <v>91</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>63</v>
@@ -3778,87 +3796,87 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A77" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A77" s="2" t="s">
+    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A78" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B78" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C77" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D78" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" s="5" t="s">
+      <c r="E78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G78" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A78" s="2" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A79" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="2" t="s">
+      <c r="E79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G79" s="2" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A79" s="2" t="s">
+    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A80" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G79" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A80" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>21</v>
@@ -3869,13 +3887,13 @@
       <c r="F80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>226</v>
+      <c r="G80" s="5" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>515</v>
+        <v>227</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>233</v>
@@ -3884,7 +3902,7 @@
         <v>237</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>260</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -3893,18 +3911,18 @@
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>431</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>435</v>
+        <v>515</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>490</v>
+        <v>233</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>477</v>
+        <v>237</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>260</v>
@@ -3919,107 +3937,107 @@
         <v>431</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A84" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B84" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C83" s="6" t="s">
+      <c r="C84" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G83" s="2" t="s">
+      <c r="E84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="2" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A84" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B86" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="C85" s="2" t="s">
+      <c r="C86" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D85" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G85" s="5" t="s">
+      <c r="E86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G86" s="5" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A86" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>9</v>
@@ -4036,13 +4054,13 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>9</v>
@@ -4059,13 +4077,13 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
@@ -4080,15 +4098,15 @@
         <v>431</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>101</v>
+        <v>447</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>102</v>
+        <v>503</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>103</v>
+        <v>469</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>9</v>
@@ -4099,19 +4117,19 @@
       <c r="F90" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G90" s="5" t="s">
-        <v>104</v>
+      <c r="G90" s="2" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>374</v>
+        <v>101</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>371</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>372</v>
+        <v>103</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>9</v>
@@ -4123,21 +4141,21 @@
         <v>6</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>373</v>
+        <v>104</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>409</v>
+        <v>374</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>413</v>
+        <v>371</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -4146,7 +4164,7 @@
         <v>6</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -4172,18 +4190,18 @@
         <v>390</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>135</v>
+        <v>409</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>141</v>
+        <v>413</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>138</v>
+        <v>412</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>9</v>
+        <v>260</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -4191,13 +4209,13 @@
       <c r="F94" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>143</v>
+      <c r="G94" s="5" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>316</v>
+        <v>135</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>141</v>
@@ -4215,21 +4233,21 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>305</v>
+        <v>143</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>326</v>
+        <v>141</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -4238,18 +4256,18 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>276</v>
+        <v>324</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>277</v>
+        <v>326</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>279</v>
+        <v>327</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>260</v>
@@ -4261,12 +4279,12 @@
         <v>6</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>278</v>
+        <v>325</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>304</v>
+        <v>276</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>277</v>
@@ -4284,12 +4302,12 @@
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>305</v>
+        <v>278</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>482</v>
+        <v>304</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>277</v>
@@ -4307,18 +4325,18 @@
         <v>6</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>431</v>
+        <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>436</v>
+        <v>482</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>491</v>
+        <v>277</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>480</v>
+        <v>279</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>260</v>
@@ -4333,64 +4351,64 @@
         <v>431</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A102" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B101" s="6" t="s">
+      <c r="B102" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C101" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="D101" s="2" t="s">
+      <c r="D102" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" s="5" t="s">
+      <c r="E102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G102" s="5" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A102" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>125</v>
+        <v>418</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>123</v>
+        <v>419</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>124</v>
+        <v>420</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -4399,12 +4417,12 @@
         <v>6</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>129</v>
+        <v>391</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>123</v>
@@ -4422,18 +4440,18 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>226</v>
+        <v>129</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>448</v>
+        <v>228</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>504</v>
+        <v>123</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>483</v>
+        <v>124</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>9</v>
@@ -4445,18 +4463,18 @@
         <v>6</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>368</v>
+        <v>448</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>369</v>
+        <v>504</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>370</v>
+        <v>483</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>9</v>
@@ -4467,65 +4485,65 @@
       <c r="F106" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G106" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A107" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="5" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A107" s="2" t="s">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B108" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C108" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D108" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" s="2" t="s">
+      <c r="E108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>361</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A108" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>449</v>
+        <v>98</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>505</v>
+        <v>99</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>484</v>
+        <v>100</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>9</v>
@@ -4536,19 +4554,19 @@
       <c r="F109" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>431</v>
+      <c r="G109" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>9</v>
@@ -4563,84 +4581,84 @@
         <v>431</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A112" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B112" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C112" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D112" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G111" s="5" t="s">
+      <c r="E112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A112" s="2" t="s">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A113" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B113" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="C112" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D112" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G112" s="2" t="s">
+      <c r="E113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>431</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A113" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>108</v>
+        <v>72</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>75</v>
@@ -4651,19 +4669,19 @@
       <c r="F114" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G114" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G114" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>287</v>
+        <v>105</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>288</v>
+        <v>107</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>75</v>
@@ -4674,19 +4692,19 @@
       <c r="F115" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G115" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" ht="28" x14ac:dyDescent="0.15">
+      <c r="G115" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>348</v>
+        <v>286</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>349</v>
+        <v>288</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>75</v>
@@ -4697,19 +4715,19 @@
       <c r="F116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G116" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G116" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>287</v>
+        <v>298</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>348</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>75</v>
@@ -4720,19 +4738,19 @@
       <c r="F117" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G117" s="5" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G117" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>130</v>
+        <v>383</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>131</v>
+        <v>287</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>133</v>
+        <v>288</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>75</v>
@@ -4743,19 +4761,19 @@
       <c r="F118" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G118" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G118" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>344</v>
+        <v>130</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>343</v>
+        <v>133</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>75</v>
@@ -4767,18 +4785,18 @@
         <v>6</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.15">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>281</v>
+        <v>342</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>282</v>
+        <v>343</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>75</v>
@@ -4790,19 +4808,18 @@
         <v>6</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H120" s="2"/>
+        <v>294</v>
+      </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>428</v>
+        <v>280</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>429</v>
+        <v>281</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>343</v>
+        <v>282</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>75</v>
@@ -4814,67 +4831,68 @@
         <v>6</v>
       </c>
       <c r="G121" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H121" s="2"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A122" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" s="2" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A122" s="2" t="s">
+    <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A123" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B123" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C123" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D122" s="2" t="s">
+      <c r="D123" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G122" s="5" t="s">
+      <c r="E123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" s="5" t="s">
         <v>390</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A123" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>76</v>
+        <v>317</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>78</v>
+        <v>318</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>30</v>
+        <v>314</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -4883,12 +4901,12 @@
         <v>6</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>132</v>
+        <v>305</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>77</v>
@@ -4906,12 +4924,12 @@
         <v>6</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>188</v>
+        <v>155</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>77</v>
@@ -4929,21 +4947,21 @@
         <v>6</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>187</v>
+        <v>154</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>452</v>
+        <v>188</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>508</v>
+        <v>77</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -4952,18 +4970,18 @@
         <v>6</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>431</v>
+        <v>187</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>229</v>
+        <v>452</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>234</v>
+        <v>508</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>238</v>
+        <v>467</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>9</v>
@@ -4975,21 +4993,21 @@
         <v>6</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>226</v>
+        <v>431</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>197</v>
+        <v>234</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>200</v>
+        <v>9</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -4998,12 +5016,12 @@
         <v>6</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>300</v>
+        <v>196</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>197</v>
@@ -5021,41 +5039,41 @@
         <v>6</v>
       </c>
       <c r="G130" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A131" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="2" t="s">
         <v>301</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A131" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>422</v>
+        <v>144</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>424</v>
+        <v>147</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>9</v>
@@ -5067,18 +5085,18 @@
         <v>6</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.15">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>87</v>
+        <v>422</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>89</v>
+        <v>423</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>424</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>9</v>
@@ -5089,13 +5107,13 @@
       <c r="F133" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G133" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G133" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>201</v>
+        <v>87</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>88</v>
@@ -5112,13 +5130,13 @@
       <c r="F134" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G134" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G134" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>296</v>
+        <v>201</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>88</v>
@@ -5135,13 +5153,13 @@
       <c r="F135" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G135" s="2" t="s">
-        <v>305</v>
+      <c r="G135" s="5" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>353</v>
+        <v>296</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>88</v>
@@ -5159,35 +5177,35 @@
         <v>6</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
-        <v>79</v>
+        <v>353</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>219</v>
+        <v>295</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>80</v>
@@ -5199,18 +5217,18 @@
         <v>75</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>80</v>
@@ -5228,12 +5246,12 @@
         <v>6</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>80</v>
@@ -5250,19 +5268,19 @@
       <c r="F140" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G140" s="5" t="s">
-        <v>293</v>
+      <c r="G140" s="2" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
-        <v>386</v>
+        <v>292</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>387</v>
+        <v>80</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>75</v>
@@ -5274,18 +5292,18 @@
         <v>6</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.15">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
-        <v>81</v>
+        <v>386</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>97</v>
+        <v>388</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>75</v>
@@ -5296,13 +5314,13 @@
       <c r="F142" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G142" s="2" t="s">
-        <v>220</v>
+      <c r="G142" s="5" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
-        <v>152</v>
+        <v>81</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>82</v>
@@ -5320,12 +5338,12 @@
         <v>6</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
-        <v>347</v>
+        <v>152</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>82</v>
@@ -5343,12 +5361,12 @@
         <v>6</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>303</v>
+        <v>153</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>82</v>
@@ -5366,12 +5384,12 @@
         <v>6</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>82</v>
@@ -5388,91 +5406,91 @@
       <c r="F146" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G146" s="5" t="s">
+      <c r="G146" s="2" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A147" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" s="5" t="s">
         <v>299</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A147" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
-        <v>204</v>
+        <v>525</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A149" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C148" s="2" t="s">
+      <c r="C149" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D148" s="2" t="s">
+      <c r="D149" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E148" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A149" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G149" s="5" t="s">
-        <v>221</v>
+      <c r="G149" s="2" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>284</v>
+        <v>204</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>17</v>
+        <v>158</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -5481,12 +5499,12 @@
         <v>6</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>85</v>
@@ -5503,19 +5521,19 @@
       <c r="F151" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G151" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G151" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B152" s="6" t="s">
-        <v>150</v>
+        <v>284</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>149</v>
+        <v>17</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>9</v>
@@ -5526,19 +5544,19 @@
       <c r="F152" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G152" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G152" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B153" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>223</v>
+        <v>453</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>9</v>
@@ -5550,18 +5568,18 @@
         <v>6</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>142</v>
+        <v>148</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>9</v>
@@ -5572,19 +5590,19 @@
       <c r="F154" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G154" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G154" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>139</v>
+        <v>222</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>223</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -5596,76 +5614,147 @@
         <v>6</v>
       </c>
       <c r="G155" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A156" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A157" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G157" s="2" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G159" s="5"/>
-    </row>
-    <row r="160" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G160" s="5"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G161" s="5"/>
+    </row>
+    <row r="165" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A169" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C165" s="2" t="s">
+      <c r="C169" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D165" s="2" t="s">
+      <c r="D169" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G165" s="2" t="s">
-        <v>402</v>
+      <c r="E169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>403</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H155">
-    <sortCondition ref="A155"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H157">
+    <sortCondition ref="A157"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G15" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G37" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G77" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G90" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G108" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G64" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G131" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G134" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G78" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G91" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G109" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G65" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G132" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G135" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
     <hyperlink ref="G46" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
     <hyperlink ref="G48" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
     <hyperlink ref="G50" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G62" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G79" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G111" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G113" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G149" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G63" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G80" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G112" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G114" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G151" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G23" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G115" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G140" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G116" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G141" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
     <hyperlink ref="G41" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
     <hyperlink ref="G49" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G146" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G106" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G91" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G72" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G117" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G141" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
-    <hyperlink ref="G132" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
+    <hyperlink ref="G147" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G107" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G92" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G73" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G118" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G142" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G133" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
     <hyperlink ref="G19" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
-    <hyperlink ref="G24" r:id="rId32" xr:uid="{96BB9605-0761-7B42-9979-49FF10E1A826}"/>
+    <hyperlink ref="G165" r:id="rId32" xr:uid="{91B34FFD-CCB4-C046-8807-0D6025131D83}"/>
+    <hyperlink ref="G56" r:id="rId33" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1502" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3AF4C9D2-3411-2041-A0AD-82C0A2803A3B}"/>
+  <xr:revisionPtr revIDLastSave="1720" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB114131-E4C6-454A-B99C-392F61D00AA9}"/>
   <bookViews>
-    <workbookView xWindow="-4380" yWindow="-21100" windowWidth="28940" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4380" yWindow="-21100" windowWidth="22080" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="570">
   <si>
     <t>Study_ID</t>
   </si>
@@ -387,9 +387,6 @@
     <t>Bluehead Sucker</t>
   </si>
   <si>
-    <t>Pantosteus discobolus</t>
-  </si>
-  <si>
     <t>FUGR-1</t>
   </si>
   <si>
@@ -645,9 +642,6 @@
     <t>RHOS-2</t>
   </si>
   <si>
-    <t>Thesis.</t>
-  </si>
-  <si>
     <t>http://dx.doi.org/10.1016/j.ympev.2014.04.027</t>
   </si>
   <si>
@@ -1203,9 +1197,6 @@
     <t>Bull Trout</t>
   </si>
   <si>
-    <t>Coastal-Puget</t>
-  </si>
-  <si>
     <t>http://www.bioone.org/doi/full/10.3955/046.085.0305</t>
   </si>
   <si>
@@ -1618,13 +1609,151 @@
   </si>
   <si>
     <t>SAFO-7</t>
+  </si>
+  <si>
+    <t>Flathead Catfish</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1186/s13104-021-05725-2</t>
+  </si>
+  <si>
+    <t>Pylodictis olivaris</t>
+  </si>
+  <si>
+    <t>ETSA-2</t>
+  </si>
+  <si>
+    <t>ETNI-2</t>
+  </si>
+  <si>
+    <t>https://www.ndsu.edu/sites/default/files/fileadmin/wrri/technicalreport/Craig-Ali_Tackette.pdf</t>
+  </si>
+  <si>
+    <t>PYOL-1</t>
+  </si>
+  <si>
+    <t>ETPA-1</t>
+  </si>
+  <si>
+    <t>Etheostoma pallididorsum</t>
+  </si>
+  <si>
+    <t>Paleback Darter</t>
+  </si>
+  <si>
+    <t>ETHRAD-1</t>
+  </si>
+  <si>
+    <t>ETHEOSTOMA RADIOSUM</t>
+  </si>
+  <si>
+    <t>https://lair.etamu.edu/etd/1074/</t>
+  </si>
+  <si>
+    <t>Orangebelly darter</t>
+  </si>
+  <si>
+    <t>ICPU-4</t>
+  </si>
+  <si>
+    <t>https://files.dnr.state.mn.us/publications/fisheries/investigational_reports/579.pdf</t>
+  </si>
+  <si>
+    <t>Catostomus discobolus</t>
+  </si>
+  <si>
+    <t>MIDO-4</t>
+  </si>
+  <si>
+    <t>doi:10.1111/jfb.13296</t>
+  </si>
+  <si>
+    <t>PEFL-4</t>
+  </si>
+  <si>
+    <t>DOI: 10.1577/T07-276.1</t>
+  </si>
+  <si>
+    <t>POSP-3</t>
+  </si>
+  <si>
+    <t>DOI: 10.3750/AIP2014.44.3.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Micropterus salmoides </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y </t>
+  </si>
+  <si>
+    <t>https://etd.auburn.edu/bitstream/handle/10415/4795/Gowan_Thesis.pdf?sequence=2</t>
+  </si>
+  <si>
+    <t>APGR-2</t>
+  </si>
+  <si>
+    <t>POAN-1</t>
+  </si>
+  <si>
+    <t>White Crappie</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1093/tafafs/vnaf052</t>
+  </si>
+  <si>
+    <t>Pomoxis annularis</t>
+  </si>
+  <si>
+    <t>MISA-2</t>
+  </si>
+  <si>
+    <t>ETCY-1</t>
+  </si>
+  <si>
+    <t>ETHZON-1</t>
+  </si>
+  <si>
+    <t>Blueface Darter</t>
+  </si>
+  <si>
+    <t>Bandfin Darter</t>
+  </si>
+  <si>
+    <t>Etheostoma cyanoprosopum</t>
+  </si>
+  <si>
+    <t>Etheostoma zonistium</t>
+  </si>
+  <si>
+    <t>PINO-2</t>
+  </si>
+  <si>
+    <t>LEMA-3</t>
+  </si>
+  <si>
+    <t>Longear Sunfish</t>
+  </si>
+  <si>
+    <t>https://thekeep.eiu.edu/theses/2433/</t>
+  </si>
+  <si>
+    <t>SAFO-X</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-017-1027-6.</t>
+  </si>
+  <si>
+    <t>RHOS-5</t>
+  </si>
+  <si>
+    <t>ONCL-6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1659,6 +1788,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1681,7 +1816,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1700,6 +1835,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2035,7 +2176,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -2044,7 +2185,7 @@
     <col min="4" max="4" width="14.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="2"/>
-    <col min="7" max="7" width="58.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="79.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
@@ -2071,18 +2212,18 @@
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -2094,18 +2235,18 @@
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>64</v>
@@ -2117,7 +2258,7 @@
         <v>6</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
@@ -2163,21 +2304,21 @@
         <v>6</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
@@ -2186,90 +2327,90 @@
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>86</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>431</v>
+      <c r="G9" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>114</v>
+        <v>462</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>11</v>
@@ -2278,21 +2419,21 @@
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>208</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>311</v>
+        <v>114</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>313</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>312</v>
+        <v>540</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>314</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>11</v>
@@ -2301,21 +2442,21 @@
         <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>305</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>378</v>
+        <v>311</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>381</v>
+        <v>310</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
@@ -2324,18 +2465,18 @@
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>382</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>25</v>
@@ -2347,21 +2488,21 @@
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>440</v>
+        <v>375</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>496</v>
+        <v>377</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>485</v>
+        <v>378</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>11</v>
@@ -2370,41 +2511,41 @@
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A16" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>25</v>
@@ -2415,22 +2556,22 @@
       <c r="F16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G16" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>463</v>
+        <v>266</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>11</v>
@@ -2439,91 +2580,91 @@
         <v>6</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>431</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="E19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    </row>
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>264</v>
+      <c r="G20" s="5" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="E21" s="2" t="s">
         <v>11</v>
       </c>
@@ -2531,21 +2672,21 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>437</v>
+        <v>264</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>492</v>
+        <v>259</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>464</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
@@ -2554,67 +2695,67 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
         <v>516</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
-        <v>438</v>
-      </c>
       <c r="B25" s="2" t="s">
-        <v>493</v>
+        <v>513</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>462</v>
+        <v>514</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>263</v>
+        <v>365</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
@@ -2622,22 +2763,22 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>431</v>
+      <c r="G25" s="8" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -2646,18 +2787,18 @@
         <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>247</v>
+        <v>439</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>252</v>
+        <v>495</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>251</v>
+        <v>483</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>9</v>
@@ -2669,18 +2810,18 @@
         <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>255</v>
+        <v>428</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
@@ -2692,18 +2833,18 @@
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>126</v>
+        <v>251</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>128</v>
+        <v>249</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>9</v>
@@ -2715,21 +2856,21 @@
         <v>6</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>129</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
@@ -2738,21 +2879,21 @@
         <v>6</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>443</v>
+        <v>162</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>499</v>
+        <v>163</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>479</v>
+        <v>164</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>160</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -2761,21 +2902,21 @@
         <v>6</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>431</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>231</v>
+        <v>440</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>235</v>
+        <v>496</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>242</v>
+        <v>476</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>241</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>11</v>
@@ -2784,21 +2925,21 @@
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>226</v>
+        <v>428</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>354</v>
+        <v>229</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>358</v>
+        <v>233</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>359</v>
+        <v>240</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
@@ -2807,18 +2948,18 @@
         <v>6</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>357</v>
+        <v>224</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>454</v>
+        <v>352</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>509</v>
+        <v>356</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>466</v>
+        <v>357</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>30</v>
@@ -2830,18 +2971,18 @@
         <v>6</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>431</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>337</v>
+        <v>451</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>339</v>
+        <v>506</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -2853,18 +2994,18 @@
         <v>6</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>341</v>
+        <v>428</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>27</v>
+        <v>335</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>28</v>
+        <v>337</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>30</v>
@@ -2876,12 +3017,12 @@
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>33</v>
+        <v>339</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>28</v>
@@ -2898,15 +3039,15 @@
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G37" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="2" t="s">
@@ -2921,13 +3062,13 @@
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G38" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>322</v>
+        <v>166</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>28</v>
@@ -2944,15 +3085,15 @@
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G39" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="B40" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -2968,18 +3109,18 @@
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>334</v>
+        <v>452</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>333</v>
+        <v>28</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>332</v>
+        <v>29</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>30</v>
@@ -2990,19 +3131,19 @@
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="5" t="s">
+      <c r="G41" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A42" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>330</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A42" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
@@ -3013,19 +3154,19 @@
       <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>431</v>
+      <c r="G42" s="5" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>171</v>
+        <v>556</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>558</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>170</v>
+        <v>560</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
@@ -3037,18 +3178,18 @@
         <v>6</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>172</v>
+        <v>405</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>30</v>
@@ -3060,18 +3201,18 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>244</v>
+        <v>168</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>245</v>
+        <v>169</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>30</v>
@@ -3082,19 +3223,19 @@
       <c r="F45" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>246</v>
+      <c r="G45" s="5" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>34</v>
+        <v>534</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>35</v>
+        <v>537</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>36</v>
+        <v>535</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>30</v>
@@ -3106,18 +3247,18 @@
         <v>6</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>207</v>
+        <v>536</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>189</v>
+        <v>557</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>195</v>
+        <v>559</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>191</v>
+        <v>561</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>30</v>
@@ -3128,19 +3269,19 @@
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G47" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>38</v>
+        <v>454</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>37</v>
+        <v>508</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>39</v>
+        <v>465</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
@@ -3151,19 +3292,19 @@
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G48" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>331</v>
+        <v>242</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>329</v>
+        <v>243</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>30</v>
@@ -3174,19 +3315,19 @@
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>330</v>
+      <c r="G49" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>30</v>
@@ -3198,18 +3339,18 @@
         <v>6</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>528</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>30</v>
@@ -3220,19 +3361,19 @@
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>46</v>
+      <c r="G51" s="5" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>458</v>
+        <v>188</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>512</v>
+        <v>194</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>470</v>
+        <v>190</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
@@ -3244,18 +3385,18 @@
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>190</v>
+        <v>38</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>193</v>
+        <v>37</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>192</v>
+        <v>39</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
@@ -3266,19 +3407,19 @@
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G53" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>248</v>
+        <v>326</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>250</v>
+        <v>329</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>30</v>
@@ -3289,19 +3430,19 @@
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>255</v>
+      <c r="G54" s="5" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>254</v>
+        <v>531</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>250</v>
+        <v>533</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>249</v>
+        <v>532</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>30</v>
@@ -3313,18 +3454,18 @@
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>255</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>520</v>
+        <v>42</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>521</v>
+        <v>40</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>522</v>
+        <v>41</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
@@ -3336,18 +3477,18 @@
         <v>6</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>340</v>
+        <v>45</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>336</v>
+        <v>44</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
@@ -3358,19 +3499,19 @@
       <c r="F57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>341</v>
+      <c r="G57" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>30</v>
@@ -3382,21 +3523,21 @@
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>439</v>
+        <v>189</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>494</v>
+        <v>192</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>471</v>
+        <v>191</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>11</v>
@@ -3405,21 +3546,21 @@
         <v>6</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>431</v>
+        <v>193</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>118</v>
+        <v>248</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>119</v>
+        <v>247</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>11</v>
@@ -3427,22 +3568,22 @@
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>211</v>
+      <c r="G60" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>47</v>
+        <v>252</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>51</v>
+        <v>248</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>49</v>
+        <v>247</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>11</v>
@@ -3451,21 +3592,21 @@
         <v>6</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>48</v>
+        <v>517</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>53</v>
+        <v>518</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>50</v>
+        <v>519</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>11</v>
@@ -3473,22 +3614,22 @@
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G62" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>53</v>
+        <v>336</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>50</v>
+        <v>334</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>11</v>
@@ -3496,68 +3637,68 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>213</v>
+      <c r="G63" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>489</v>
+        <v>456</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>50</v>
+        <v>472</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A65" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A65" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>113</v>
+      <c r="G65" s="2" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>460</v>
+        <v>116</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>514</v>
+        <v>117</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>478</v>
+        <v>118</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>433</v>
+        <v>52</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -3565,22 +3706,22 @@
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>431</v>
+      <c r="G66" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -3589,21 +3730,21 @@
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>315</v>
+        <v>48</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -3612,21 +3753,21 @@
         <v>6</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -3634,22 +3775,22 @@
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G69" s="5" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>426</v>
+        <v>486</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -3657,22 +3798,22 @@
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G70" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>58</v>
+        <v>110</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -3680,68 +3821,68 @@
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>60</v>
+      <c r="G71" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>120</v>
+        <v>457</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>121</v>
+        <v>511</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>122</v>
+        <v>475</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A73" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A73" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>373</v>
+      <c r="G73" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>346</v>
+        <v>139</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>345</v>
+        <v>136</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3750,21 +3891,21 @@
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -3773,21 +3914,21 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>61</v>
+        <v>422</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>423</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3795,22 +3936,22 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>215</v>
+      <c r="G76" s="5" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>230</v>
+        <v>57</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -3819,21 +3960,21 @@
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>95</v>
+        <v>9</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -3841,22 +3982,22 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G78" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>473</v>
+        <v>120</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>472</v>
+        <v>121</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>432</v>
+        <v>373</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -3864,22 +4005,22 @@
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G79" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>66</v>
+        <v>300</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>67</v>
+        <v>344</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>68</v>
+        <v>343</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -3887,22 +4028,22 @@
       <c r="F80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="5" t="s">
-        <v>216</v>
+      <c r="G80" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>233</v>
+        <v>63</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -3911,21 +4052,21 @@
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>226</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>515</v>
+        <v>91</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>233</v>
+        <v>63</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>237</v>
+        <v>61</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>260</v>
+        <v>64</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -3934,21 +4075,21 @@
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>431</v>
+        <v>213</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>435</v>
+        <v>228</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>490</v>
+        <v>63</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>477</v>
+        <v>61</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>260</v>
+        <v>64</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -3957,67 +4098,67 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A84" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A85" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="2" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A84" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A86" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="B86" s="2" t="s">
-        <v>415</v>
+        <v>470</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>260</v>
+        <v>429</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -4025,22 +4166,22 @@
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G86" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>444</v>
+        <v>66</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>500</v>
+        <v>67</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>476</v>
+        <v>68</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -4048,22 +4189,22 @@
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>431</v>
+      <c r="G87" s="5" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>445</v>
+        <v>225</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>501</v>
+        <v>231</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>488</v>
+        <v>235</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -4072,21 +4213,21 @@
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>431</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>446</v>
+        <v>512</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>502</v>
+        <v>231</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>481</v>
+        <v>235</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -4095,21 +4236,21 @@
         <v>6</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>447</v>
+        <v>563</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>503</v>
+        <v>564</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -4117,22 +4258,22 @@
       <c r="F90" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G90" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>101</v>
+        <v>432</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>102</v>
+        <v>487</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>103</v>
+        <v>474</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -4140,22 +4281,22 @@
       <c r="F91" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G91" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>374</v>
+        <v>172</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>372</v>
+        <v>173</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -4163,22 +4304,22 @@
       <c r="F92" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G92" s="5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G92" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>409</v>
+        <v>177</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>413</v>
+        <v>178</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>412</v>
+        <v>179</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -4186,22 +4327,22 @@
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>390</v>
+      <c r="G93" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="D94" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -4210,18 +4351,18 @@
         <v>6</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>135</v>
+        <v>441</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>141</v>
+        <v>497</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>138</v>
+        <v>473</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>9</v>
@@ -4233,18 +4374,18 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>143</v>
+        <v>428</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>316</v>
+        <v>442</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>141</v>
+        <v>498</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>138</v>
+        <v>485</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>9</v>
@@ -4256,21 +4397,21 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>305</v>
+        <v>428</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>324</v>
+        <v>443</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>326</v>
+        <v>499</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>327</v>
+        <v>478</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -4279,21 +4420,21 @@
         <v>6</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>325</v>
+        <v>428</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>276</v>
+        <v>444</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>277</v>
+        <v>500</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>279</v>
+        <v>466</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -4302,21 +4443,21 @@
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>277</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -4324,22 +4465,22 @@
       <c r="F99" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G99" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>482</v>
+        <v>372</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>277</v>
+        <v>369</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>279</v>
+        <v>370</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>260</v>
+        <v>9</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -4347,22 +4488,22 @@
       <c r="F100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G100" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>491</v>
+        <v>410</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>480</v>
+        <v>409</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -4370,22 +4511,22 @@
       <c r="F101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G101" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>184</v>
+        <v>134</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -4393,22 +4534,22 @@
       <c r="F102" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G102" s="5" t="s">
-        <v>186</v>
+      <c r="G102" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>418</v>
+        <v>314</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>419</v>
+        <v>140</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>420</v>
+        <v>137</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>421</v>
+        <v>9</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -4417,21 +4558,21 @@
         <v>6</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>391</v>
+        <v>303</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>125</v>
+        <v>322</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>123</v>
+        <v>324</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>124</v>
+        <v>325</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -4440,21 +4581,21 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>129</v>
+        <v>323</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>123</v>
+        <v>275</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -4463,21 +4604,21 @@
         <v>6</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>226</v>
+        <v>276</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>448</v>
+        <v>302</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>504</v>
+        <v>275</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>483</v>
+        <v>277</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -4486,21 +4627,21 @@
         <v>6</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>368</v>
+        <v>479</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>370</v>
+        <v>277</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -4508,22 +4649,22 @@
       <c r="F107" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G107" s="5" t="s">
-        <v>373</v>
+      <c r="G107" s="2" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
-        <v>355</v>
+        <v>541</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>360</v>
+        <v>275</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>363</v>
+        <v>277</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>362</v>
+        <v>258</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -4532,21 +4673,21 @@
         <v>6</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>98</v>
+        <v>433</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>99</v>
+        <v>488</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>100</v>
+        <v>477</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -4554,45 +4695,45 @@
       <c r="F109" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G109" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G109" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>449</v>
+        <v>555</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>484</v>
+        <v>547</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>11</v>
+        <v>548</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G110" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>506</v>
+        <v>182</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>487</v>
+        <v>184</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -4600,22 +4741,22 @@
       <c r="F111" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G111" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G111" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>70</v>
+        <v>415</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>69</v>
+        <v>416</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>71</v>
+        <v>417</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>30</v>
+        <v>418</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -4623,19 +4764,19 @@
       <c r="F112" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G112" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G112" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>451</v>
+        <v>124</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>507</v>
+        <v>122</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>474</v>
+        <v>123</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>9</v>
@@ -4647,758 +4788,755 @@
         <v>6</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A115" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A116" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A117" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A118" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G118" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A119" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A120" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A121" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A122" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A123" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B123" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C123" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D114" s="2" t="s">
+      <c r="D123" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G114" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A115" s="2" t="s">
+      <c r="E123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A124" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B124" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C115" s="2" t="s">
+      <c r="C124" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D115" s="2" t="s">
+      <c r="D124" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G115" s="2" t="s">
+      <c r="E124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A116" s="2" t="s">
+    <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A125" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="D125" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C116" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D116" s="2" t="s">
+    </row>
+    <row r="126" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A126" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D126" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A117" s="2" t="s">
+      <c r="E126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A127" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A128" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A129" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A130" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A131" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H131" s="2"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A132" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A133" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A134" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A135" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A136" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A137" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A138" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A139" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A140" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A141" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A142" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A143" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A144" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="B117" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A118" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G118" s="5" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A119" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G119" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A120" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A121" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H121" s="2"/>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A122" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A123" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A124" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A125" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A126" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A127" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A128" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A129" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A130" s="2" t="s">
+      <c r="B144" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="C144" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G130" s="2" t="s">
+      <c r="D144" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A131" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B131" s="2" t="s">
+      <c r="E144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C145" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="C131" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A132" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G132" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A133" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A134" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A135" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G135" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A136" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A137" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A138" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A139" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A140" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A141" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A142" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G142" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A143" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A144" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A145" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="2" t="s">
+      <c r="D145" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>351</v>
+        <v>530</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>97</v>
+        <v>526</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -5406,22 +5544,22 @@
       <c r="F146" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G146" s="2" t="s">
-        <v>352</v>
+      <c r="G146" s="5" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
-        <v>350</v>
+        <v>143</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>97</v>
+        <v>145</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -5430,21 +5568,21 @@
         <v>6</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.15">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
-        <v>525</v>
+        <v>419</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>97</v>
+        <v>420</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>421</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -5452,22 +5590,22 @@
       <c r="F148" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G148" s="2" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G148" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -5476,21 +5614,21 @@
         <v>6</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.15">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>157</v>
+        <v>88</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>158</v>
+        <v>89</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -5498,19 +5636,19 @@
       <c r="F150" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G150" s="2" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G150" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>84</v>
+        <v>294</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>9</v>
@@ -5521,19 +5659,19 @@
       <c r="F151" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G151" s="5" t="s">
-        <v>221</v>
+      <c r="G151" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>284</v>
+        <v>351</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>9</v>
@@ -5545,18 +5683,18 @@
         <v>6</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>453</v>
+        <v>568</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>9</v>
@@ -5568,44 +5706,44 @@
         <v>6</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B154" s="6" t="s">
-        <v>150</v>
+        <v>79</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>149</v>
+        <v>83</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G154" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G154" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>223</v>
+        <v>158</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -5614,21 +5752,21 @@
         <v>6</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>225</v>
+        <v>159</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>136</v>
+        <v>288</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -5637,21 +5775,21 @@
         <v>6</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -5659,102 +5797,521 @@
       <c r="F157" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G157" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G160" s="5"/>
-    </row>
-    <row r="161" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G161" s="5"/>
-    </row>
-    <row r="165" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G157" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A158" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G158" s="5" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A159" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A160" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A161" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A162" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A163" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A164" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
         <v>523</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A166" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C165" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D165" s="2" t="s">
+      <c r="D166" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E165" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E166" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A167" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A168" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
-        <v>526</v>
+        <v>84</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A170" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A171" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A172" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A173" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B173" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A174" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A175" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B176" s="9"/>
+      <c r="C176" s="9"/>
+      <c r="D176" s="9"/>
+      <c r="E176" s="9"/>
+      <c r="F176" s="9"/>
+    </row>
+    <row r="178" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G178" s="5"/>
+    </row>
+    <row r="180" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A181" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A187" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C169" s="2" t="s">
+      <c r="C187" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D169" s="2" t="s">
+      <c r="D187" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E169" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>403</v>
+      <c r="E187" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H157">
-    <sortCondition ref="A157"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H175">
+    <sortCondition ref="A175"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G15" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G37" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G78" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G91" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G109" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G65" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G132" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G135" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G16" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G38" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G85" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G99" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G118" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G71" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G147" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G150" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
-    <hyperlink ref="G8" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G46" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G48" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G50" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G63" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G80" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G112" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G114" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G151" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G23" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G116" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G141" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G41" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G49" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G147" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G107" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G92" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G73" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G118" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G142" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
-    <hyperlink ref="G133" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
-    <hyperlink ref="G19" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
-    <hyperlink ref="G165" r:id="rId32" xr:uid="{91B34FFD-CCB4-C046-8807-0D6025131D83}"/>
-    <hyperlink ref="G56" r:id="rId33" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
+    <hyperlink ref="G9" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
+    <hyperlink ref="G50" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G53" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G56" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G69" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G87" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G121" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G123" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G169" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G24" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G125" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G157" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G42" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G54" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G163" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G116" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G100" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G79" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G127" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G158" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G148" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
+    <hyperlink ref="G20" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
+    <hyperlink ref="G62" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
+    <hyperlink ref="G168" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
+    <hyperlink ref="G51" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
+    <hyperlink ref="G146" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
+    <hyperlink ref="G84" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
+    <hyperlink ref="G46" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
+    <hyperlink ref="G7" r:id="rId38" xr:uid="{AD3618A6-5FE8-B940-9FEF-9FF5D1F662CA}"/>
+    <hyperlink ref="G142" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
+    <hyperlink ref="G47" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
+    <hyperlink ref="G43" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
+    <hyperlink ref="G110" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
+    <hyperlink ref="G90" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5773,102 +6330,102 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1720" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB114131-E4C6-454A-B99C-392F61D00AA9}"/>
+  <xr:revisionPtr revIDLastSave="1721" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A546BC3-297E-A045-897D-D1EE3925B9A7}"/>
   <bookViews>
     <workbookView xWindow="-4380" yWindow="-21100" windowWidth="22080" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -1737,9 +1737,6 @@
     <t>https://thekeep.eiu.edu/theses/2433/</t>
   </si>
   <si>
-    <t>SAFO-X</t>
-  </si>
-  <si>
     <t>DOI 10.1007/s10592-017-1027-6.</t>
   </si>
   <si>
@@ -1747,6 +1744,9 @@
   </si>
   <si>
     <t>ONCL-6</t>
+  </si>
+  <si>
+    <t>SAFO-8</t>
   </si>
 </sst>
 </file>
@@ -5115,7 +5115,7 @@
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>285</v>
@@ -5614,7 +5614,7 @@
         <v>6</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -5688,7 +5688,7 @@
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>88</v>
@@ -6242,7 +6242,7 @@
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A187" s="2" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>82</v>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1721" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A546BC3-297E-A045-897D-D1EE3925B9A7}"/>
+  <xr:revisionPtr revIDLastSave="1757" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E2BE3C-8107-5447-878C-7221DD6E8C7F}"/>
   <bookViews>
-    <workbookView xWindow="-4380" yWindow="-21100" windowWidth="22080" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4380" yWindow="-21100" windowWidth="36500" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="569">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1209,15 +1209,6 @@
     <t>https://doi.org/10.11646/zootaxa.5154.5.1</t>
   </si>
   <si>
-    <t>https://doi.org/10.1093/evolut/qpaf249</t>
-  </si>
-  <si>
-    <t>https://scispace.com/pdf/population-genetic-structure-and-temporal-stability-at-the-2kj9rf8mqa.pdf</t>
-  </si>
-  <si>
-    <t>https://scholarsjunction.msstate.edu/td/6714/</t>
-  </si>
-  <si>
     <t>DOI: 10.1002/aqc.3510</t>
   </si>
   <si>
@@ -1227,33 +1218,15 @@
     <t>DOI 10.1007/s10592-016-0845-2</t>
   </si>
   <si>
-    <t>https://scholarworks.uni.edu/etd/1204/</t>
-  </si>
-  <si>
-    <t>DOI: 10.1111/eva.12990</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1186/s12862-023-02191-1</t>
   </si>
   <si>
-    <t>DOI: 10.1111/eva.12454</t>
-  </si>
-  <si>
     <t>DOI: 10.1080/00028487.2017.1285351</t>
   </si>
   <si>
     <t>DOI: 10.1002/ece3.5237</t>
   </si>
   <si>
-    <t xml:space="preserve"> https://doi.org/10.1002/eap.2147</t>
-  </si>
-  <si>
-    <t>doi: 10.1111/mec.17558</t>
-  </si>
-  <si>
-    <t>DOI: 10.1111/jfb.15999</t>
-  </si>
-  <si>
     <t>https://doi.org/10.3354/esr00986</t>
   </si>
   <si>
@@ -1644,9 +1617,6 @@
     <t>ETHRAD-1</t>
   </si>
   <si>
-    <t>ETHEOSTOMA RADIOSUM</t>
-  </si>
-  <si>
     <t>https://lair.etamu.edu/etd/1074/</t>
   </si>
   <si>
@@ -1747,6 +1717,33 @@
   </si>
   <si>
     <t>SAFO-8</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10980-025-02163-4</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/eff.12769</t>
+  </si>
+  <si>
+    <t>ETSA-3</t>
+  </si>
+  <si>
+    <t>Etheostoma radiosum</t>
+  </si>
+  <si>
+    <t>Etheostoma sagitta spilotum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roanake logperch </t>
+  </si>
+  <si>
+    <t>doi: 10.1111/eff.12177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roanake logperch V2 </t>
+  </si>
+  <si>
+    <t>https://escholarship.org/content/qt9z7718m5/qt9z7718m5.pdf</t>
   </si>
 </sst>
 </file>
@@ -1816,7 +1813,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1841,6 +1838,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1857,6 +1857,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2332,7 +2336,7 @@
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>234</v>
@@ -2350,7 +2354,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>553</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -2401,7 +2405,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -2419,7 +2423,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.15">
@@ -2430,7 +2434,7 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>25</v>
@@ -2516,13 +2520,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>9</v>
@@ -2534,7 +2538,7 @@
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
@@ -2585,13 +2589,13 @@
     </row>
     <row r="18" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>9</v>
@@ -2603,7 +2607,7 @@
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
@@ -2631,7 +2635,7 @@
     </row>
     <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>363</v>
@@ -2700,13 +2704,13 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>261</v>
@@ -2718,7 +2722,7 @@
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -2746,13 +2750,13 @@
     </row>
     <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>365</v>
@@ -2769,13 +2773,13 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>261</v>
@@ -2787,18 +2791,18 @@
         <v>6</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>9</v>
@@ -2810,7 +2814,7 @@
         <v>6</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
@@ -2907,13 +2911,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>9</v>
@@ -2925,7 +2929,7 @@
         <v>6</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
@@ -2976,13 +2980,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>30</v>
@@ -2994,7 +2998,7 @@
         <v>6</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
@@ -3114,7 +3118,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>28</v>
@@ -3132,7 +3136,7 @@
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -3160,13 +3164,13 @@
     </row>
     <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>556</v>
+        <v>546</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
@@ -3178,18 +3182,18 @@
         <v>6</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>30</v>
@@ -3201,7 +3205,7 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -3229,13 +3233,13 @@
     </row>
     <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>30</v>
@@ -3247,18 +3251,18 @@
         <v>6</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>30</v>
@@ -3270,18 +3274,18 @@
         <v>6</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
@@ -3293,7 +3297,7 @@
         <v>6</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.15">
@@ -3344,7 +3348,7 @@
     </row>
     <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>35</v>
@@ -3362,7 +3366,7 @@
         <v>6</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
@@ -3436,13 +3440,13 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>30</v>
@@ -3454,7 +3458,7 @@
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
@@ -3503,61 +3507,61 @@
         <v>46</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>455</v>
+        <v>518</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>509</v>
+        <v>43</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>467</v>
+        <v>564</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>428</v>
+      <c r="G58" s="10" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>189</v>
+        <v>562</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>191</v>
+        <v>564</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="2" t="s">
-        <v>193</v>
+      <c r="G59" s="4" t="s">
+        <v>561</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>246</v>
+        <v>446</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>248</v>
+        <v>500</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>247</v>
+        <v>458</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>30</v>
@@ -3569,18 +3573,18 @@
         <v>6</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>253</v>
+        <v>419</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>30</v>
@@ -3592,18 +3596,18 @@
         <v>6</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>517</v>
+        <v>246</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>518</v>
+        <v>248</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>519</v>
+        <v>247</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>30</v>
@@ -3614,19 +3618,19 @@
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G62" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>338</v>
+        <v>252</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>334</v>
+        <v>247</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>30</v>
@@ -3638,18 +3642,18 @@
         <v>6</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>456</v>
+        <v>508</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>30</v>
@@ -3660,22 +3664,22 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G64" s="5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>491</v>
+        <v>336</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>468</v>
+        <v>334</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>11</v>
@@ -3684,21 +3688,21 @@
         <v>6</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>428</v>
+        <v>339</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>116</v>
+        <v>447</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>118</v>
+        <v>463</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>11</v>
@@ -3706,19 +3710,19 @@
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="4" t="s">
-        <v>209</v>
+      <c r="G66" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>47</v>
+        <v>427</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>51</v>
+        <v>482</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>49</v>
+        <v>459</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>52</v>
@@ -3730,18 +3734,18 @@
         <v>6</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>210</v>
+        <v>419</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>52</v>
@@ -3752,19 +3756,19 @@
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G68" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>52</v>
@@ -3775,16 +3779,16 @@
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="5" t="s">
-        <v>211</v>
+      <c r="G69" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>486</v>
+        <v>48</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>492</v>
+        <v>53</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>50</v>
@@ -3799,21 +3803,21 @@
         <v>6</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>428</v>
+        <v>210</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -3822,21 +3826,21 @@
         <v>6</v>
       </c>
       <c r="G71" s="5" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>511</v>
+        <v>483</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>475</v>
+        <v>50</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>430</v>
+        <v>52</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -3845,21 +3849,21 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -3867,22 +3871,22 @@
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>142</v>
+      <c r="G73" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>313</v>
+        <v>448</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>139</v>
+        <v>502</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>136</v>
+        <v>466</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3891,18 +3895,18 @@
         <v>6</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>303</v>
+        <v>419</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>54</v>
+        <v>139</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>9</v>
@@ -3914,18 +3918,18 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>424</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>423</v>
+        <v>313</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>9</v>
@@ -3936,19 +3940,19 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="5" t="s">
-        <v>395</v>
+      <c r="G76" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>9</v>
@@ -3960,18 +3964,18 @@
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>121</v>
+        <v>413</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>414</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
@@ -3982,22 +3986,22 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G78" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>383</v>
+        <v>57</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -4005,22 +4009,22 @@
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="5" t="s">
-        <v>371</v>
+      <c r="G79" s="2" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>300</v>
+        <v>119</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>344</v>
+        <v>120</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>343</v>
+        <v>121</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -4029,21 +4033,21 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>62</v>
+        <v>383</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>64</v>
+        <v>373</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -4051,22 +4055,22 @@
       <c r="F81" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G81" s="2" t="s">
-        <v>65</v>
+      <c r="G81" s="5" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>91</v>
+        <v>300</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>61</v>
+        <v>343</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -4075,12 +4079,12 @@
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>213</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>228</v>
+        <v>62</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>63</v>
@@ -4098,12 +4102,12 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>538</v>
+        <v>91</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>63</v>
@@ -4120,22 +4124,22 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G84" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>92</v>
+        <v>228</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -4143,22 +4147,22 @@
       <c r="F85" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>96</v>
+      <c r="G85" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>431</v>
+        <v>528</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>470</v>
+        <v>63</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>469</v>
+        <v>61</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>429</v>
+        <v>64</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -4166,22 +4170,22 @@
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>428</v>
+      <c r="G86" s="5" t="s">
+        <v>529</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>68</v>
+        <v>94</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -4190,87 +4194,87 @@
         <v>6</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>214</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A89" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A90" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B90" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C88" s="2" t="s">
+      <c r="C90" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="D88" s="2" t="s">
+      <c r="D90" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G88" s="2" t="s">
+      <c r="E90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="2" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A89" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>432</v>
+        <v>503</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>487</v>
+        <v>231</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>474</v>
+        <v>235</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>258</v>
@@ -4282,21 +4286,21 @@
         <v>6</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>172</v>
+        <v>553</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>174</v>
+        <v>554</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>465</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>176</v>
+        <v>258</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -4304,22 +4308,22 @@
       <c r="F92" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>175</v>
+      <c r="G92" s="5" t="s">
+        <v>555</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>177</v>
+        <v>423</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>178</v>
+        <v>478</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>179</v>
+        <v>465</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -4328,21 +4332,21 @@
         <v>6</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>407</v>
+        <v>172</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>413</v>
+        <v>173</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>258</v>
+        <v>176</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -4350,22 +4354,22 @@
       <c r="F94" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G94" s="5" t="s">
-        <v>387</v>
+      <c r="G94" s="2" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>441</v>
+        <v>177</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>497</v>
+        <v>178</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>473</v>
+        <v>179</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -4374,21 +4378,21 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>442</v>
+        <v>398</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>498</v>
+        <v>403</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>485</v>
+        <v>404</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -4396,19 +4400,19 @@
       <c r="F96" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>428</v>
+      <c r="G96" s="5" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>9</v>
@@ -4420,18 +4424,18 @@
         <v>6</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>9</v>
@@ -4443,18 +4447,18 @@
         <v>6</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>101</v>
+        <v>434</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>102</v>
+        <v>490</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>103</v>
+        <v>469</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>9</v>
@@ -4465,19 +4469,19 @@
       <c r="F99" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G99" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G99" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>372</v>
+        <v>435</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>369</v>
+        <v>491</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>370</v>
+        <v>457</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>9</v>
@@ -4488,22 +4492,22 @@
       <c r="F100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="5" t="s">
-        <v>371</v>
+      <c r="G100" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>406</v>
+        <v>101</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>410</v>
+        <v>102</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>409</v>
+        <v>103</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -4512,18 +4516,18 @@
         <v>6</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>134</v>
+        <v>372</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>140</v>
+        <v>369</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>137</v>
+        <v>370</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>9</v>
@@ -4534,22 +4538,22 @@
       <c r="F102" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G102" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>314</v>
+        <v>397</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>140</v>
+        <v>401</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>137</v>
+        <v>400</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -4557,22 +4561,22 @@
       <c r="F103" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>303</v>
+      <c r="G103" s="5" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>322</v>
+        <v>134</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>324</v>
+        <v>140</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>325</v>
+        <v>137</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -4581,21 +4585,21 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>323</v>
+        <v>142</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>274</v>
+        <v>314</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -4604,18 +4608,18 @@
         <v>6</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>275</v>
+        <v>324</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>258</v>
@@ -4627,12 +4631,12 @@
         <v>6</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>479</v>
+        <v>274</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>275</v>
@@ -4650,12 +4654,12 @@
         <v>6</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>428</v>
+        <v>276</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
-        <v>541</v>
+        <v>302</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>275</v>
@@ -4673,18 +4677,18 @@
         <v>6</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>542</v>
+        <v>303</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>488</v>
+        <v>275</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>477</v>
+        <v>277</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>258</v>
@@ -4696,113 +4700,113 @@
         <v>6</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>488</v>
+        <v>275</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>547</v>
+        <v>277</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>258</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>548</v>
+        <v>11</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G110" s="5" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G110" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A112" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A113" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B111" s="6" t="s">
+      <c r="B113" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C111" s="2" t="s">
+      <c r="C113" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="D113" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G111" s="5" t="s">
+      <c r="E113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G113" s="5" t="s">
         <v>185</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A112" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A113" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D113" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>226</v>
+        <v>406</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>122</v>
+        <v>407</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>123</v>
+        <v>408</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>9</v>
+        <v>409</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -4811,18 +4815,18 @@
         <v>6</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>224</v>
+        <v>388</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>445</v>
+        <v>124</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>501</v>
+        <v>122</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>480</v>
+        <v>123</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>9</v>
@@ -4834,18 +4838,18 @@
         <v>6</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>366</v>
+        <v>226</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>367</v>
+        <v>122</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>368</v>
+        <v>123</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>9</v>
@@ -4856,22 +4860,22 @@
       <c r="F116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G116" s="5" t="s">
-        <v>371</v>
+      <c r="G116" s="2" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>353</v>
+        <v>436</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>358</v>
+        <v>492</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>361</v>
+        <v>471</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>360</v>
+        <v>9</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -4880,18 +4884,18 @@
         <v>6</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>359</v>
+        <v>419</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>98</v>
+        <v>366</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>99</v>
+        <v>367</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>100</v>
+        <v>368</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>9</v>
@@ -4903,21 +4907,21 @@
         <v>6</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>104</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>446</v>
+        <v>353</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>502</v>
+        <v>358</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>481</v>
+        <v>361</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>9</v>
+        <v>360</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -4926,18 +4930,18 @@
         <v>6</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>428</v>
+        <v>359</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>447</v>
+        <v>98</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>503</v>
+        <v>99</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>484</v>
+        <v>100</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>9</v>
@@ -4948,22 +4952,22 @@
       <c r="F120" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G120" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G120" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>70</v>
+        <v>437</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>69</v>
+        <v>493</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>71</v>
+        <v>472</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -4971,19 +4975,19 @@
       <c r="F121" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G121" s="5" t="s">
-        <v>215</v>
+      <c r="G121" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>9</v>
@@ -4995,21 +4999,21 @@
         <v>6</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -5018,21 +5022,21 @@
         <v>6</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>108</v>
+        <v>439</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -5041,18 +5045,18 @@
         <v>6</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>106</v>
+        <v>419</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
-        <v>284</v>
+        <v>72</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>285</v>
+        <v>73</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>286</v>
+        <v>74</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>75</v>
@@ -5064,18 +5068,18 @@
         <v>6</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>287</v>
+        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>296</v>
+        <v>105</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>346</v>
+        <v>108</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>347</v>
+        <v>107</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>75</v>
@@ -5087,12 +5091,12 @@
         <v>6</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>295</v>
+        <v>106</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>381</v>
+        <v>284</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>285</v>
@@ -5110,18 +5114,18 @@
         <v>6</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.15">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="28" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>285</v>
+        <v>296</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>346</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>286</v>
+        <v>347</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>75</v>
@@ -5132,16 +5136,19 @@
       <c r="F128" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G128" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>129</v>
+        <v>381</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>130</v>
+        <v>285</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>132</v>
+        <v>286</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>75</v>
@@ -5152,19 +5159,19 @@
       <c r="F129" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G129" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="G129" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B130" s="6" t="s">
-        <v>342</v>
+        <v>558</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>341</v>
+        <v>286</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>75</v>
@@ -5175,19 +5182,19 @@
       <c r="F130" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G130" s="2" t="s">
-        <v>292</v>
+      <c r="G130" s="5" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>278</v>
+        <v>129</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>279</v>
+        <v>130</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>280</v>
+        <v>132</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>75</v>
@@ -5199,16 +5206,15 @@
         <v>6</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H131" s="2"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>426</v>
+        <v>340</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>342</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>341</v>
@@ -5223,21 +5229,21 @@
         <v>6</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>408</v>
+        <v>278</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>411</v>
+        <v>279</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>414</v>
+        <v>280</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>258</v>
+        <v>75</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -5245,22 +5251,23 @@
       <c r="F133" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G133" s="5" t="s">
-        <v>387</v>
-      </c>
+      <c r="G133" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H133" s="2"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>315</v>
+        <v>416</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>317</v>
+        <v>417</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>316</v>
+        <v>341</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>312</v>
+        <v>75</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -5269,21 +5276,21 @@
         <v>6</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>303</v>
+        <v>418</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>76</v>
+        <v>399</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>77</v>
+        <v>402</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>78</v>
+        <v>405</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -5291,22 +5298,22 @@
       <c r="F135" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G135" s="2" t="s">
-        <v>131</v>
+      <c r="G135" s="5" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>154</v>
+        <v>315</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>78</v>
+        <v>316</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -5315,12 +5322,12 @@
         <v>6</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>153</v>
+        <v>303</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
-        <v>187</v>
+        <v>76</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>77</v>
@@ -5338,12 +5345,12 @@
         <v>6</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>186</v>
+        <v>131</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
-        <v>543</v>
+        <v>154</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>77</v>
@@ -5361,21 +5368,21 @@
         <v>6</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>544</v>
+        <v>153</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>449</v>
+        <v>187</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>464</v>
+        <v>78</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -5384,21 +5391,21 @@
         <v>6</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>562</v>
+        <v>533</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>464</v>
+        <v>78</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -5406,19 +5413,19 @@
       <c r="F140" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G140" s="5" t="s">
-        <v>565</v>
+      <c r="G140" s="2" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
-        <v>227</v>
+        <v>440</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>232</v>
+        <v>496</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>236</v>
+        <v>455</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>9</v>
@@ -5430,21 +5437,21 @@
         <v>6</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>224</v>
+        <v>419</v>
       </c>
     </row>
     <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>552</v>
+        <v>496</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>554</v>
+        <v>455</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -5453,21 +5460,21 @@
         <v>6</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>199</v>
+        <v>9</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -5476,21 +5483,21 @@
         <v>6</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
-        <v>298</v>
+        <v>541</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>196</v>
+        <v>542</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>197</v>
+        <v>544</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>199</v>
+        <v>258</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -5498,45 +5505,45 @@
       <c r="F144" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G144" s="2" t="s">
-        <v>299</v>
+      <c r="G144" s="5" t="s">
+        <v>543</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="B145" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="C145" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D145" s="9" t="s">
+      <c r="D145" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="E145" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="9" t="s">
+      <c r="E145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>530</v>
+        <v>298</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>524</v>
+        <v>196</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>526</v>
+        <v>197</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>64</v>
+        <v>199</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -5544,45 +5551,45 @@
       <c r="F146" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G146" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G146" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>144</v>
+        <v>535</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
-        <v>419</v>
+        <v>521</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>421</v>
+        <v>515</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>517</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -5591,18 +5598,18 @@
         <v>6</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>398</v>
+        <v>516</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>9</v>
@@ -5613,19 +5620,19 @@
       <c r="F149" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G149" s="2" t="s">
-        <v>566</v>
+      <c r="G149" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>89</v>
+        <v>411</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>412</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>9</v>
@@ -5637,12 +5644,12 @@
         <v>6</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>201</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>294</v>
+        <v>87</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>88</v>
@@ -5660,12 +5667,12 @@
         <v>6</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>88</v>
@@ -5682,13 +5689,13 @@
       <c r="F152" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G152" s="2" t="s">
-        <v>293</v>
+      <c r="G152" s="5" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>567</v>
+        <v>294</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>88</v>
@@ -5706,44 +5713,44 @@
         <v>6</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>79</v>
+        <v>351</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>217</v>
+        <v>293</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>158</v>
+        <v>557</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -5752,12 +5759,12 @@
         <v>6</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>159</v>
+        <v>293</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>80</v>
@@ -5769,18 +5776,18 @@
         <v>75</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>290</v>
+        <v>158</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>80</v>
@@ -5797,16 +5804,16 @@
       <c r="F157" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G157" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G157" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
-        <v>384</v>
+        <v>288</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>385</v>
+        <v>80</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>83</v>
@@ -5820,19 +5827,19 @@
       <c r="F158" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G158" s="5" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G158" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
-        <v>81</v>
+        <v>290</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>75</v>
@@ -5843,19 +5850,19 @@
       <c r="F159" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G159" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G159" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
-        <v>151</v>
+        <v>384</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>75</v>
@@ -5866,13 +5873,13 @@
       <c r="F160" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G160" s="2" t="s">
-        <v>152</v>
+      <c r="G160" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
-        <v>345</v>
+        <v>81</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>82</v>
@@ -5890,12 +5897,12 @@
         <v>6</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>301</v>
+        <v>218</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
-        <v>349</v>
+        <v>151</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>82</v>
@@ -5913,12 +5920,12 @@
         <v>6</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>82</v>
@@ -5935,13 +5942,13 @@
       <c r="F163" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G163" s="5" t="s">
-        <v>297</v>
+      <c r="G163" s="2" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>522</v>
+        <v>349</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>82</v>
@@ -5959,12 +5966,12 @@
         <v>6</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.15">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>523</v>
+        <v>348</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>82</v>
@@ -5981,22 +5988,22 @@
       <c r="F165" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G165" s="2" t="s">
-        <v>401</v>
+      <c r="G165" s="5" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>155</v>
+        <v>513</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -6005,21 +6012,21 @@
         <v>6</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>153</v>
+        <v>218</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>202</v>
+        <v>514</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -6028,12 +6035,12 @@
         <v>6</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>520</v>
+        <v>155</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>156</v>
@@ -6050,59 +6057,59 @@
       <c r="F168" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G168" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G168" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A170" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A171" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B169" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F169" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A170" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B170" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F170" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G170" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A171" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>85</v>
@@ -6119,19 +6126,19 @@
       <c r="F171" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G171" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>149</v>
+        <v>282</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>9</v>
@@ -6142,19 +6149,19 @@
       <c r="F172" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G172" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G172" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C173" s="6" t="s">
-        <v>221</v>
+        <v>441</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>9</v>
@@ -6166,18 +6173,18 @@
         <v>6</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>9</v>
@@ -6188,19 +6195,19 @@
       <c r="F174" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G174" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G174" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>138</v>
+        <v>220</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>9</v>
@@ -6212,37 +6219,68 @@
         <v>6</v>
       </c>
       <c r="G175" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A176" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A177" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G177" s="2" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B176" s="9"/>
-      <c r="C176" s="9"/>
-      <c r="D176" s="9"/>
-      <c r="E176" s="9"/>
-      <c r="F176" s="9"/>
     </row>
     <row r="178" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G178" s="5"/>
     </row>
     <row r="180" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A181" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B181" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E181" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F181" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="181" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G181" s="10"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G182" s="4"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A187" s="2" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>82</v>
@@ -6260,58 +6298,60 @@
         <v>6</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H175">
-    <sortCondition ref="A175"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H177">
+    <sortCondition ref="A177"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G16" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
     <hyperlink ref="G38" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G85" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G99" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G118" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G71" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G147" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G150" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G87" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G101" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G120" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G73" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G149" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G152" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G9" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
     <hyperlink ref="G50" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
     <hyperlink ref="G53" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
     <hyperlink ref="G56" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G69" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G87" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G121" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G123" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G169" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G71" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G89" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G123" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G125" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G171" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G24" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G125" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G157" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G127" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G159" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
     <hyperlink ref="G42" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
     <hyperlink ref="G54" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G163" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G116" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G100" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G79" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G127" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G158" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
-    <hyperlink ref="G148" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
+    <hyperlink ref="G165" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G118" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G102" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G81" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G129" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G160" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G150" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
     <hyperlink ref="G20" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
-    <hyperlink ref="G62" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
-    <hyperlink ref="G168" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
+    <hyperlink ref="G64" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
+    <hyperlink ref="G170" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
     <hyperlink ref="G51" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
-    <hyperlink ref="G146" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
-    <hyperlink ref="G84" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
+    <hyperlink ref="G148" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
+    <hyperlink ref="G86" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
     <hyperlink ref="G46" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
     <hyperlink ref="G7" r:id="rId38" xr:uid="{AD3618A6-5FE8-B940-9FEF-9FF5D1F662CA}"/>
-    <hyperlink ref="G142" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
+    <hyperlink ref="G144" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
     <hyperlink ref="G47" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
     <hyperlink ref="G43" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
-    <hyperlink ref="G110" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
-    <hyperlink ref="G90" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
+    <hyperlink ref="G112" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
+    <hyperlink ref="G92" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
+    <hyperlink ref="G58" r:id="rId44" xr:uid="{3E4AD335-D90F-8E4F-99D9-B5A29F73491A}"/>
+    <hyperlink ref="G130" r:id="rId45" xr:uid="{5496842B-F19F-F64D-AE34-576CA41371CE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6320,125 +6360,50 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D2BF60-27FC-AE44-BE48-175A6AFC76C6}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>404</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="B2" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="7"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="7"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="7"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="7"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="7"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="7"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="7"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>405</v>
-      </c>
+      <c r="A21" s="7"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A4" r:id="rId1" xr:uid="{D9D17451-9130-AB4E-B96E-5E9D8890900A}"/>
-    <hyperlink ref="A5" r:id="rId2" xr:uid="{D7B39A72-5A83-8845-876E-755A6FE0F199}"/>
-    <hyperlink ref="A6" r:id="rId3" xr:uid="{5BB4B890-A333-7446-AB88-D2B3CC3685FD}"/>
-    <hyperlink ref="A7" r:id="rId4" xr:uid="{468A1DEE-C6C6-7C4C-A701-301937A047DF}"/>
-    <hyperlink ref="A9" r:id="rId5" xr:uid="{B095DED7-3261-3C4B-95BF-879B19908C6F}"/>
-    <hyperlink ref="A11" r:id="rId6" xr:uid="{AC321152-D02E-514C-81C1-6E9C3AE50660}"/>
-    <hyperlink ref="A13" r:id="rId7" xr:uid="{8EA87D1C-C36E-B44F-8CED-C439FBD142A9}"/>
-    <hyperlink ref="A21" r:id="rId8" xr:uid="{082A3BE1-8E40-C940-B27B-ED3626DC70EF}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1757" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48E2BE3C-8107-5447-878C-7221DD6E8C7F}"/>
+  <xr:revisionPtr revIDLastSave="1808" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C1B84E8-F1AF-E642-84AF-1E38FC6F4A26}"/>
   <bookViews>
-    <workbookView xWindow="-4380" yWindow="-21100" windowWidth="36500" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28720" windowHeight="16680" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1250" uniqueCount="569">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="579">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1473,9 +1473,6 @@
     <t>FUOL-3</t>
   </si>
   <si>
-    <t>Longear sunfish</t>
-  </si>
-  <si>
     <t>Largemouth Bass</t>
   </si>
   <si>
@@ -1744,6 +1741,39 @@
   </si>
   <si>
     <t>https://escholarship.org/content/qt9z7718m5/qt9z7718m5.pdf</t>
+  </si>
+  <si>
+    <t>Lepomis cyanellus</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/j.1095-8312.2012.01973.x</t>
+  </si>
+  <si>
+    <t>Cyprinella venusta</t>
+  </si>
+  <si>
+    <t>Green Sunfish</t>
+  </si>
+  <si>
+    <t>Blacktail Shiner</t>
+  </si>
+  <si>
+    <t>CAAN-3</t>
+  </si>
+  <si>
+    <t>CYVE-1</t>
+  </si>
+  <si>
+    <t>CYLU-2</t>
+  </si>
+  <si>
+    <t>LEME-3</t>
+  </si>
+  <si>
+    <t>LECY-1</t>
+  </si>
+  <si>
+    <t>LEME-2</t>
   </si>
 </sst>
 </file>
@@ -1813,7 +1843,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1840,6 +1870,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2180,7 +2213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H187"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -2336,7 +2369,7 @@
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>234</v>
@@ -2354,7 +2387,7 @@
         <v>6</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
@@ -2426,41 +2459,41 @@
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>114</v>
+        <v>573</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>530</v>
+        <v>86</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>206</v>
+      <c r="G11" s="5" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
-        <v>309</v>
+        <v>114</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>311</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>310</v>
+        <v>529</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>312</v>
+        <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>11</v>
@@ -2469,21 +2502,21 @@
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>303</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
-        <v>374</v>
+        <v>309</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>376</v>
+        <v>311</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>379</v>
+        <v>310</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
@@ -2492,18 +2525,18 @@
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>380</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
@@ -2520,16 +2553,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>428</v>
+        <v>375</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>484</v>
+        <v>377</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>473</v>
+        <v>378</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>11</v>
@@ -2538,41 +2571,41 @@
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>419</v>
+        <v>380</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A17" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>25</v>
@@ -2583,22 +2616,22 @@
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>269</v>
+      <c r="G17" s="3" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>451</v>
+        <v>266</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>267</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>11</v>
@@ -2607,35 +2640,35 @@
         <v>6</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>419</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>363</v>
@@ -2652,36 +2685,36 @@
       <c r="F20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>389</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>259</v>
@@ -2699,18 +2732,18 @@
         <v>6</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>425</v>
+        <v>264</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>480</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>452</v>
+        <v>263</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>261</v>
@@ -2722,18 +2755,18 @@
         <v>6</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
-        <v>270</v>
+        <v>425</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>271</v>
+        <v>479</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>272</v>
+        <v>452</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>261</v>
@@ -2744,68 +2777,68 @@
       <c r="F24" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="B25" s="2" t="s">
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="E26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>389</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A26" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>11</v>
@@ -2819,13 +2852,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>245</v>
+        <v>430</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>250</v>
+        <v>485</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>249</v>
+        <v>474</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>9</v>
@@ -2837,12 +2870,12 @@
         <v>6</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>253</v>
+        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>250</v>
@@ -2865,13 +2898,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
-        <v>125</v>
+        <v>251</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>250</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>9</v>
@@ -2883,21 +2916,21 @@
         <v>6</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>128</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -2906,44 +2939,44 @@
         <v>6</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>431</v>
+        <v>575</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>487</v>
+        <v>126</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>467</v>
+        <v>127</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>419</v>
+      <c r="G32" s="11" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>229</v>
+        <v>162</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>233</v>
+        <v>163</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>240</v>
+        <v>164</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>239</v>
+        <v>160</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
@@ -2952,44 +2985,44 @@
         <v>6</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>352</v>
+        <v>574</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>356</v>
+        <v>572</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>357</v>
+        <v>570</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>355</v>
+      <c r="G34" s="5" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
@@ -3003,16 +3036,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>335</v>
+        <v>229</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>337</v>
+        <v>233</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>333</v>
+        <v>240</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -3021,18 +3054,18 @@
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>339</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>27</v>
+        <v>352</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>28</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>29</v>
+        <v>357</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>30</v>
@@ -3044,18 +3077,18 @@
         <v>6</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>33</v>
+        <v>355</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>31</v>
+        <v>442</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>28</v>
+        <v>496</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>29</v>
+        <v>454</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>30</v>
@@ -3066,19 +3099,19 @@
       <c r="F38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G38" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>28</v>
+        <v>335</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>30</v>
@@ -3089,15 +3122,15 @@
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G39" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -3113,12 +3146,12 @@
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>321</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>443</v>
+        <v>31</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>28</v>
@@ -3135,19 +3168,19 @@
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>419</v>
+      <c r="G41" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>331</v>
+        <v>166</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>330</v>
+        <v>29</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
@@ -3159,18 +3192,18 @@
         <v>6</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>548</v>
+        <v>320</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>550</v>
+        <v>29</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
@@ -3181,19 +3214,19 @@
       <c r="F43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G43" s="5" t="s">
-        <v>396</v>
+      <c r="G43" s="2" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>498</v>
+        <v>28</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>449</v>
+        <v>29</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>30</v>
@@ -3210,13 +3243,13 @@
     </row>
     <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>170</v>
+        <v>332</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>331</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>169</v>
+        <v>330</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>30</v>
@@ -3228,18 +3261,18 @@
         <v>6</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>171</v>
+        <v>328</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>30</v>
@@ -3251,18 +3284,18 @@
         <v>6</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>526</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>547</v>
+        <v>444</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>549</v>
+        <v>497</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>551</v>
+        <v>449</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>30</v>
@@ -3273,19 +3306,19 @@
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G47" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>499</v>
+        <v>168</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>456</v>
+        <v>169</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
@@ -3296,19 +3329,19 @@
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G48" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>241</v>
+        <v>524</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>242</v>
+        <v>526</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>243</v>
+        <v>562</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>30</v>
@@ -3319,19 +3352,19 @@
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>244</v>
+      <c r="G49" s="5" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>34</v>
+        <v>546</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>35</v>
+        <v>548</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>36</v>
+        <v>550</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>30</v>
@@ -3343,18 +3376,18 @@
         <v>6</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>519</v>
+        <v>445</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>35</v>
+        <v>498</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>36</v>
+        <v>456</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>30</v>
@@ -3365,19 +3398,19 @@
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="5" t="s">
-        <v>520</v>
+      <c r="G51" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>188</v>
+        <v>241</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>194</v>
+        <v>242</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>190</v>
+        <v>243</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
@@ -3389,18 +3422,18 @@
         <v>6</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
@@ -3412,18 +3445,18 @@
         <v>6</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>326</v>
+        <v>518</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>329</v>
+        <v>35</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>327</v>
+        <v>36</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>30</v>
@@ -3435,18 +3468,18 @@
         <v>6</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>328</v>
+        <v>519</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>522</v>
+        <v>188</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>524</v>
+        <v>194</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>523</v>
+        <v>190</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>30</v>
@@ -3458,18 +3491,18 @@
         <v>6</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>390</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
@@ -3481,18 +3514,18 @@
         <v>6</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>45</v>
+        <v>326</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>43</v>
+        <v>329</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>44</v>
+        <v>327</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
@@ -3503,65 +3536,65 @@
       <c r="F57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G57" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.15">
+      <c r="G57" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>43</v>
+        <v>523</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>564</v>
+        <v>522</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="10" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G58" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>562</v>
+        <v>42</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>564</v>
+        <v>41</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>561</v>
+      <c r="G59" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>446</v>
+        <v>45</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>500</v>
+        <v>43</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>458</v>
+        <v>44</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>30</v>
@@ -3572,65 +3605,65 @@
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G60" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>189</v>
+        <v>517</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>192</v>
+        <v>43</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>191</v>
+        <v>563</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="2" t="s">
-        <v>193</v>
+      <c r="G61" s="10" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>246</v>
+        <v>561</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>248</v>
+        <v>43</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>247</v>
+        <v>563</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>253</v>
+      <c r="G62" s="4" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>252</v>
+        <v>446</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>248</v>
+        <v>499</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>247</v>
+        <v>458</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>30</v>
@@ -3642,18 +3675,18 @@
         <v>6</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>508</v>
+        <v>189</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>509</v>
+        <v>192</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>510</v>
+        <v>191</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>30</v>
@@ -3664,19 +3697,19 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G64" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>338</v>
+        <v>246</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>248</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>334</v>
+        <v>247</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>30</v>
@@ -3688,18 +3721,18 @@
         <v>6</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>339</v>
+        <v>253</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>447</v>
+        <v>252</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>501</v>
+        <v>248</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>463</v>
+        <v>247</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>30</v>
@@ -3711,21 +3744,21 @@
         <v>6</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>427</v>
+        <v>507</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>459</v>
+        <v>509</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>11</v>
@@ -3733,22 +3766,22 @@
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G67" s="5" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>117</v>
+        <v>336</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>118</v>
+        <v>334</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>11</v>
@@ -3756,22 +3789,22 @@
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="4" t="s">
-        <v>209</v>
+      <c r="G68" s="2" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>47</v>
+        <v>447</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>51</v>
+        <v>500</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>49</v>
+        <v>463</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>11</v>
@@ -3780,18 +3813,18 @@
         <v>6</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>210</v>
+        <v>419</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>48</v>
+        <v>427</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>53</v>
+        <v>481</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>50</v>
+        <v>459</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>52</v>
@@ -3803,18 +3836,18 @@
         <v>6</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>53</v>
+        <v>117</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>52</v>
@@ -3825,19 +3858,19 @@
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="5" t="s">
-        <v>211</v>
+      <c r="G71" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>477</v>
+        <v>47</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>483</v>
+        <v>51</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>52</v>
@@ -3849,21 +3882,21 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>112</v>
+        <v>52</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -3871,22 +3904,22 @@
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G73" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>448</v>
+        <v>90</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>502</v>
+        <v>53</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>466</v>
+        <v>50</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>421</v>
+        <v>52</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3894,22 +3927,22 @@
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>419</v>
+      <c r="G74" s="5" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>133</v>
+        <v>477</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>139</v>
+        <v>482</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -3918,21 +3951,21 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>313</v>
+        <v>109</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>11</v>
@@ -3940,22 +3973,22 @@
       <c r="F76" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>303</v>
+      <c r="G76" s="5" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>56</v>
+        <v>448</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>54</v>
+        <v>501</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>466</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>9</v>
+        <v>421</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -3964,18 +3997,18 @@
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>414</v>
+        <v>133</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
@@ -3986,19 +4019,19 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="5" t="s">
-        <v>392</v>
+      <c r="G78" s="2" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>57</v>
+        <v>313</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>9</v>
@@ -4010,18 +4043,18 @@
         <v>6</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>60</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>121</v>
+        <v>55</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>9</v>
@@ -4033,21 +4066,21 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>121</v>
+        <v>413</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>414</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -4056,21 +4089,21 @@
         <v>6</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>300</v>
+        <v>57</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>344</v>
+        <v>58</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>343</v>
+        <v>59</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -4079,21 +4112,21 @@
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>299</v>
+        <v>60</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -4102,21 +4135,21 @@
         <v>6</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>91</v>
+        <v>383</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>64</v>
+        <v>373</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -4124,22 +4157,22 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>213</v>
+      <c r="G84" s="5" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>228</v>
+        <v>300</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>63</v>
+        <v>344</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>61</v>
+        <v>343</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -4148,12 +4181,12 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>224</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>528</v>
+        <v>62</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>63</v>
@@ -4170,22 +4203,22 @@
       <c r="F86" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G86" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G86" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -4193,22 +4226,22 @@
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>96</v>
+      <c r="G87" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>422</v>
+        <v>228</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>461</v>
+        <v>63</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>460</v>
+        <v>61</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>420</v>
+        <v>64</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -4217,21 +4250,21 @@
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>419</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>66</v>
+        <v>527</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -4240,21 +4273,21 @@
         <v>6</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>225</v>
+        <v>92</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>231</v>
+        <v>93</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>235</v>
+        <v>94</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -4262,22 +4295,22 @@
       <c r="F90" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G90" s="2" t="s">
-        <v>224</v>
+      <c r="G90" s="5" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>503</v>
+        <v>422</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>231</v>
+        <v>461</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>235</v>
+        <v>460</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>258</v>
+        <v>420</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -4291,16 +4324,16 @@
     </row>
     <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>553</v>
+        <v>66</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>554</v>
+        <v>67</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>465</v>
+        <v>68</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -4309,44 +4342,44 @@
         <v>6</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>423</v>
+        <v>577</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>478</v>
+        <v>571</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>465</v>
+        <v>568</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>258</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G93" s="5" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>172</v>
+        <v>225</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>174</v>
+        <v>231</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>235</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -4355,21 +4388,21 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>175</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>177</v>
+        <v>502</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>180</v>
+        <v>258</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -4378,18 +4411,18 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>398</v>
+        <v>552</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>403</v>
+        <v>231</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>404</v>
+        <v>235</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>258</v>
@@ -4400,22 +4433,22 @@
       <c r="F96" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G96" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>488</v>
+        <v>553</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -4423,22 +4456,22 @@
       <c r="F97" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G97" s="2" t="s">
-        <v>419</v>
+      <c r="G97" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>433</v>
+        <v>578</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>489</v>
+        <v>553</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -4450,41 +4483,41 @@
         <v>419</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>434</v>
+        <v>576</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>490</v>
+        <v>553</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G99" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>435</v>
+        <v>172</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>457</v>
+        <v>173</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -4493,21 +4526,21 @@
         <v>6</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>101</v>
+        <v>177</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>102</v>
+        <v>178</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -4515,65 +4548,65 @@
       <c r="F101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G101" s="5" t="s">
-        <v>104</v>
+      <c r="G101" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="D102" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G102" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A103" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G102" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A103" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G103" s="5" t="s">
-        <v>387</v>
+      <c r="G103" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>134</v>
+        <v>433</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>140</v>
+        <v>488</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>137</v>
+        <v>476</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
@@ -4585,18 +4618,18 @@
         <v>6</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>142</v>
+        <v>419</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>314</v>
+        <v>434</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>140</v>
+        <v>489</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>137</v>
+        <v>469</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>9</v>
@@ -4608,21 +4641,21 @@
         <v>6</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>303</v>
+        <v>419</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>322</v>
+        <v>435</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>324</v>
+        <v>490</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>325</v>
+        <v>457</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -4631,21 +4664,21 @@
         <v>6</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>274</v>
+        <v>101</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>275</v>
+        <v>102</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -4653,22 +4686,22 @@
       <c r="F107" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G107" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
-        <v>302</v>
+        <v>372</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>277</v>
+        <v>370</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -4676,19 +4709,19 @@
       <c r="F108" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G108" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G108" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>470</v>
+        <v>397</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>275</v>
+        <v>401</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>277</v>
+        <v>400</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>258</v>
@@ -4699,22 +4732,22 @@
       <c r="F109" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G109" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G109" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>531</v>
+        <v>134</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -4723,21 +4756,21 @@
         <v>6</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.15">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>424</v>
+        <v>314</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>479</v>
+        <v>140</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>468</v>
+        <v>137</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -4746,44 +4779,44 @@
         <v>6</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>545</v>
+        <v>322</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>479</v>
+        <v>324</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>537</v>
+        <v>325</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>258</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>538</v>
+        <v>11</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G112" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G112" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>183</v>
+        <v>274</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>184</v>
+        <v>277</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -4791,22 +4824,22 @@
       <c r="F113" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G113" s="5" t="s">
-        <v>185</v>
+      <c r="G113" s="2" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>406</v>
+        <v>302</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>407</v>
+        <v>275</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>408</v>
+        <v>277</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>409</v>
+        <v>258</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -4815,21 +4848,21 @@
         <v>6</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>124</v>
+        <v>470</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -4838,21 +4871,21 @@
         <v>6</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>226</v>
+        <v>530</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>11</v>
@@ -4861,21 +4894,21 @@
         <v>6</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>224</v>
+        <v>531</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -4887,41 +4920,41 @@
         <v>419</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>366</v>
+        <v>544</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>367</v>
+        <v>478</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>368</v>
+        <v>536</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>11</v>
+        <v>537</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>358</v>
+        <v>182</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>361</v>
+        <v>184</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>360</v>
+        <v>25</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -4929,22 +4962,22 @@
       <c r="F119" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G119" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G119" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>98</v>
+        <v>406</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>99</v>
+        <v>407</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>100</v>
+        <v>408</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>9</v>
+        <v>409</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -4952,19 +4985,19 @@
       <c r="F120" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G120" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G120" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>437</v>
+        <v>124</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>493</v>
+        <v>122</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>472</v>
+        <v>123</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>9</v>
@@ -4976,18 +5009,18 @@
         <v>6</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>419</v>
+        <v>128</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>438</v>
+        <v>226</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>494</v>
+        <v>122</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>475</v>
+        <v>123</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>9</v>
@@ -4999,41 +5032,41 @@
         <v>6</v>
       </c>
       <c r="G122" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A123" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G123" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A123" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G123" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>439</v>
+        <v>366</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>495</v>
+        <v>367</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>462</v>
+        <v>368</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>9</v>
@@ -5044,91 +5077,91 @@
       <c r="F124" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="G124" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A125" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A126" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G126" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A127" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G127" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A125" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G125" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A126" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A127" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G127" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="28" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B128" s="6" t="s">
-        <v>346</v>
+        <v>438</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>347</v>
+        <v>475</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -5137,21 +5170,21 @@
         <v>6</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>295</v>
+        <v>419</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>381</v>
+        <v>70</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>285</v>
+        <v>69</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>286</v>
+        <v>71</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -5160,21 +5193,21 @@
         <v>6</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>558</v>
+        <v>439</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>285</v>
+        <v>494</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>286</v>
+        <v>462</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -5182,19 +5215,19 @@
       <c r="F130" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G130" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G130" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>75</v>
@@ -5205,19 +5238,19 @@
       <c r="F131" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G131" s="2" t="s">
-        <v>131</v>
+      <c r="G131" s="5" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>342</v>
+        <v>108</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>341</v>
+        <v>107</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>75</v>
@@ -5229,18 +5262,18 @@
         <v>6</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.15">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>75</v>
@@ -5251,20 +5284,19 @@
       <c r="F133" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G133" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H133" s="2"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G133" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="28" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>417</v>
+        <v>296</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>346</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>75</v>
@@ -5276,21 +5308,21 @@
         <v>6</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>402</v>
+        <v>285</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>405</v>
+        <v>286</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>258</v>
+        <v>75</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -5299,21 +5331,21 @@
         <v>6</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.15">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
-        <v>315</v>
+        <v>557</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>316</v>
+        <v>286</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>312</v>
+        <v>75</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -5321,22 +5353,22 @@
       <c r="F136" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G136" s="2" t="s">
-        <v>303</v>
+      <c r="G136" s="5" t="s">
+        <v>567</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -5348,18 +5380,18 @@
         <v>131</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:8" ht="14" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>77</v>
+        <v>340</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>342</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -5368,21 +5400,21 @@
         <v>6</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>153</v>
+        <v>292</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>187</v>
+        <v>278</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>78</v>
+        <v>280</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -5391,21 +5423,22 @@
         <v>6</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>186</v>
-      </c>
+        <v>281</v>
+      </c>
+      <c r="H139" s="2"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>533</v>
+        <v>416</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>77</v>
+        <v>417</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>78</v>
+        <v>341</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -5414,21 +5447,21 @@
         <v>6</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
-        <v>440</v>
+        <v>399</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>496</v>
+        <v>402</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>455</v>
+        <v>405</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -5436,22 +5469,22 @@
       <c r="F141" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G141" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G141" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
-        <v>552</v>
+        <v>315</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>496</v>
+        <v>317</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>455</v>
+        <v>316</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>9</v>
+        <v>312</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -5459,22 +5492,22 @@
       <c r="F142" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G142" s="5" t="s">
-        <v>555</v>
+      <c r="G142" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
-        <v>227</v>
+        <v>76</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>236</v>
+        <v>78</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -5483,21 +5516,21 @@
         <v>6</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
-        <v>541</v>
+        <v>154</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>542</v>
+        <v>77</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>544</v>
+        <v>78</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>258</v>
+        <v>30</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -5505,22 +5538,22 @@
       <c r="F144" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G144" s="5" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G144" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -5529,21 +5562,21 @@
         <v>6</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.15">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>298</v>
+        <v>532</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -5552,44 +5585,44 @@
         <v>6</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>299</v>
+        <v>533</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="B147" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C147" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D147" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="E147" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>536</v>
+        <v>419</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
-        <v>521</v>
+        <v>551</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>517</v>
+        <v>455</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -5598,18 +5631,18 @@
         <v>6</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
-        <v>143</v>
+        <v>227</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>146</v>
+        <v>232</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>9</v>
@@ -5620,22 +5653,22 @@
       <c r="F149" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G149" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G149" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>410</v>
+        <v>540</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>412</v>
+        <v>541</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>543</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -5644,21 +5677,21 @@
         <v>6</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>393</v>
+        <v>542</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>87</v>
+        <v>195</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -5667,21 +5700,21 @@
         <v>6</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>200</v>
+        <v>298</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -5689,45 +5722,45 @@
       <c r="F152" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G152" s="5" t="s">
-        <v>201</v>
+      <c r="G152" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D153" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E153" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F153" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.15">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>351</v>
+        <v>520</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>88</v>
+        <v>514</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>89</v>
+        <v>516</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -5735,19 +5768,19 @@
       <c r="F154" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G154" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G154" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>557</v>
+        <v>143</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>88</v>
+        <v>146</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -5758,45 +5791,45 @@
       <c r="F155" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G155" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G155" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>79</v>
+        <v>410</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>83</v>
+        <v>411</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>412</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G156" s="2" t="s">
-        <v>217</v>
+      <c r="G156" s="5" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>158</v>
+        <v>87</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -5805,21 +5838,21 @@
         <v>6</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.15">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
-        <v>288</v>
+        <v>200</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -5827,22 +5860,22 @@
       <c r="F158" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G158" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G158" s="5" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -5850,22 +5883,22 @@
       <c r="F159" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G159" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G159" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
-        <v>384</v>
+        <v>351</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>385</v>
+        <v>88</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -5873,22 +5906,22 @@
       <c r="F160" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G160" s="5" t="s">
-        <v>386</v>
+      <c r="G160" s="2" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
-        <v>81</v>
+        <v>556</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -5897,41 +5930,41 @@
         <v>6</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
-        <v>151</v>
+        <v>79</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>345</v>
+        <v>158</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>75</v>
@@ -5943,18 +5976,18 @@
         <v>6</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>301</v>
+        <v>159</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>349</v>
+        <v>288</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>75</v>
@@ -5966,18 +5999,18 @@
         <v>6</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>350</v>
+        <v>289</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>348</v>
+        <v>290</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>75</v>
@@ -5989,18 +6022,18 @@
         <v>6</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>513</v>
+        <v>384</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>75</v>
@@ -6011,13 +6044,13 @@
       <c r="F166" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G166" s="2" t="s">
-        <v>218</v>
+      <c r="G166" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>514</v>
+        <v>81</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>82</v>
@@ -6035,21 +6068,21 @@
         <v>6</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>395</v>
+        <v>218</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -6058,21 +6091,21 @@
         <v>6</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
-        <v>202</v>
+        <v>345</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -6081,21 +6114,21 @@
         <v>6</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>511</v>
+        <v>349</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -6103,22 +6136,22 @@
       <c r="F170" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G170" s="5" t="s">
-        <v>512</v>
+      <c r="G170" s="2" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="171" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -6127,21 +6160,21 @@
         <v>6</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>219</v>
+        <v>297</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>282</v>
+        <v>512</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -6150,110 +6183,110 @@
         <v>6</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
-        <v>441</v>
+        <v>513</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A174" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A175" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A176" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A177" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C173" s="2" t="s">
+      <c r="C177" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F173" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A174" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G174" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A175" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G175" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A176" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B176" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F176" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A177" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B177" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>9</v>
@@ -6264,94 +6297,230 @@
       <c r="F177" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G177" s="2" t="s">
+      <c r="G177" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A178" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A179" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A180" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A181" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A182" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A183" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G183" s="2" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G178" s="5"/>
-    </row>
-    <row r="180" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G181" s="10"/>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="G182" s="4"/>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A187" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="B187" s="2" t="s">
+    <row r="184" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G184" s="5"/>
+    </row>
+    <row r="185" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G185" s="5"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A191" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C187" s="2" t="s">
+      <c r="C191" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="D191" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E187" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G187" s="2" t="s">
+      <c r="E191" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G191" s="2" t="s">
         <v>394</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H177">
-    <sortCondition ref="A177"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H188">
+    <sortCondition ref="A65:A188"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G16" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G38" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G87" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G101" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G120" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G73" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G149" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G152" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G17" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G41" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G90" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G107" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G126" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G76" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G155" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G158" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G9" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G50" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G53" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G56" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G71" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G89" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G123" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G125" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G171" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G24" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G127" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G159" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G42" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G54" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G165" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G118" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G102" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G81" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G129" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G160" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
-    <hyperlink ref="G150" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
-    <hyperlink ref="G20" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
-    <hyperlink ref="G64" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
-    <hyperlink ref="G170" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
-    <hyperlink ref="G51" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
-    <hyperlink ref="G148" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
-    <hyperlink ref="G86" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
-    <hyperlink ref="G46" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
+    <hyperlink ref="G53" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G56" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G59" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G74" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G92" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G129" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G131" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G177" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G25" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G133" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G165" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G45" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G57" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G171" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G124" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G108" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G84" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G135" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G166" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G156" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
+    <hyperlink ref="G21" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
+    <hyperlink ref="G67" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
+    <hyperlink ref="G176" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
+    <hyperlink ref="G54" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
+    <hyperlink ref="G154" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
+    <hyperlink ref="G89" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
+    <hyperlink ref="G49" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
     <hyperlink ref="G7" r:id="rId38" xr:uid="{AD3618A6-5FE8-B940-9FEF-9FF5D1F662CA}"/>
-    <hyperlink ref="G144" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
-    <hyperlink ref="G47" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
-    <hyperlink ref="G43" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
-    <hyperlink ref="G112" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
-    <hyperlink ref="G92" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
-    <hyperlink ref="G58" r:id="rId44" xr:uid="{3E4AD335-D90F-8E4F-99D9-B5A29F73491A}"/>
-    <hyperlink ref="G130" r:id="rId45" xr:uid="{5496842B-F19F-F64D-AE34-576CA41371CE}"/>
+    <hyperlink ref="G150" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
+    <hyperlink ref="G50" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
+    <hyperlink ref="G46" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
+    <hyperlink ref="G118" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
+    <hyperlink ref="G97" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
+    <hyperlink ref="G61" r:id="rId44" xr:uid="{3E4AD335-D90F-8E4F-99D9-B5A29F73491A}"/>
+    <hyperlink ref="G136" r:id="rId45" xr:uid="{5496842B-F19F-F64D-AE34-576CA41371CE}"/>
+    <hyperlink ref="G93" r:id="rId46" xr:uid="{F15A6606-6F28-5141-8864-8E110DF5FF49}"/>
+    <hyperlink ref="G99" r:id="rId47" xr:uid="{2D5CC932-530B-3943-8E48-2E3B2B48A21A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6368,15 +6537,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1808" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C1B84E8-F1AF-E642-84AF-1E38FC6F4A26}"/>
+  <xr:revisionPtr revIDLastSave="1816" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B96457C-CE0D-934A-A7A8-C89A61EF3071}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28720" windowHeight="16680" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4420" yWindow="-21100" windowWidth="19980" windowHeight="21100" activeTab="1" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="583">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1774,6 +1774,18 @@
   </si>
   <si>
     <t>LEME-2</t>
+  </si>
+  <si>
+    <t>Boardman paper</t>
+  </si>
+  <si>
+    <t>Niagara falls</t>
+  </si>
+  <si>
+    <t>DOI: 10.1080/00028487.2012.670184</t>
+  </si>
+  <si>
+    <t>ETCA - Belcik</t>
   </si>
 </sst>
 </file>
@@ -2213,7 +2225,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H191"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -5912,30 +5924,30 @@
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
-        <v>556</v>
+        <v>79</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F161" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.15">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>80</v>
@@ -5947,18 +5959,18 @@
         <v>75</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F162" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>80</v>
@@ -5976,12 +5988,12 @@
         <v>6</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.15">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>80</v>
@@ -5998,16 +6010,16 @@
       <c r="F164" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G164" s="2" t="s">
-        <v>289</v>
+      <c r="G164" s="5" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>290</v>
+        <v>384</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>80</v>
+        <v>385</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>83</v>
@@ -6022,18 +6034,18 @@
         <v>6</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>384</v>
+        <v>81</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>75</v>
@@ -6044,13 +6056,13 @@
       <c r="F166" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G166" s="5" t="s">
-        <v>386</v>
+      <c r="G166" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>82</v>
@@ -6068,12 +6080,12 @@
         <v>6</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>218</v>
+        <v>152</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>151</v>
+        <v>345</v>
       </c>
       <c r="B168" s="2" t="s">
         <v>82</v>
@@ -6091,12 +6103,12 @@
         <v>6</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>152</v>
+        <v>301</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>82</v>
@@ -6114,12 +6126,12 @@
         <v>6</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B170" s="2" t="s">
         <v>82</v>
@@ -6136,13 +6148,13 @@
       <c r="F170" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G170" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G170" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
-        <v>348</v>
+        <v>512</v>
       </c>
       <c r="B171" s="2" t="s">
         <v>82</v>
@@ -6159,13 +6171,13 @@
       <c r="F171" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G171" s="5" t="s">
-        <v>297</v>
+      <c r="G171" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B172" s="2" t="s">
         <v>82</v>
@@ -6183,21 +6195,21 @@
         <v>6</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>218</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
-        <v>513</v>
+        <v>155</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>82</v>
+        <v>156</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -6206,12 +6218,12 @@
         <v>6</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>395</v>
+        <v>153</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>156</v>
@@ -6229,12 +6241,12 @@
         <v>6</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
-        <v>202</v>
+        <v>510</v>
       </c>
       <c r="B175" s="2" t="s">
         <v>156</v>
@@ -6251,22 +6263,22 @@
       <c r="F175" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G175" s="2" t="s">
-        <v>203</v>
+      <c r="G175" s="5" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
-        <v>510</v>
+        <v>84</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>157</v>
+        <v>17</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -6275,12 +6287,12 @@
         <v>6</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
-        <v>84</v>
+        <v>282</v>
       </c>
       <c r="B177" s="2" t="s">
         <v>85</v>
@@ -6297,13 +6309,13 @@
       <c r="F177" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G177" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G177" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A178" s="2" t="s">
-        <v>282</v>
+        <v>441</v>
       </c>
       <c r="B178" s="2" t="s">
         <v>85</v>
@@ -6321,18 +6333,18 @@
         <v>6</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A179" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>85</v>
+        <v>147</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>17</v>
+        <v>148</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>9</v>
@@ -6343,19 +6355,19 @@
       <c r="F179" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G179" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G179" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A180" s="2" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>148</v>
+        <v>222</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>9</v>
@@ -6366,19 +6378,19 @@
       <c r="F180" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G180" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G180" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A181" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C181" s="6" t="s">
-        <v>221</v>
+        <v>135</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>9</v>
@@ -6390,12 +6402,12 @@
         <v>6</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>223</v>
+        <v>142</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A182" s="2" t="s">
-        <v>135</v>
+        <v>318</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>141</v>
@@ -6413,64 +6425,64 @@
         <v>6</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A183" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="B183" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E183" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F183" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G183" s="2" t="s">
         <v>303</v>
       </c>
+    </row>
+    <row r="183" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G183" s="5"/>
     </row>
     <row r="184" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="G184" s="5"/>
     </row>
-    <row r="185" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G185" s="5"/>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A191" s="2" t="s">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A190" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B190" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C191" s="2" t="s">
+      <c r="C190" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D191" s="2" t="s">
+      <c r="D190" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E191" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G191" s="2" t="s">
+      <c r="E190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G190" s="2" t="s">
         <v>394</v>
       </c>
     </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A195" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H188">
-    <sortCondition ref="A65:A188"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H187">
+    <sortCondition ref="A65:A187"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
@@ -6491,22 +6503,22 @@
     <hyperlink ref="G92" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
     <hyperlink ref="G129" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
     <hyperlink ref="G131" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G177" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G176" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
     <hyperlink ref="G25" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
     <hyperlink ref="G133" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G165" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G164" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
     <hyperlink ref="G45" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
     <hyperlink ref="G57" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G171" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G170" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
     <hyperlink ref="G124" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
     <hyperlink ref="G108" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
     <hyperlink ref="G84" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
     <hyperlink ref="G135" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G166" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G165" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
     <hyperlink ref="G156" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
     <hyperlink ref="G21" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
     <hyperlink ref="G67" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
-    <hyperlink ref="G176" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
+    <hyperlink ref="G175" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
     <hyperlink ref="G54" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
     <hyperlink ref="G154" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
     <hyperlink ref="G89" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
@@ -6548,11 +6560,20 @@
         <v>565</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>579</v>
+      </c>
+    </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="7"/>
+      <c r="A4" s="7" t="s">
+        <v>580</v>
+      </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="7"/>
+      <c r="A5" s="7" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1816" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B96457C-CE0D-934A-A7A8-C89A61EF3071}"/>
+  <xr:revisionPtr revIDLastSave="1933" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A7CE26-E182-814E-A386-D271F36F4CB0}"/>
   <bookViews>
-    <workbookView xWindow="-4420" yWindow="-21100" windowWidth="19980" windowHeight="21100" activeTab="1" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
+    <workbookView xWindow="-4380" yWindow="-21100" windowWidth="31320" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
   <sheets>
     <sheet name="processed_data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1295" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="614">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1786,6 +1786,99 @@
   </si>
   <si>
     <t>ETCA - Belcik</t>
+  </si>
+  <si>
+    <t>RHOS-6</t>
+  </si>
+  <si>
+    <t>CAPL-1</t>
+  </si>
+  <si>
+    <t>Mountain Sucker</t>
+  </si>
+  <si>
+    <t>CATA-1</t>
+  </si>
+  <si>
+    <t>Tahoe sucker</t>
+  </si>
+  <si>
+    <t>RHEG-1</t>
+  </si>
+  <si>
+    <t>Lahontan Redside</t>
+  </si>
+  <si>
+    <t>Catostomus platyrhynchus</t>
+  </si>
+  <si>
+    <t>Catostomus tahoensis</t>
+  </si>
+  <si>
+    <t>Richardsonius egregious</t>
+  </si>
+  <si>
+    <t>http://dx.doi.org/10.1016/j.scitotenv.2016.04.056</t>
+  </si>
+  <si>
+    <t>ETSO-1</t>
+  </si>
+  <si>
+    <t>Candy Darter</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/fishes8100490</t>
+  </si>
+  <si>
+    <t>Etheostoma osburni</t>
+  </si>
+  <si>
+    <t>ETCA-6</t>
+  </si>
+  <si>
+    <t>DOI: 10.1111/eva.13135</t>
+  </si>
+  <si>
+    <t>ORCR-1</t>
+  </si>
+  <si>
+    <t>Oregon Chub</t>
+  </si>
+  <si>
+    <t>Oregonichthys crameri</t>
+  </si>
+  <si>
+    <t>CHSP-1</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/fishes8070365</t>
+  </si>
+  <si>
+    <t>Laurel dace</t>
+  </si>
+  <si>
+    <t>Chrosomus saylori</t>
+  </si>
+  <si>
+    <t>SAVI-4</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-023-01504-7</t>
+  </si>
+  <si>
+    <t>CYEL-1</t>
+  </si>
+  <si>
+    <t>Cycleptus elongatus</t>
+  </si>
+  <si>
+    <t>Blue Sucker</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-007-9401-4</t>
+  </si>
+  <si>
+    <t>COBA-3</t>
   </si>
 </sst>
 </file>
@@ -1902,10 +1995,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2225,7 +2314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -2609,18 +2698,18 @@
         <v>419</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
-        <v>22</v>
+        <v>584</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>23</v>
+        <v>585</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>24</v>
+        <v>590</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>25</v>
+        <v>312</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>11</v>
@@ -2628,19 +2717,19 @@
       <c r="F17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>26</v>
+      <c r="G17" s="5" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>267</v>
+        <v>22</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>25</v>
@@ -2651,91 +2740,91 @@
       <c r="F18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A20" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A21" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="E21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A20" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A21" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>260</v>
+        <v>603</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>259</v>
+        <v>605</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>263</v>
+        <v>606</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>261</v>
+        <v>9</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>11</v>
@@ -2743,65 +2832,65 @@
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>262</v>
+      <c r="G22" s="5" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
-        <v>264</v>
+        <v>354</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>261</v>
@@ -2812,22 +2901,22 @@
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G25" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
-        <v>506</v>
+        <v>264</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>503</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>504</v>
+        <v>263</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>365</v>
+        <v>261</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>11</v>
@@ -2835,19 +2924,19 @@
       <c r="F26" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G26" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>480</v>
+        <v>259</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>450</v>
+        <v>263</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>261</v>
@@ -2858,22 +2947,22 @@
       <c r="F27" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>419</v>
+      <c r="G27" s="5" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>474</v>
+        <v>452</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>11</v>
@@ -2885,18 +2974,18 @@
         <v>419</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>11</v>
@@ -2904,22 +2993,22 @@
       <c r="F29" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G29" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>251</v>
+        <v>506</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>250</v>
+        <v>503</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>249</v>
+        <v>504</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9</v>
+        <v>365</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>11</v>
@@ -2927,22 +3016,22 @@
       <c r="F30" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>253</v>
+      <c r="G30" s="8" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
-        <v>125</v>
+        <v>426</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>126</v>
+        <v>480</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>127</v>
+        <v>450</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>9</v>
+        <v>261</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>11</v>
@@ -2951,44 +3040,44 @@
         <v>6</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
-        <v>575</v>
+        <v>609</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>127</v>
+        <v>611</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>610</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>9</v>
+        <v>312</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>569</v>
+      <c r="G32" s="5" t="s">
+        <v>612</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
-        <v>162</v>
+        <v>430</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>163</v>
+        <v>485</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>164</v>
+        <v>474</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>160</v>
+        <v>9</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>11</v>
@@ -2997,41 +3086,41 @@
         <v>6</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>574</v>
+        <v>245</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>572</v>
+        <v>250</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>570</v>
+        <v>249</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G34" s="5" t="s">
-        <v>569</v>
+      <c r="G34" s="2" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>431</v>
+        <v>251</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>486</v>
+        <v>250</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>467</v>
+        <v>249</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>9</v>
@@ -3043,21 +3132,21 @@
         <v>6</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>419</v>
+        <v>253</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>233</v>
+        <v>126</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>240</v>
+        <v>127</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>239</v>
+        <v>9</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>11</v>
@@ -3066,44 +3155,44 @@
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>352</v>
+        <v>575</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>356</v>
+        <v>126</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>357</v>
+        <v>127</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G37" s="2" t="s">
-        <v>355</v>
+      <c r="G37" s="11" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
-        <v>442</v>
+        <v>162</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>496</v>
+        <v>163</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>454</v>
+        <v>164</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
@@ -3112,44 +3201,44 @@
         <v>6</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
-        <v>335</v>
+        <v>574</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>337</v>
+        <v>572</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>333</v>
+        <v>570</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>339</v>
+      <c r="G39" s="5" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
-        <v>27</v>
+        <v>431</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>28</v>
+        <v>486</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>29</v>
+        <v>467</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>11</v>
@@ -3158,21 +3247,21 @@
         <v>6</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>33</v>
+        <v>419</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>31</v>
+        <v>229</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>28</v>
+        <v>233</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>29</v>
+        <v>240</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>30</v>
+        <v>239</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>
@@ -3180,19 +3269,19 @@
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G41" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>28</v>
+        <v>352</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>29</v>
+        <v>357</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>30</v>
@@ -3203,19 +3292,19 @@
       <c r="F42" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G42" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G42" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>28</v>
+        <v>442</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>496</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>29</v>
+        <v>454</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
@@ -3227,18 +3316,18 @@
         <v>6</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>321</v>
+        <v>419</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>443</v>
+        <v>335</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>28</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>30</v>
@@ -3250,18 +3339,18 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>332</v>
+        <v>27</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>331</v>
+        <v>28</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>330</v>
+        <v>29</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>30</v>
@@ -3272,19 +3361,19 @@
       <c r="F45" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G45" s="5" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G45" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>545</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>547</v>
+        <v>28</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>549</v>
+        <v>29</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>30</v>
@@ -3295,19 +3384,19 @@
       <c r="F46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="5" t="s">
-        <v>396</v>
+      <c r="G46" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>497</v>
+        <v>166</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>449</v>
+        <v>29</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>30</v>
@@ -3318,19 +3407,19 @@
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G47" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>168</v>
+        <v>320</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>170</v>
+        <v>28</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
@@ -3341,19 +3430,19 @@
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G48" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>524</v>
+        <v>443</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>526</v>
+        <v>28</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>562</v>
+        <v>29</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>30</v>
@@ -3364,42 +3453,42 @@
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G49" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="D50" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="E50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>445</v>
+        <v>332</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>498</v>
+        <v>331</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>456</v>
+        <v>330</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>30</v>
@@ -3410,19 +3499,19 @@
       <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G51" s="5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>241</v>
+        <v>545</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>242</v>
+        <v>547</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>243</v>
+        <v>549</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
@@ -3433,19 +3522,19 @@
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G52" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>34</v>
+        <v>444</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>35</v>
+        <v>497</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>36</v>
+        <v>449</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
@@ -3456,19 +3545,19 @@
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="5" t="s">
-        <v>205</v>
+      <c r="G53" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>35</v>
+        <v>168</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>36</v>
+        <v>169</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>30</v>
@@ -3480,18 +3569,18 @@
         <v>6</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>188</v>
+        <v>524</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>194</v>
+        <v>526</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>190</v>
+        <v>562</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>30</v>
@@ -3502,19 +3591,19 @@
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G55" s="2" t="s">
-        <v>193</v>
+      <c r="G55" s="5" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>38</v>
+        <v>546</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>37</v>
+        <v>548</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>39</v>
+        <v>550</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
@@ -3526,18 +3615,18 @@
         <v>6</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>326</v>
+        <v>445</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>329</v>
+        <v>498</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>327</v>
+        <v>456</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
@@ -3548,19 +3637,19 @@
       <c r="F57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>328</v>
+      <c r="G57" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>521</v>
+        <v>241</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>523</v>
+        <v>242</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>522</v>
+        <v>243</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>30</v>
@@ -3572,18 +3661,18 @@
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>390</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>30</v>
@@ -3595,18 +3684,18 @@
         <v>6</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.15">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>45</v>
+        <v>518</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>30</v>
@@ -3617,65 +3706,65 @@
       <c r="F60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="17" x14ac:dyDescent="0.15">
+      <c r="G60" s="5" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>517</v>
+        <v>188</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>563</v>
+        <v>190</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="10" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G61" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>561</v>
+        <v>38</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>563</v>
+        <v>39</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="4" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G62" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>446</v>
+        <v>326</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>499</v>
+        <v>329</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>458</v>
+        <v>327</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>30</v>
@@ -3686,19 +3775,19 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>419</v>
+      <c r="G63" s="5" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>189</v>
+        <v>521</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>192</v>
+        <v>523</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>191</v>
+        <v>522</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>30</v>
@@ -3710,18 +3799,18 @@
         <v>6</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>246</v>
+        <v>42</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>248</v>
+        <v>40</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>247</v>
+        <v>41</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>30</v>
@@ -3732,19 +3821,19 @@
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>253</v>
+      <c r="G65" s="5" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>252</v>
+        <v>45</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>248</v>
+        <v>43</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>247</v>
+        <v>44</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>30</v>
@@ -3755,65 +3844,65 @@
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G66" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>507</v>
+        <v>517</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>508</v>
+        <v>43</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>509</v>
+        <v>563</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G67" s="10" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>338</v>
+        <v>561</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>334</v>
+        <v>563</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G68" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>447</v>
+        <v>594</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>500</v>
+        <v>595</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>463</v>
+        <v>597</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>30</v>
@@ -3824,22 +3913,22 @@
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>419</v>
+      <c r="G69" s="5" t="s">
+        <v>596</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>11</v>
@@ -3853,16 +3942,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>117</v>
+        <v>192</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>118</v>
+        <v>191</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>11</v>
@@ -3870,22 +3959,22 @@
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="4" t="s">
-        <v>209</v>
+      <c r="G71" s="2" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>47</v>
+        <v>246</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>51</v>
+        <v>248</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>49</v>
+        <v>247</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>11</v>
@@ -3894,21 +3983,21 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>48</v>
+        <v>252</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>53</v>
+        <v>248</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>50</v>
+        <v>247</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>11</v>
@@ -3917,21 +4006,21 @@
         <v>6</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>210</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>90</v>
+        <v>507</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>53</v>
+        <v>508</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>50</v>
+        <v>509</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>11</v>
@@ -3940,21 +4029,21 @@
         <v>6</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.15">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>482</v>
+        <v>336</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>50</v>
+        <v>334</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>11</v>
@@ -3963,44 +4052,44 @@
         <v>6</v>
       </c>
       <c r="G75" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A76" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>419</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A76" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>421</v>
+        <v>52</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -4014,16 +4103,16 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -4031,22 +4120,22 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>142</v>
+      <c r="G78" s="4" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>313</v>
+        <v>47</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>139</v>
+        <v>51</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -4055,21 +4144,21 @@
         <v>6</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>303</v>
+        <v>210</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -4078,21 +4167,21 @@
         <v>6</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>414</v>
+        <v>90</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -4101,21 +4190,21 @@
         <v>6</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>392</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>57</v>
+        <v>477</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>58</v>
+        <v>482</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -4124,21 +4213,21 @@
         <v>6</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>9</v>
+        <v>112</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>11</v>
@@ -4146,22 +4235,22 @@
       <c r="F83" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G83" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>383</v>
+        <v>448</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>120</v>
+        <v>501</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>121</v>
+        <v>466</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>373</v>
+        <v>421</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -4169,22 +4258,22 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>371</v>
+      <c r="G84" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>300</v>
+        <v>133</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>344</v>
+        <v>139</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>343</v>
+        <v>136</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -4193,21 +4282,21 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>299</v>
+        <v>142</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>62</v>
+        <v>313</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -4216,182 +4305,182 @@
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>65</v>
+        <v>303</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A88" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A89" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A90" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A91" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A92" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A93" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C93" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="D93" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A88" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G88" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A89" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A90" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A91" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A92" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A93" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E93" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>569</v>
+      <c r="G93" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>235</v>
+        <v>61</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -4400,21 +4489,21 @@
         <v>6</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>502</v>
+        <v>228</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>235</v>
+        <v>61</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>258</v>
+        <v>64</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -4423,21 +4512,21 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>552</v>
+        <v>527</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>231</v>
+        <v>63</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>235</v>
+        <v>61</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>258</v>
+        <v>64</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -4445,22 +4534,22 @@
       <c r="F96" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G96" s="2" t="s">
-        <v>419</v>
+      <c r="G96" s="5" t="s">
+        <v>528</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>423</v>
+        <v>92</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>553</v>
+        <v>93</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>465</v>
+        <v>94</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>258</v>
+        <v>95</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -4469,21 +4558,21 @@
         <v>6</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>554</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>578</v>
+        <v>422</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>553</v>
+        <v>461</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>258</v>
+        <v>420</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -4495,64 +4584,64 @@
         <v>419</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="17" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>576</v>
+        <v>66</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>553</v>
+        <v>67</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>465</v>
+        <v>68</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A100" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E99" s="2" t="s">
+      <c r="E100" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" s="10" t="s">
+      <c r="F100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>569</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A100" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>177</v>
+        <v>225</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>178</v>
+        <v>231</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -4561,18 +4650,18 @@
         <v>6</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>398</v>
+        <v>502</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>403</v>
+        <v>231</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>404</v>
+        <v>235</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>258</v>
@@ -4583,22 +4672,22 @@
       <c r="F102" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G102" s="5" t="s">
-        <v>387</v>
+      <c r="G102" s="2" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>432</v>
+        <v>552</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>487</v>
+        <v>231</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>464</v>
+        <v>235</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -4610,18 +4699,18 @@
         <v>419</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>488</v>
+        <v>553</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -4629,22 +4718,22 @@
       <c r="F104" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G104" s="2" t="s">
-        <v>419</v>
+      <c r="G104" s="5" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>434</v>
+        <v>578</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>489</v>
+        <v>553</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -4656,41 +4745,41 @@
         <v>419</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>435</v>
+        <v>576</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>490</v>
+        <v>553</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G106" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G106" s="10" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
-        <v>101</v>
+        <v>172</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>103</v>
+        <v>173</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -4698,22 +4787,22 @@
       <c r="F107" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G107" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G107" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
-        <v>372</v>
+        <v>177</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>369</v>
+        <v>178</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>370</v>
+        <v>179</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>9</v>
+        <v>180</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -4721,19 +4810,19 @@
       <c r="F108" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G108" s="5" t="s">
-        <v>371</v>
+      <c r="G108" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>258</v>
@@ -4750,13 +4839,13 @@
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>134</v>
+        <v>432</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>140</v>
+        <v>487</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>137</v>
+        <v>464</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>9</v>
@@ -4768,18 +4857,18 @@
         <v>6</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>142</v>
+        <v>419</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>314</v>
+        <v>433</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>140</v>
+        <v>488</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>137</v>
+        <v>476</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>9</v>
@@ -4791,21 +4880,21 @@
         <v>6</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>303</v>
+        <v>419</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>322</v>
+        <v>434</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>324</v>
+        <v>489</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>325</v>
+        <v>469</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -4814,21 +4903,21 @@
         <v>6</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>323</v>
+        <v>419</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>274</v>
+        <v>435</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>275</v>
+        <v>490</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>277</v>
+        <v>457</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -4837,21 +4926,21 @@
         <v>6</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>302</v>
+        <v>101</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>275</v>
+        <v>102</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>277</v>
+        <v>103</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -4859,22 +4948,22 @@
       <c r="F114" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G114" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G114" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>470</v>
+        <v>372</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>277</v>
+        <v>370</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -4882,19 +4971,19 @@
       <c r="F115" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G115" s="2" t="s">
-        <v>419</v>
+      <c r="G115" s="5" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>530</v>
+        <v>397</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>275</v>
+        <v>401</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>277</v>
+        <v>400</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>258</v>
@@ -4905,22 +4994,22 @@
       <c r="F116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G116" s="2" t="s">
-        <v>531</v>
+      <c r="G116" s="5" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>424</v>
+        <v>134</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>478</v>
+        <v>140</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>468</v>
+        <v>137</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -4929,44 +5018,44 @@
         <v>6</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>544</v>
+        <v>314</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>478</v>
+        <v>140</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>536</v>
+        <v>137</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>537</v>
+        <v>11</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G118" s="5" t="s">
-        <v>538</v>
+      <c r="G118" s="2" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>183</v>
+        <v>322</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>184</v>
+        <v>325</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>25</v>
+        <v>258</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -4974,22 +5063,22 @@
       <c r="F119" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G119" s="5" t="s">
-        <v>185</v>
+      <c r="G119" s="2" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>406</v>
+        <v>274</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>407</v>
+        <v>275</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>408</v>
+        <v>277</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>409</v>
+        <v>258</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -4998,21 +5087,21 @@
         <v>6</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>388</v>
+        <v>276</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>124</v>
+        <v>302</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -5021,21 +5110,21 @@
         <v>6</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>128</v>
+        <v>303</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>226</v>
+        <v>470</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>122</v>
+        <v>275</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>123</v>
+        <v>277</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -5044,21 +5133,21 @@
         <v>6</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>224</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>436</v>
+        <v>530</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>491</v>
+        <v>275</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>471</v>
+        <v>277</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -5067,67 +5156,67 @@
         <v>6</v>
       </c>
       <c r="G123" s="2" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A124" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G124" s="2" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A124" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
-        <v>353</v>
+        <v>544</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>358</v>
+        <v>478</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>361</v>
+        <v>536</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>360</v>
+        <v>258</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>11</v>
+        <v>537</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G125" s="2" t="s">
-        <v>359</v>
+      <c r="G125" s="5" t="s">
+        <v>538</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>99</v>
+        <v>182</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>100</v>
+        <v>184</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>11</v>
@@ -5136,21 +5225,21 @@
         <v>6</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>104</v>
+        <v>185</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>437</v>
+        <v>406</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>492</v>
+        <v>407</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>472</v>
+        <v>408</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>9</v>
+        <v>409</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -5159,18 +5248,18 @@
         <v>6</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>419</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>438</v>
+        <v>124</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>493</v>
+        <v>122</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>475</v>
+        <v>123</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>9</v>
@@ -5182,21 +5271,21 @@
         <v>6</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>70</v>
+        <v>226</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>69</v>
+        <v>122</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -5204,19 +5293,19 @@
       <c r="F129" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G129" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G129" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>9</v>
@@ -5231,176 +5320,176 @@
         <v>419</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A132" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A133" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A134" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A135" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A136" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G136" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A137" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A138" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B138" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C131" s="2" t="s">
+      <c r="C138" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G131" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A132" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A133" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" ht="28" x14ac:dyDescent="0.15">
-      <c r="A134" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A135" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G135" s="5" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A136" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G136" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A137" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A138" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>75</v>
@@ -5411,19 +5500,19 @@
       <c r="F138" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G138" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G138" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>279</v>
+        <v>105</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>280</v>
+        <v>107</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>75</v>
@@ -5435,19 +5524,18 @@
         <v>6</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H139" s="2"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.15">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
-        <v>416</v>
+        <v>284</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>417</v>
+        <v>285</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>341</v>
+        <v>286</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>75</v>
@@ -5458,180 +5546,181 @@
       <c r="F140" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="G140" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="28" x14ac:dyDescent="0.15">
+      <c r="A141" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A142" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A143" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A144" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="14" x14ac:dyDescent="0.15">
+      <c r="A145" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H146" s="2"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A147" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" s="2" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A141" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G141" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A142" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A143" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A144" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A145" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A146" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D146" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A147" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
-        <v>551</v>
+        <v>600</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>455</v>
+        <v>601</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>602</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>9</v>
@@ -5643,21 +5732,21 @@
         <v>6</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.15">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
-        <v>227</v>
+        <v>399</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>232</v>
+        <v>402</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>236</v>
+        <v>405</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -5665,22 +5754,22 @@
       <c r="F149" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G149" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G149" s="5" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>540</v>
+        <v>315</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>541</v>
+        <v>317</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>543</v>
+        <v>316</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -5688,22 +5777,22 @@
       <c r="F150" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G150" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G150" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>195</v>
+        <v>76</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -5712,21 +5801,21 @@
         <v>6</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.15">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>298</v>
+        <v>154</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -5735,44 +5824,44 @@
         <v>6</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.15">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B153" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="C153" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D153" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="E153" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F153" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>514</v>
+        <v>77</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>516</v>
+        <v>78</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -5780,19 +5869,19 @@
       <c r="F154" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G154" s="5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G154" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>143</v>
+        <v>440</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>146</v>
+        <v>495</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>145</v>
+        <v>455</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -5803,19 +5892,19 @@
       <c r="F155" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G155" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G155" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>410</v>
+        <v>551</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>412</v>
+        <v>495</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>455</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>9</v>
@@ -5827,18 +5916,18 @@
         <v>6</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.15">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>87</v>
+        <v>227</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>88</v>
+        <v>232</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>89</v>
+        <v>236</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>9</v>
@@ -5850,21 +5939,21 @@
         <v>6</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
-        <v>200</v>
+        <v>540</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>88</v>
+        <v>541</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>89</v>
+        <v>543</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>9</v>
+        <v>258</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -5873,21 +5962,21 @@
         <v>6</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.15">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -5896,21 +5985,21 @@
         <v>6</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.15">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
-        <v>351</v>
+        <v>298</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>89</v>
+        <v>197</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>9</v>
+        <v>199</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -5919,44 +6008,44 @@
         <v>6</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B161" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F161" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="9" t="s">
         <v>6</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>217</v>
+        <v>535</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
-        <v>158</v>
+        <v>520</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>80</v>
+        <v>514</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>83</v>
+        <v>516</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -5964,22 +6053,22 @@
       <c r="F162" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G162" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G162" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>288</v>
+        <v>143</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -5987,22 +6076,22 @@
       <c r="F163" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G163" s="2" t="s">
-        <v>289</v>
+      <c r="G163" s="5" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>290</v>
+        <v>588</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>80</v>
+        <v>589</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>83</v>
+        <v>592</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -6011,21 +6100,21 @@
         <v>6</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>291</v>
+        <v>593</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>83</v>
+        <v>411</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>412</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -6034,21 +6123,21 @@
         <v>6</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -6057,21 +6146,21 @@
         <v>6</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.15">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -6079,22 +6168,22 @@
       <c r="F167" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G167" s="2" t="s">
-        <v>152</v>
+      <c r="G167" s="5" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -6103,21 +6192,21 @@
         <v>6</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -6126,21 +6215,21 @@
         <v>6</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>350</v>
+        <v>293</v>
       </c>
     </row>
     <row r="170" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>348</v>
+        <v>556</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -6149,21 +6238,21 @@
         <v>6</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>297</v>
+        <v>593</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
-        <v>512</v>
+        <v>583</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -6172,44 +6261,44 @@
         <v>6</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>218</v>
+        <v>581</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>513</v>
+        <v>79</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>75</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>395</v>
+        <v>217</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -6218,21 +6307,21 @@
         <v>6</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
-        <v>202</v>
+        <v>288</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -6241,21 +6330,21 @@
         <v>6</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>203</v>
+        <v>289</v>
       </c>
     </row>
     <row r="175" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
-        <v>510</v>
+        <v>290</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -6264,21 +6353,21 @@
         <v>6</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>511</v>
+        <v>291</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
-        <v>84</v>
+        <v>384</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>85</v>
+        <v>385</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -6287,21 +6376,21 @@
         <v>6</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>219</v>
+        <v>386</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
-        <v>282</v>
+        <v>81</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -6310,21 +6399,21 @@
         <v>6</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>283</v>
+        <v>218</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A178" s="2" t="s">
-        <v>441</v>
+        <v>151</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -6333,21 +6422,21 @@
         <v>6</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A179" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>149</v>
+        <v>345</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -6355,22 +6444,22 @@
       <c r="F179" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G179" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G179" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A180" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C180" s="6" t="s">
-        <v>221</v>
+        <v>349</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -6379,21 +6468,21 @@
         <v>6</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A181" s="2" t="s">
-        <v>135</v>
+        <v>348</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -6401,138 +6490,411 @@
       <c r="F181" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G181" s="2" t="s">
-        <v>142</v>
+      <c r="G181" s="5" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A182" s="2" t="s">
-        <v>318</v>
+        <v>512</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="D182" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A183" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A184" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A185" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A186" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A187" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="D187" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A188" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E182" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F182" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G182" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G183" s="5"/>
-    </row>
-    <row r="184" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="G184" s="5"/>
+      <c r="E188" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A189" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A190" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A191" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B191" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G191" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A192" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B192" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A193" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A194" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="C195" s="6"/>
+      <c r="G195" s="5"/>
+    </row>
+    <row r="196" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="B196" s="9"/>
+      <c r="C196" s="9"/>
+      <c r="D196" s="9"/>
+      <c r="E196" s="9"/>
+      <c r="F196" s="9"/>
+      <c r="G196" s="5"/>
+    </row>
+    <row r="197" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G197" s="5"/>
+    </row>
+    <row r="198" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G198" s="5"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A203" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B203" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="C203" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D190" s="2" t="s">
+      <c r="D203" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E190" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G190" s="2" t="s">
+      <c r="E203" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G203" s="2" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A195" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G195" s="2" t="s">
-        <v>581</v>
-      </c>
-    </row>
+    <row r="207" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H187">
-    <sortCondition ref="A65:A187"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H194">
+    <sortCondition ref="A194"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="G17" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G41" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G90" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G107" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G126" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G76" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G155" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G158" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G18" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
+    <hyperlink ref="G46" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G97" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G114" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G133" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G83" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G163" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G167" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G9" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G53" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G56" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G59" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G74" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G92" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G129" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G131" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G176" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G25" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G133" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G164" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G45" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G57" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G170" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G124" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G108" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G84" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G135" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G165" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
-    <hyperlink ref="G156" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
-    <hyperlink ref="G21" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
-    <hyperlink ref="G67" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
-    <hyperlink ref="G175" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
-    <hyperlink ref="G54" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
-    <hyperlink ref="G154" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
-    <hyperlink ref="G89" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
-    <hyperlink ref="G49" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
+    <hyperlink ref="G59" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G62" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G65" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G81" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G99" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G136" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G138" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G188" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G29" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G140" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G175" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G51" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G63" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G181" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G131" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G115" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G91" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G142" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G176" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G165" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
+    <hyperlink ref="G24" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
+    <hyperlink ref="G74" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
+    <hyperlink ref="G186" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
+    <hyperlink ref="G60" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
+    <hyperlink ref="G162" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
+    <hyperlink ref="G96" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
+    <hyperlink ref="G55" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
     <hyperlink ref="G7" r:id="rId38" xr:uid="{AD3618A6-5FE8-B940-9FEF-9FF5D1F662CA}"/>
-    <hyperlink ref="G150" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
-    <hyperlink ref="G50" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
-    <hyperlink ref="G46" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
-    <hyperlink ref="G118" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
-    <hyperlink ref="G97" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
-    <hyperlink ref="G61" r:id="rId44" xr:uid="{3E4AD335-D90F-8E4F-99D9-B5A29F73491A}"/>
-    <hyperlink ref="G136" r:id="rId45" xr:uid="{5496842B-F19F-F64D-AE34-576CA41371CE}"/>
-    <hyperlink ref="G93" r:id="rId46" xr:uid="{F15A6606-6F28-5141-8864-8E110DF5FF49}"/>
-    <hyperlink ref="G99" r:id="rId47" xr:uid="{2D5CC932-530B-3943-8E48-2E3B2B48A21A}"/>
+    <hyperlink ref="G158" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
+    <hyperlink ref="G56" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
+    <hyperlink ref="G52" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
+    <hyperlink ref="G125" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
+    <hyperlink ref="G104" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
+    <hyperlink ref="G67" r:id="rId44" xr:uid="{3E4AD335-D90F-8E4F-99D9-B5A29F73491A}"/>
+    <hyperlink ref="G143" r:id="rId45" xr:uid="{5496842B-F19F-F64D-AE34-576CA41371CE}"/>
+    <hyperlink ref="G100" r:id="rId46" xr:uid="{F15A6606-6F28-5141-8864-8E110DF5FF49}"/>
+    <hyperlink ref="G106" r:id="rId47" xr:uid="{2D5CC932-530B-3943-8E48-2E3B2B48A21A}"/>
+    <hyperlink ref="G170" r:id="rId48" xr:uid="{807DF35C-A240-BB4F-9F45-8193ACA2A798}"/>
+    <hyperlink ref="G17" r:id="rId49" xr:uid="{F012A175-E6BC-0248-BF34-CE8E37280780}"/>
+    <hyperlink ref="G164" r:id="rId50" xr:uid="{C4E26972-A711-6B47-A806-72736AA3275D}"/>
+    <hyperlink ref="G20" r:id="rId51" xr:uid="{63B81492-6338-8A4F-BCAA-75B0E6510CB1}"/>
+    <hyperlink ref="G69" r:id="rId52" xr:uid="{93A8D2A5-3A2B-3F42-A5B4-3172CA508BB8}"/>
+    <hyperlink ref="G22" r:id="rId53" xr:uid="{CAFBFC16-130B-7E40-9B56-BAB3FB4B3736}"/>
+    <hyperlink ref="G187" r:id="rId54" xr:uid="{1CE77970-0B87-8B4E-A6B0-6639D7FA5FD9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1933" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59A7CE26-E182-814E-A386-D271F36F4CB0}"/>
+  <xr:revisionPtr revIDLastSave="1948" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A42450C6-5566-694B-9DFB-361E3279E6DC}"/>
   <bookViews>
     <workbookView xWindow="-4380" yWindow="-21100" windowWidth="31320" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="615">
   <si>
     <t>Study_ID</t>
   </si>
@@ -171,9 +171,6 @@
     <t>Kentucky Arrow Darter</t>
   </si>
   <si>
-    <t>Etheostoma sagitta spilotum)</t>
-  </si>
-  <si>
     <t>ETSA-1</t>
   </si>
   <si>
@@ -1879,6 +1876,12 @@
   </si>
   <si>
     <t>COBA-3</t>
+  </si>
+  <si>
+    <t>CHSA-1</t>
+  </si>
+  <si>
+    <t>Clinch Dace</t>
   </si>
 </sst>
 </file>
@@ -1995,6 +1998,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2350,18 +2357,18 @@
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
@@ -2373,21 +2380,21 @@
         <v>6</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>308</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -2396,7 +2403,7 @@
         <v>6</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
@@ -2442,22 +2449,22 @@
         <v>6</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
@@ -2465,22 +2472,22 @@
         <v>6</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>238</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
@@ -2488,22 +2495,22 @@
         <v>6</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>11</v>
       </c>
@@ -2511,7 +2518,7 @@
         <v>6</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.15">
@@ -2522,7 +2529,7 @@
         <v>16</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -2534,18 +2541,18 @@
         <v>6</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>9</v>
@@ -2557,18 +2564,18 @@
         <v>6</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>9</v>
@@ -2580,18 +2587,18 @@
         <v>6</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>25</v>
@@ -2603,22 +2610,22 @@
         <v>6</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="E13" s="2" t="s">
         <v>11</v>
       </c>
@@ -2626,18 +2633,18 @@
         <v>6</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>25</v>
@@ -2649,18 +2656,18 @@
         <v>6</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>25</v>
@@ -2672,18 +2679,18 @@
         <v>6</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>9</v>
@@ -2695,21 +2702,21 @@
         <v>6</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>584</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>585</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>11</v>
@@ -2718,7 +2725,7 @@
         <v>6</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
@@ -2746,13 +2753,13 @@
     </row>
     <row r="19" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>25</v>
@@ -2764,21 +2771,21 @@
         <v>6</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>587</v>
-      </c>
       <c r="C20" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>11</v>
@@ -2787,18 +2794,18 @@
         <v>6</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>9</v>
@@ -2810,18 +2817,18 @@
         <v>6</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>9</v>
@@ -2832,272 +2839,272 @@
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="10" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A23" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A23" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="B23" s="2" t="s">
+      <c r="C23" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A24" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="C23" s="2" t="s">
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A25" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="C25" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A24" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A25" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="E25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>262</v>
+      <c r="G25" s="5" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A27" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A27" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G27" s="5" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A28" s="2" t="s">
         <v>612</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A28" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A29" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A30" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A32" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B32" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A29" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A31" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A32" s="2" t="s">
+      <c r="C32" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A33" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>611</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>610</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A33" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
-        <v>245</v>
+        <v>429</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>250</v>
+        <v>484</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>249</v>
+        <v>473</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>9</v>
@@ -3109,18 +3116,18 @@
         <v>6</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>253</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>9</v>
@@ -3132,18 +3139,18 @@
         <v>6</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>126</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>9</v>
@@ -3155,113 +3162,113 @@
         <v>6</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
-        <v>575</v>
+        <v>124</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G37" s="11" t="s">
+      <c r="F38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A39" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>569</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A38" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A39" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A40" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>419</v>
+      <c r="G40" s="5" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
-        <v>229</v>
+        <v>430</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>233</v>
+        <v>485</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>240</v>
+        <v>466</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>239</v>
+        <v>9</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>
@@ -3270,21 +3277,21 @@
         <v>6</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>224</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>352</v>
+        <v>228</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>356</v>
+        <v>232</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>357</v>
+        <v>239</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>30</v>
+        <v>238</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
@@ -3293,18 +3300,18 @@
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>355</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>442</v>
+        <v>351</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>496</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>454</v>
+        <v>356</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>30</v>
@@ -3316,18 +3323,18 @@
         <v>6</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>419</v>
+        <v>354</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>335</v>
+        <v>441</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>337</v>
+        <v>495</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>333</v>
+        <v>453</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>30</v>
@@ -3339,18 +3346,18 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>339</v>
+        <v>418</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>27</v>
+        <v>334</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>29</v>
+        <v>332</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>30</v>
@@ -3362,12 +3369,12 @@
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>33</v>
+        <v>338</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>28</v>
@@ -3384,15 +3391,15 @@
       <c r="F46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>32</v>
+      <c r="G46" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B47" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -3407,13 +3414,13 @@
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G47" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>28</v>
@@ -3430,15 +3437,15 @@
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G48" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B49" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -3454,64 +3461,64 @@
         <v>6</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>419</v>
+        <v>320</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A51" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A51" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>545</v>
+        <v>331</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>547</v>
+        <v>330</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>549</v>
+        <v>329</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
@@ -3523,18 +3530,18 @@
         <v>6</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.15">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>444</v>
+        <v>544</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>497</v>
+        <v>546</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>449</v>
+        <v>548</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
@@ -3545,19 +3552,19 @@
       <c r="F53" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G53" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>170</v>
+        <v>443</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>496</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>169</v>
+        <v>448</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>30</v>
@@ -3568,19 +3575,19 @@
       <c r="F54" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G54" s="5" t="s">
-        <v>171</v>
+      <c r="G54" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>526</v>
+        <v>167</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>562</v>
+        <v>168</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>30</v>
@@ -3592,18 +3599,18 @@
         <v>6</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>525</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>546</v>
+        <v>523</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>548</v>
+        <v>525</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>30</v>
@@ -3615,18 +3622,18 @@
         <v>6</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.15">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>445</v>
+        <v>545</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>498</v>
+        <v>547</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>456</v>
+        <v>549</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
@@ -3637,19 +3644,19 @@
       <c r="F57" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G57" s="2" t="s">
-        <v>419</v>
+      <c r="G57" s="5" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>241</v>
+        <v>444</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>242</v>
+        <v>497</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>243</v>
+        <v>455</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>30</v>
@@ -3661,18 +3668,18 @@
         <v>6</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>34</v>
+        <v>240</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>35</v>
+        <v>241</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>36</v>
+        <v>242</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>30</v>
@@ -3683,13 +3690,13 @@
       <c r="F59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>205</v>
+      <c r="G59" s="2" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>518</v>
+        <v>34</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>35</v>
@@ -3707,18 +3714,18 @@
         <v>6</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.15">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>188</v>
+        <v>517</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>30</v>
@@ -3729,19 +3736,19 @@
       <c r="F61" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="5" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A62" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B62" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A62" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="C62" s="2" t="s">
-        <v>39</v>
+        <v>189</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>30</v>
@@ -3752,19 +3759,19 @@
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="5" t="s">
-        <v>207</v>
+      <c r="G62" s="2" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>326</v>
+        <v>38</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>329</v>
+        <v>37</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>327</v>
+        <v>39</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>30</v>
@@ -3776,18 +3783,18 @@
         <v>6</v>
       </c>
       <c r="G63" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A64" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B64" s="2" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A64" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="C64" s="2" t="s">
-        <v>522</v>
+        <v>326</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>30</v>
@@ -3798,19 +3805,19 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G64" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>42</v>
+        <v>520</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>40</v>
+        <v>522</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>41</v>
+        <v>521</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>30</v>
@@ -3821,19 +3828,19 @@
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G65" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>30</v>
@@ -3844,42 +3851,42 @@
       <c r="F66" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G66" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="17" x14ac:dyDescent="0.15">
+      <c r="G66" s="5" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>517</v>
+        <v>44</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="10" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G67" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>561</v>
+        <v>516</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>30</v>
@@ -3890,42 +3897,42 @@
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="10" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A69" s="2" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A69" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="B69" s="2" t="s">
-        <v>595</v>
+        <v>43</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>597</v>
+        <v>562</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A70" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>596</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A70" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>30</v>
@@ -3936,19 +3943,19 @@
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="2" t="s">
-        <v>419</v>
+      <c r="G70" s="5" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>189</v>
+        <v>445</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>192</v>
+        <v>498</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>191</v>
+        <v>457</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>30</v>
@@ -3960,18 +3967,18 @@
         <v>6</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>193</v>
+        <v>418</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>246</v>
+        <v>188</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>247</v>
+        <v>190</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>30</v>
@@ -3983,18 +3990,18 @@
         <v>6</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>253</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>30</v>
@@ -4006,18 +4013,18 @@
         <v>6</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>507</v>
+        <v>251</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>508</v>
+        <v>247</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>509</v>
+        <v>246</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>30</v>
@@ -4028,19 +4035,19 @@
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G74" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="B75" s="6" t="s">
-        <v>338</v>
+        <v>506</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>334</v>
+        <v>508</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>30</v>
@@ -4051,19 +4058,19 @@
       <c r="F75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G75" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>500</v>
+        <v>335</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>337</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>463</v>
+        <v>333</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>30</v>
@@ -4075,21 +4082,21 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>419</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>11</v>
@@ -4098,21 +4105,21 @@
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>116</v>
+        <v>426</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>117</v>
+        <v>480</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>118</v>
+        <v>458</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -4120,160 +4127,160 @@
       <c r="F78" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G78" s="4" t="s">
-        <v>209</v>
+      <c r="G78" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>210</v>
+      <c r="G79" s="4" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="D80" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A81" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G80" s="2" t="s">
+      <c r="C81" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A82" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G82" s="5" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A81" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G81" s="5" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A82" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A84" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="C84" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C83" s="2" t="s">
+      <c r="D84" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D83" s="2" t="s">
+      <c r="E84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G84" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A84" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>133</v>
+        <v>447</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>139</v>
+        <v>500</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>136</v>
+        <v>465</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>9</v>
+        <v>420</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -4282,18 +4289,18 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>142</v>
+        <v>418</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>313</v>
+        <v>132</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>9</v>
@@ -4305,18 +4312,18 @@
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>303</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>56</v>
+        <v>312</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>54</v>
+        <v>138</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>9</v>
@@ -4328,18 +4335,18 @@
         <v>6</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>415</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>414</v>
+        <v>55</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>9</v>
@@ -4350,19 +4357,19 @@
       <c r="F88" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G88" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G88" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>59</v>
+        <v>412</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>413</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>9</v>
@@ -4373,19 +4380,19 @@
       <c r="F89" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>60</v>
+      <c r="G89" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>119</v>
+        <v>56</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>9</v>
@@ -4397,21 +4404,21 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>383</v>
+        <v>118</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="D91" s="2" t="s">
-        <v>373</v>
+        <v>9</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>11</v>
@@ -4419,22 +4426,22 @@
       <c r="F91" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G91" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>300</v>
+        <v>382</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>344</v>
+        <v>119</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>343</v>
+        <v>120</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>25</v>
+        <v>372</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -4442,22 +4449,22 @@
       <c r="F92" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G92" s="2" t="s">
-        <v>299</v>
+      <c r="G92" s="5" t="s">
+        <v>370</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>62</v>
+        <v>299</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>63</v>
+        <v>343</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>61</v>
+        <v>342</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -4466,45 +4473,45 @@
         <v>6</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>65</v>
+        <v>298</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D94" s="2" t="s">
+      <c r="E94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>228</v>
+        <v>90</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D95" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
       </c>
@@ -4512,159 +4519,159 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>527</v>
+        <v>227</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G96" s="5" t="s">
-        <v>528</v>
+      <c r="G96" s="2" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A98" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="C98" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C97" s="2" t="s">
+      <c r="D98" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="E98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G98" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G97" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A98" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="C98" s="2" t="s">
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A99" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G98" s="2" t="s">
+      <c r="C99" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A99" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G99" s="5" t="s">
-        <v>214</v>
+      <c r="G99" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>577</v>
+        <v>65</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>571</v>
+        <v>66</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G100" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A101" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G101" s="5" t="s">
         <v>568</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G100" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A101" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>502</v>
+        <v>224</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>258</v>
+        <v>21</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -4673,182 +4680,182 @@
         <v>6</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>419</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A104" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A105" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G103" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A104" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B104" s="2" t="s">
+      <c r="C105" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G105" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="C104" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G104" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A105" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="17" x14ac:dyDescent="0.15">
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.15">
+      <c r="A107" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G106" s="10" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A107" s="2" t="s">
+      <c r="F107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="C108" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="D108" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D107" s="2" t="s">
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A109" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A108" s="2" t="s">
+      <c r="B109" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="C109" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C108" s="2" t="s">
+      <c r="D109" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D108" s="2" t="s">
+      <c r="E109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A109" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="B109" s="2" t="s">
+    </row>
+    <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A110" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A110" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>464</v>
-      </c>
       <c r="D110" s="2" t="s">
-        <v>9</v>
+        <v>257</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -4856,19 +4863,19 @@
       <c r="F110" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G110" s="2" t="s">
-        <v>419</v>
+      <c r="G110" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>476</v>
+        <v>463</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>9</v>
@@ -4880,18 +4887,18 @@
         <v>6</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>9</v>
@@ -4903,18 +4910,18 @@
         <v>6</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>9</v>
@@ -4926,18 +4933,18 @@
         <v>6</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>101</v>
+        <v>434</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>102</v>
+        <v>489</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>103</v>
+        <v>456</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>9</v>
@@ -4948,19 +4955,19 @@
       <c r="F114" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G114" s="5" t="s">
-        <v>104</v>
+      <c r="G114" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>372</v>
+        <v>100</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>369</v>
+        <v>101</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>370</v>
+        <v>102</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>9</v>
@@ -4972,44 +4979,44 @@
         <v>6</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>371</v>
+        <v>103</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>401</v>
+        <v>368</v>
       </c>
       <c r="C116" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G116" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A117" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G116" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A117" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="C117" s="2" t="s">
-        <v>137</v>
+        <v>399</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>9</v>
+        <v>257</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -5017,19 +5024,19 @@
       <c r="F117" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G117" s="2" t="s">
-        <v>142</v>
+      <c r="G117" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>314</v>
+        <v>133</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>9</v>
@@ -5041,21 +5048,21 @@
         <v>6</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>303</v>
+        <v>141</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>324</v>
+        <v>139</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>325</v>
+        <v>136</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -5064,21 +5071,21 @@
         <v>6</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>274</v>
+        <v>321</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -5087,44 +5094,44 @@
         <v>6</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G121" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D121" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>470</v>
+        <v>301</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -5133,21 +5140,21 @@
         <v>6</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>419</v>
+        <v>302</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>530</v>
+        <v>469</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -5156,21 +5163,21 @@
         <v>6</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>531</v>
+        <v>418</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>424</v>
+        <v>529</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>478</v>
+        <v>274</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>468</v>
+        <v>276</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -5179,67 +5186,67 @@
         <v>6</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
-        <v>544</v>
+        <v>423</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>536</v>
+        <v>467</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>537</v>
+        <v>11</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G125" s="5" t="s">
-        <v>538</v>
+      <c r="G125" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>183</v>
+        <v>543</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>477</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>184</v>
+        <v>535</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>25</v>
+        <v>257</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>11</v>
+        <v>536</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>185</v>
+        <v>537</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>407</v>
+        <v>181</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>182</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>408</v>
+        <v>183</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>409</v>
+        <v>25</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -5247,22 +5254,22 @@
       <c r="F127" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G127" s="2" t="s">
-        <v>388</v>
+      <c r="G127" s="5" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
-        <v>124</v>
+        <v>405</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>122</v>
+        <v>406</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>123</v>
+        <v>407</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>9</v>
+        <v>408</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -5271,18 +5278,18 @@
         <v>6</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>128</v>
+        <v>387</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
-        <v>226</v>
+        <v>123</v>
       </c>
       <c r="B129" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C129" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>9</v>
@@ -5294,18 +5301,18 @@
         <v>6</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>224</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
-        <v>436</v>
+        <v>225</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>491</v>
+        <v>121</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>471</v>
+        <v>122</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>9</v>
@@ -5317,18 +5324,18 @@
         <v>6</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>367</v>
+        <v>490</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>368</v>
+        <v>470</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>9</v>
@@ -5339,65 +5346,65 @@
       <c r="F131" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G131" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G131" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G132" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A133" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A133" s="2" t="s">
+    </row>
+    <row r="134" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A134" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="C134" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C133" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G133" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A134" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>9</v>
@@ -5408,19 +5415,19 @@
       <c r="F134" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G134" s="2" t="s">
-        <v>419</v>
+      <c r="G134" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>9</v>
@@ -5432,159 +5439,159 @@
         <v>6</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A137" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C137" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C136" s="2" t="s">
+      <c r="D137" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A138" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A139" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G136" s="5" t="s">
+      <c r="B139" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G139" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A137" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A138" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C138" s="2" t="s">
+    <row r="140" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="A140" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D138" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G138" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A139" s="2" t="s">
+      <c r="E140" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G140" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B139" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A140" s="2" t="s">
+    </row>
+    <row r="141" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A141" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="C141" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C140" s="2" t="s">
+      <c r="D141" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G141" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G140" s="5" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="28" x14ac:dyDescent="0.15">
-      <c r="A141" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B141" s="6" t="s">
+    </row>
+    <row r="142" spans="1:7" ht="28" x14ac:dyDescent="0.15">
+      <c r="A142" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C141" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A142" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="D142" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -5592,22 +5599,22 @@
       <c r="F142" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G142" s="5" t="s">
-        <v>382</v>
+      <c r="G142" s="2" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
-        <v>557</v>
+        <v>380</v>
       </c>
       <c r="B143" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C143" s="2" t="s">
-        <v>286</v>
-      </c>
       <c r="D143" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -5616,67 +5623,67 @@
         <v>6</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.15">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A145" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="C145" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G145" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" ht="14" x14ac:dyDescent="0.15">
-      <c r="A145" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>279</v>
+        <v>339</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>341</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -5685,68 +5692,68 @@
         <v>6</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H146" s="2"/>
+        <v>291</v>
+      </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H147" s="2"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A148" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C148" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G148" s="2" t="s">
         <v>417</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D147" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" ht="16" x14ac:dyDescent="0.15">
-      <c r="A148" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G148" s="5" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
-        <v>399</v>
+        <v>599</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>405</v>
+        <v>600</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>601</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>258</v>
+        <v>9</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -5755,21 +5762,21 @@
         <v>6</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>387</v>
+        <v>580</v>
       </c>
     </row>
     <row r="150" spans="1:8" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
-        <v>315</v>
+        <v>398</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>317</v>
+        <v>401</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>316</v>
+        <v>404</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -5777,22 +5784,22 @@
       <c r="F150" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G150" s="2" t="s">
-        <v>303</v>
+      <c r="G150" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
-        <v>76</v>
+        <v>314</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>77</v>
+        <v>316</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>30</v>
+        <v>311</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -5801,18 +5808,18 @@
         <v>6</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>131</v>
+        <v>302</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
-        <v>154</v>
+        <v>75</v>
       </c>
       <c r="B152" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>30</v>
@@ -5824,18 +5831,18 @@
         <v>6</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>153</v>
+        <v>130</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>30</v>
@@ -5847,18 +5854,18 @@
         <v>6</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
-        <v>532</v>
+        <v>186</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>30</v>
@@ -5870,21 +5877,21 @@
         <v>6</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>533</v>
+        <v>185</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
-        <v>440</v>
+        <v>531</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>495</v>
+        <v>76</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -5893,18 +5900,18 @@
         <v>6</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
-        <v>551</v>
+        <v>439</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>9</v>
@@ -5915,19 +5922,19 @@
       <c r="F156" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G156" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="G156" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="16" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
-        <v>227</v>
+        <v>550</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>232</v>
+        <v>494</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>236</v>
+        <v>454</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>9</v>
@@ -5938,137 +5945,137 @@
       <c r="F157" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G157" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="G157" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="16" x14ac:dyDescent="0.15">
+      <c r="A159" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="C159" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G159" s="5" t="s">
         <v>541</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A159" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D159" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E159" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
-        <v>298</v>
+        <v>194</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="D160" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G160" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="B161" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C161" s="9" t="s">
-        <v>197</v>
-      </c>
-      <c r="D161" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="E161" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F161" s="9" t="s">
+      <c r="D161" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F161" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>535</v>
+        <v>298</v>
       </c>
     </row>
     <row r="162" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="B162" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>515</v>
+        <v>533</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="163" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
-        <v>143</v>
+        <v>519</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>146</v>
+        <v>513</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>145</v>
+        <v>515</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -6077,18 +6084,18 @@
         <v>6</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>144</v>
+        <v>514</v>
       </c>
     </row>
     <row r="164" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
-        <v>588</v>
+        <v>142</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>589</v>
+        <v>145</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>592</v>
+        <v>144</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>9</v>
@@ -6100,18 +6107,18 @@
         <v>6</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>593</v>
+        <v>143</v>
       </c>
     </row>
     <row r="165" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
-        <v>410</v>
+        <v>587</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>412</v>
+        <v>588</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>591</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>9</v>
@@ -6123,18 +6130,18 @@
         <v>6</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.15">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
-        <v>87</v>
+        <v>409</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>89</v>
+        <v>410</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>411</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>9</v>
@@ -6145,19 +6152,19 @@
       <c r="F166" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G166" s="2" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G166" s="5" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
-        <v>200</v>
+        <v>86</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>9</v>
@@ -6168,19 +6175,19 @@
       <c r="F167" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G167" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G167" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
-        <v>294</v>
+        <v>199</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>9</v>
@@ -6191,19 +6198,19 @@
       <c r="F168" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G168" s="2" t="s">
-        <v>303</v>
+      <c r="G168" s="5" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
-        <v>351</v>
+        <v>293</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>9</v>
@@ -6215,18 +6222,18 @@
         <v>6</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
-        <v>556</v>
+        <v>350</v>
       </c>
       <c r="B170" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C170" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>9</v>
@@ -6237,19 +6244,19 @@
       <c r="F170" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G170" s="5" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G170" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>9</v>
@@ -6260,114 +6267,114 @@
       <c r="F171" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G171" s="2" t="s">
-        <v>581</v>
+      <c r="G171" s="5" t="s">
+        <v>592</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
-        <v>79</v>
+        <v>582</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>75</v>
+        <v>9</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>217</v>
+        <v>580</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>159</v>
+        <v>216</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A175" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G175" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F174" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G174" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A175" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B175" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="176" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
-        <v>384</v>
+        <v>289</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>385</v>
+        <v>79</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -6376,21 +6383,21 @@
         <v>6</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>386</v>
+        <v>290</v>
       </c>
     </row>
     <row r="177" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
-        <v>81</v>
+        <v>383</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C177" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D177" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -6398,22 +6405,22 @@
       <c r="F177" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G177" s="2" t="s">
-        <v>218</v>
+      <c r="G177" s="5" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A178" s="2" t="s">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -6422,21 +6429,21 @@
         <v>6</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>152</v>
+        <v>217</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A179" s="2" t="s">
-        <v>345</v>
+        <v>150</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -6445,21 +6452,21 @@
         <v>6</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>301</v>
+        <v>151</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A180" s="2" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -6468,21 +6475,21 @@
         <v>6</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A181" s="2" t="s">
         <v>348</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -6490,22 +6497,22 @@
       <c r="F181" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G181" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G181" s="2" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A182" s="2" t="s">
-        <v>512</v>
+        <v>347</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -6513,22 +6520,22 @@
       <c r="F182" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G182" s="2" t="s">
-        <v>218</v>
+      <c r="G182" s="5" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="183" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A183" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -6537,21 +6544,21 @@
         <v>6</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>395</v>
+        <v>217</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A184" s="2" t="s">
-        <v>155</v>
+        <v>512</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -6560,18 +6567,18 @@
         <v>6</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>153</v>
+        <v>394</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A185" s="2" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>30</v>
@@ -6583,18 +6590,18 @@
         <v>6</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A186" s="2" t="s">
-        <v>510</v>
+        <v>201</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>157</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>30</v>
@@ -6605,62 +6612,62 @@
       <c r="F186" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G186" s="5" t="s">
-        <v>511</v>
+      <c r="G186" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="187" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A187" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="B187" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C187" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D187" s="9" t="s">
+      <c r="D187" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E187" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F187" s="9" t="s">
+      <c r="E187" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F187" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G187" s="5" t="s">
-        <v>608</v>
+        <v>510</v>
       </c>
     </row>
     <row r="188" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A188" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C188" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D188" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F188" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A189" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B189" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G188" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A189" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>17</v>
@@ -6674,16 +6681,16 @@
       <c r="F189" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G189" s="2" t="s">
-        <v>283</v>
+      <c r="G189" s="5" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A190" s="2" t="s">
-        <v>441</v>
+        <v>281</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>17</v>
@@ -6698,18 +6705,18 @@
         <v>6</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A191" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>149</v>
+        <v>440</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>84</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>9</v>
@@ -6720,19 +6727,19 @@
       <c r="F191" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G191" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G191" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A192" s="2" t="s">
-        <v>220</v>
+        <v>146</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>221</v>
+        <v>148</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>9</v>
@@ -6743,19 +6750,19 @@
       <c r="F192" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G192" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G192" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A193" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>138</v>
+        <v>219</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>220</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>9</v>
@@ -6767,18 +6774,18 @@
         <v>6</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>142</v>
+        <v>222</v>
       </c>
     </row>
     <row r="194" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A194" s="2" t="s">
-        <v>318</v>
+        <v>134</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>9</v>
@@ -6790,12 +6797,31 @@
         <v>6</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="C195" s="6"/>
-      <c r="G195" s="5"/>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A195" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="196" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="B196" s="9"/>
@@ -6809,20 +6835,20 @@
       <c r="G197" s="5"/>
     </row>
     <row r="198" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G198" s="5"/>
+      <c r="G198" s="10"/>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A203" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -6831,70 +6857,71 @@
         <v>6</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="207" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H194">
-    <sortCondition ref="A194"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H195">
+    <sortCondition ref="A195"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G18" r:id="rId1" xr:uid="{653DA17D-ECDD-E64B-9D03-571B884756B4}"/>
-    <hyperlink ref="G46" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
-    <hyperlink ref="G97" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
-    <hyperlink ref="G114" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
-    <hyperlink ref="G133" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
-    <hyperlink ref="G83" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
-    <hyperlink ref="G163" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
-    <hyperlink ref="G167" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
+    <hyperlink ref="G47" r:id="rId2" xr:uid="{31E17336-E2E8-2F49-8F8B-E195A587BAA9}"/>
+    <hyperlink ref="G98" r:id="rId3" xr:uid="{5598D5A2-B846-4341-8CC5-3BA0C26428CD}"/>
+    <hyperlink ref="G115" r:id="rId4" xr:uid="{3775BD46-0CD1-604F-9850-77C620BB00C0}"/>
+    <hyperlink ref="G134" r:id="rId5" xr:uid="{D0537993-EF32-2F42-8C3B-EFE38D49B5E4}"/>
+    <hyperlink ref="G84" r:id="rId6" xr:uid="{F822A05A-201B-F945-A82A-A39B82C78917}"/>
+    <hyperlink ref="G164" r:id="rId7" xr:uid="{6908E0B1-BE8B-6049-BDD3-F9314D3CAFEF}"/>
+    <hyperlink ref="G168" r:id="rId8" xr:uid="{4334E89A-EE38-6540-BF10-0B0939AAA4EA}"/>
     <hyperlink ref="G5" r:id="rId9" display="NA. thesis" xr:uid="{4766B83D-750C-9044-AE2E-68AD813ED619}"/>
     <hyperlink ref="G9" r:id="rId10" xr:uid="{C04E52B1-839A-7B4D-A64A-4C8A8B08D3BB}"/>
-    <hyperlink ref="G59" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
-    <hyperlink ref="G62" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
-    <hyperlink ref="G65" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
-    <hyperlink ref="G81" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
-    <hyperlink ref="G99" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
-    <hyperlink ref="G136" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
-    <hyperlink ref="G138" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
-    <hyperlink ref="G188" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
-    <hyperlink ref="G29" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
-    <hyperlink ref="G140" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
-    <hyperlink ref="G175" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
-    <hyperlink ref="G51" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
-    <hyperlink ref="G63" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
-    <hyperlink ref="G181" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
-    <hyperlink ref="G131" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
-    <hyperlink ref="G115" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
-    <hyperlink ref="G91" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
-    <hyperlink ref="G142" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
-    <hyperlink ref="G176" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
-    <hyperlink ref="G165" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
-    <hyperlink ref="G24" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
-    <hyperlink ref="G74" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
-    <hyperlink ref="G186" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
-    <hyperlink ref="G60" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
-    <hyperlink ref="G162" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
-    <hyperlink ref="G96" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
-    <hyperlink ref="G55" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
+    <hyperlink ref="G60" r:id="rId11" display="NA. thesis" xr:uid="{CE883A11-8D18-004E-ABF8-9A1C3CDE3773}"/>
+    <hyperlink ref="G63" r:id="rId12" xr:uid="{301A07C8-41EC-9943-A8FC-5AEDBD63E34F}"/>
+    <hyperlink ref="G66" r:id="rId13" xr:uid="{34501B1F-FC38-3A42-89CB-C4B440537808}"/>
+    <hyperlink ref="G82" r:id="rId14" xr:uid="{E75939BE-2BD9-D84A-BF82-329182376E47}"/>
+    <hyperlink ref="G100" r:id="rId15" xr:uid="{7619F626-D672-AA49-8CF2-CA3D5A9C4703}"/>
+    <hyperlink ref="G137" r:id="rId16" xr:uid="{5A620DBA-0B54-F24F-BB85-A412271FD7FF}"/>
+    <hyperlink ref="G139" r:id="rId17" xr:uid="{9960F6EC-AE6D-EE40-B413-9EFC8A88AB7B}"/>
+    <hyperlink ref="G189" r:id="rId18" xr:uid="{23829EAF-44FD-1A47-B2CF-1517ACB7DBBD}"/>
+    <hyperlink ref="G30" r:id="rId19" xr:uid="{D5CBD137-60D4-F748-ACDC-BE9CF60E1BF5}"/>
+    <hyperlink ref="G141" r:id="rId20" xr:uid="{2BA80289-B059-DD4E-9721-5085C5988E7C}"/>
+    <hyperlink ref="G176" r:id="rId21" xr:uid="{25624964-74EA-F744-94A0-EAF08F4C9B9F}"/>
+    <hyperlink ref="G52" r:id="rId22" xr:uid="{1D458B8A-61C7-8B49-8DD7-D81EDB7EC526}"/>
+    <hyperlink ref="G64" r:id="rId23" xr:uid="{6D283718-EEAC-4241-ACFA-A3FB20DADD1E}"/>
+    <hyperlink ref="G182" r:id="rId24" xr:uid="{C7952A8A-1DEE-2747-9C76-8ED36FC2366D}"/>
+    <hyperlink ref="G132" r:id="rId25" xr:uid="{73E0D5A0-48EB-F848-8E02-D658780A1984}"/>
+    <hyperlink ref="G116" r:id="rId26" xr:uid="{C0999421-AD4C-D44B-B8CF-1E7C3A873C87}"/>
+    <hyperlink ref="G92" r:id="rId27" xr:uid="{1FD295C2-D13C-D344-9965-FEC7D4A94A8C}"/>
+    <hyperlink ref="G143" r:id="rId28" xr:uid="{64B082E3-A39C-6D40-B0E8-44D5ADCC5635}"/>
+    <hyperlink ref="G177" r:id="rId29" xr:uid="{34C9D55D-4DC1-9642-AAB9-3FAA16999FCD}"/>
+    <hyperlink ref="G166" r:id="rId30" xr:uid="{6D859D4A-21C9-774C-9D70-F02F54E7E39E}"/>
+    <hyperlink ref="G25" r:id="rId31" xr:uid="{999B637D-D2C8-9B49-8515-B8E71683067F}"/>
+    <hyperlink ref="G75" r:id="rId32" xr:uid="{27E76403-C5A2-A145-9E85-98BCB0231D6D}"/>
+    <hyperlink ref="G187" r:id="rId33" xr:uid="{078C11FC-E393-9240-B17A-38D2FB95C73B}"/>
+    <hyperlink ref="G61" r:id="rId34" xr:uid="{0DA9D85C-D48A-114C-B5E5-DEC7D9A4DCA9}"/>
+    <hyperlink ref="G163" r:id="rId35" xr:uid="{B29CE641-4E96-DD43-8694-76C303FADA42}"/>
+    <hyperlink ref="G97" r:id="rId36" xr:uid="{BBFECD96-6543-3148-8844-C304E2107938}"/>
+    <hyperlink ref="G56" r:id="rId37" xr:uid="{536B0D2E-ED55-C647-A7A0-C90FFAA6DDCB}"/>
     <hyperlink ref="G7" r:id="rId38" xr:uid="{AD3618A6-5FE8-B940-9FEF-9FF5D1F662CA}"/>
-    <hyperlink ref="G158" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
-    <hyperlink ref="G56" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
-    <hyperlink ref="G52" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
-    <hyperlink ref="G125" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
-    <hyperlink ref="G104" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
-    <hyperlink ref="G67" r:id="rId44" xr:uid="{3E4AD335-D90F-8E4F-99D9-B5A29F73491A}"/>
-    <hyperlink ref="G143" r:id="rId45" xr:uid="{5496842B-F19F-F64D-AE34-576CA41371CE}"/>
-    <hyperlink ref="G100" r:id="rId46" xr:uid="{F15A6606-6F28-5141-8864-8E110DF5FF49}"/>
-    <hyperlink ref="G106" r:id="rId47" xr:uid="{2D5CC932-530B-3943-8E48-2E3B2B48A21A}"/>
-    <hyperlink ref="G170" r:id="rId48" xr:uid="{807DF35C-A240-BB4F-9F45-8193ACA2A798}"/>
+    <hyperlink ref="G159" r:id="rId39" xr:uid="{94D8FB7E-9FBF-CA47-A575-A519506F98BF}"/>
+    <hyperlink ref="G57" r:id="rId40" xr:uid="{7836BFAB-C842-974A-9AA5-D2D4E0125F75}"/>
+    <hyperlink ref="G53" r:id="rId41" xr:uid="{9CF6CB66-035E-BC49-89FC-3C30D76AA37A}"/>
+    <hyperlink ref="G126" r:id="rId42" xr:uid="{01BBBD47-DC62-6A48-95F3-E2D376617271}"/>
+    <hyperlink ref="G105" r:id="rId43" xr:uid="{0F583B35-295B-8849-9968-F0978B7EE123}"/>
+    <hyperlink ref="G68" r:id="rId44" xr:uid="{3E4AD335-D90F-8E4F-99D9-B5A29F73491A}"/>
+    <hyperlink ref="G144" r:id="rId45" xr:uid="{5496842B-F19F-F64D-AE34-576CA41371CE}"/>
+    <hyperlink ref="G101" r:id="rId46" xr:uid="{F15A6606-6F28-5141-8864-8E110DF5FF49}"/>
+    <hyperlink ref="G107" r:id="rId47" xr:uid="{2D5CC932-530B-3943-8E48-2E3B2B48A21A}"/>
+    <hyperlink ref="G171" r:id="rId48" xr:uid="{807DF35C-A240-BB4F-9F45-8193ACA2A798}"/>
     <hyperlink ref="G17" r:id="rId49" xr:uid="{F012A175-E6BC-0248-BF34-CE8E37280780}"/>
-    <hyperlink ref="G164" r:id="rId50" xr:uid="{C4E26972-A711-6B47-A806-72736AA3275D}"/>
+    <hyperlink ref="G165" r:id="rId50" xr:uid="{C4E26972-A711-6B47-A806-72736AA3275D}"/>
     <hyperlink ref="G20" r:id="rId51" xr:uid="{63B81492-6338-8A4F-BCAA-75B0E6510CB1}"/>
-    <hyperlink ref="G69" r:id="rId52" xr:uid="{93A8D2A5-3A2B-3F42-A5B4-3172CA508BB8}"/>
-    <hyperlink ref="G22" r:id="rId53" xr:uid="{CAFBFC16-130B-7E40-9B56-BAB3FB4B3736}"/>
-    <hyperlink ref="G187" r:id="rId54" xr:uid="{1CE77970-0B87-8B4E-A6B0-6639D7FA5FD9}"/>
+    <hyperlink ref="G70" r:id="rId52" xr:uid="{93A8D2A5-3A2B-3F42-A5B4-3172CA508BB8}"/>
+    <hyperlink ref="G23" r:id="rId53" xr:uid="{CAFBFC16-130B-7E40-9B56-BAB3FB4B3736}"/>
+    <hyperlink ref="G188" r:id="rId54" xr:uid="{1CE77970-0B87-8B4E-A6B0-6639D7FA5FD9}"/>
+    <hyperlink ref="G22" r:id="rId55" xr:uid="{DFD95C1E-FC0B-974F-8085-03A463DF293B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -6911,30 +6938,30 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">

--- a/Objective 2/Data/Study_metadata.xlsx
+++ b/Objective 2/Data/Study_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://buckeyemailosu-my.sharepoint.com/personal/mccall_257_buckeyemail_osu_edu/Documents/Spring_2026/Landgen_DGS/DGS-Patterns-of-Fish-Diversity/DGS-Patterns-of-Fish-Diversity/Objective 2/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1948" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A42450C6-5566-694B-9DFB-361E3279E6DC}"/>
+  <xr:revisionPtr revIDLastSave="1989" documentId="8_{D0FE9348-49AB-D84F-A51D-D9F26EF9DB58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{970E2C84-C410-B74A-B857-279925277A46}"/>
   <bookViews>
     <workbookView xWindow="-4380" yWindow="-21100" windowWidth="31320" windowHeight="21100" xr2:uid="{BFE04C59-CE9B-744B-B3FF-DA35D679F80E}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="624">
   <si>
     <t>Study_ID</t>
   </si>
@@ -1882,6 +1882,33 @@
   </si>
   <si>
     <t>Clinch Dace</t>
+  </si>
+  <si>
+    <t>CYLU-3</t>
+  </si>
+  <si>
+    <t>doi:10.1111/j.1365-2427.2011.02709.x</t>
+  </si>
+  <si>
+    <t>ETBL-2</t>
+  </si>
+  <si>
+    <t>DOI 10.1007/s10592-008-9627-9</t>
+  </si>
+  <si>
+    <t>ETBL-3</t>
+  </si>
+  <si>
+    <t>ETBL-4</t>
+  </si>
+  <si>
+    <t>ETBL-5</t>
+  </si>
+  <si>
+    <t>SAFO-9</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10592-021-01404-8</t>
   </si>
 </sst>
 </file>
@@ -2321,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3D815D-5E91-F643-AF9A-1DD227761228}">
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H213"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="2" customWidth="1"/>
@@ -3213,85 +3240,85 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A40" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B40" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="2" t="s">
+      <c r="E40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.15">
-      <c r="A40" s="2" t="s">
+    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="A41" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B41" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C41" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.15">
-      <c r="A41" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G41" s="2" t="s">
-        <v>418</v>
+      <c r="G41" s="5" t="s">
+        <v>568</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
-        <v>228</v>
+        <v>430</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>232</v>
+        <v>485</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>239</v>
+        <v>466</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>238</v>
+        <v>9</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>11</v>
@@ -3300,21 +3327,21 @@
         <v>6</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>223</v>
+        <v>418</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
-        <v>351</v>
+        <v>228</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>355</v>
+        <v>232</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>356</v>
+        <v>239</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>30</v>
+        <v>238</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>11</v>
@@ -3323,18 +3350,18 @@
         <v>6</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>354</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
-        <v>441</v>
+        <v>351</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>495</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>453</v>
+        <v>356</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>30</v>
@@ -3346,18 +3373,18 @@
         <v>6</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>418</v>
+        <v>354</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
-        <v>334</v>
+        <v>441</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>336</v>
+        <v>495</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>332</v>
+        <v>453</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>30</v>
@@ -3369,18 +3396,18 @@
         <v>6</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.15">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
-        <v>27</v>
+        <v>617</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>28</v>
+        <v>495</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>29</v>
+        <v>453</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>30</v>
@@ -3391,19 +3418,19 @@
       <c r="F46" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>33</v>
+      <c r="G46" s="10" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
-        <v>31</v>
+        <v>619</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>28</v>
+        <v>495</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>29</v>
+        <v>453</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>30</v>
@@ -3414,19 +3441,19 @@
       <c r="F47" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G47" s="10" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>28</v>
+        <v>620</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>29</v>
+        <v>453</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>30</v>
@@ -3437,19 +3464,19 @@
       <c r="F48" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G48" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+      <c r="G48" s="10" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>28</v>
+        <v>621</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>29</v>
+        <v>453</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>30</v>
@@ -3460,19 +3487,19 @@
       <c r="F49" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G49" s="2" t="s">
-        <v>320</v>
+      <c r="G49" s="10" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
-        <v>442</v>
+        <v>334</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>29</v>
+        <v>332</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>30</v>
@@ -3484,41 +3511,41 @@
         <v>6</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>418</v>
+        <v>338</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="B51" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="9" t="s">
+      <c r="C51" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D51" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E51" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="9" t="s">
+      <c r="E51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
-        <v>331</v>
+        <v>31</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>330</v>
+        <v>28</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>329</v>
+        <v>29</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>30</v>
@@ -3529,19 +3556,19 @@
       <c r="F52" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G52" s="5" t="s">
-        <v>327</v>
+      <c r="G52" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>546</v>
+        <v>165</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>548</v>
+        <v>29</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>30</v>
@@ -3553,18 +3580,18 @@
         <v>6</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.15">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>496</v>
+        <v>319</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>448</v>
+        <v>29</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>30</v>
@@ -3576,18 +3603,18 @@
         <v>6</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>169</v>
+        <v>442</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>30</v>
@@ -3598,42 +3625,42 @@
       <c r="F55" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G55" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="D56" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>524</v>
+      <c r="E56" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>598</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
-        <v>545</v>
+        <v>331</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>547</v>
+        <v>330</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>549</v>
+        <v>329</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>30</v>
@@ -3645,18 +3672,18 @@
         <v>6</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.15">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
-        <v>444</v>
+        <v>544</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>497</v>
+        <v>546</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>455</v>
+        <v>548</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>30</v>
@@ -3667,19 +3694,19 @@
       <c r="F58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>418</v>
+      <c r="G58" s="5" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
-        <v>240</v>
+        <v>443</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>241</v>
+        <v>496</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>242</v>
+        <v>448</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>30</v>
@@ -3691,18 +3718,18 @@
         <v>6</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>243</v>
+        <v>418</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>35</v>
+        <v>167</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>36</v>
+        <v>168</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>30</v>
@@ -3714,18 +3741,18 @@
         <v>6</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>35</v>
+        <v>525</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>36</v>
+        <v>561</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>30</v>
@@ -3737,18 +3764,18 @@
         <v>6</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.15">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
-        <v>187</v>
+        <v>545</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>193</v>
+        <v>547</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>189</v>
+        <v>549</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>30</v>
@@ -3759,19 +3786,19 @@
       <c r="F62" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G62" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G62" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
-        <v>38</v>
+        <v>444</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>37</v>
+        <v>497</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>39</v>
+        <v>455</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>30</v>
@@ -3782,19 +3809,19 @@
       <c r="F63" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G63" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
-        <v>325</v>
+        <v>240</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>328</v>
+        <v>241</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>326</v>
+        <v>242</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>30</v>
@@ -3805,19 +3832,19 @@
       <c r="F64" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G64" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G64" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
-        <v>520</v>
+        <v>34</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>522</v>
+        <v>35</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>521</v>
+        <v>36</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>30</v>
@@ -3828,19 +3855,19 @@
       <c r="F65" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>389</v>
+      <c r="G65" s="5" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
-        <v>42</v>
+        <v>517</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>30</v>
@@ -3852,18 +3879,18 @@
         <v>6</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>207</v>
+        <v>518</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>43</v>
+        <v>193</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>562</v>
+        <v>189</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>30</v>
@@ -3874,65 +3901,65 @@
       <c r="F67" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.15">
+      <c r="G67" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
-        <v>516</v>
+        <v>38</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>562</v>
+        <v>39</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G68" s="10" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G68" s="5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
-        <v>560</v>
+        <v>325</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>43</v>
+        <v>328</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>562</v>
+        <v>326</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G69" s="4" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G69" s="5" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
-        <v>593</v>
+        <v>520</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>594</v>
+        <v>522</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>596</v>
+        <v>521</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>30</v>
@@ -3943,19 +3970,19 @@
       <c r="F70" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G70" s="5" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G70" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
-        <v>445</v>
+        <v>42</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>498</v>
+        <v>40</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>457</v>
+        <v>41</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>30</v>
@@ -3966,19 +3993,19 @@
       <c r="F71" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G71" s="2" t="s">
-        <v>418</v>
+      <c r="G71" s="5" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>190</v>
+        <v>562</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>30</v>
@@ -3989,65 +4016,65 @@
       <c r="F72" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G72" s="2" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G72" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
-        <v>245</v>
+        <v>516</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>246</v>
+        <v>562</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G73" s="2" t="s">
-        <v>252</v>
+      <c r="G73" s="10" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
-        <v>251</v>
+        <v>560</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>247</v>
+        <v>43</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>246</v>
+        <v>562</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>30</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>252</v>
+      <c r="G74" s="4" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
-        <v>506</v>
+        <v>593</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>507</v>
+        <v>594</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>508</v>
+        <v>596</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>30</v>
@@ -4059,18 +4086,18 @@
         <v>6</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="14" x14ac:dyDescent="0.15">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>337</v>
+        <v>445</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>498</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>333</v>
+        <v>457</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>30</v>
@@ -4082,18 +4109,18 @@
         <v>6</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>338</v>
+        <v>418</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
-        <v>446</v>
+        <v>188</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>499</v>
+        <v>191</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>462</v>
+        <v>190</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>30</v>
@@ -4105,21 +4132,21 @@
         <v>6</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>418</v>
+        <v>192</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
-        <v>426</v>
+        <v>245</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>480</v>
+        <v>247</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>458</v>
+        <v>246</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>11</v>
@@ -4128,21 +4155,21 @@
         <v>6</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>418</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
-        <v>115</v>
+        <v>251</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>116</v>
+        <v>247</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>11</v>
@@ -4150,22 +4177,22 @@
       <c r="F79" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="4" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G79" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
-        <v>46</v>
+        <v>506</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>50</v>
+        <v>507</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>48</v>
+        <v>508</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>11</v>
@@ -4173,22 +4200,22 @@
       <c r="F80" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G80" s="5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>52</v>
+        <v>335</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>337</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>49</v>
+        <v>333</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>11</v>
@@ -4197,21 +4224,21 @@
         <v>6</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
-        <v>89</v>
+        <v>446</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>52</v>
+        <v>499</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>49</v>
+        <v>462</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>11</v>
@@ -4219,19 +4246,19 @@
       <c r="F82" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G82" s="5" t="s">
-        <v>210</v>
+      <c r="G82" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
-        <v>476</v>
+        <v>426</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>49</v>
+        <v>458</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>51</v>
@@ -4246,18 +4273,18 @@
         <v>418</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>11</v>
@@ -4265,22 +4292,22 @@
       <c r="F84" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G84" s="5" t="s">
-        <v>112</v>
+      <c r="G84" s="4" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
-        <v>447</v>
+        <v>46</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>465</v>
+        <v>48</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>420</v>
+        <v>51</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>11</v>
@@ -4289,21 +4316,21 @@
         <v>6</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>418</v>
+        <v>209</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="13" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>11</v>
@@ -4312,21 +4339,21 @@
         <v>6</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.15">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
-        <v>312</v>
+        <v>89</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>11</v>
@@ -4334,22 +4361,22 @@
       <c r="F87" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>302</v>
+      <c r="G87" s="5" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
-        <v>55</v>
+        <v>476</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>53</v>
+        <v>481</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>11</v>
@@ -4358,21 +4385,21 @@
         <v>6</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>211</v>
+        <v>418</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>414</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>413</v>
+        <v>108</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>9</v>
+        <v>111</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>11</v>
@@ -4381,21 +4408,21 @@
         <v>6</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>391</v>
+        <v>112</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
-        <v>56</v>
+        <v>447</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>57</v>
+        <v>500</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>58</v>
+        <v>465</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>9</v>
+        <v>420</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>11</v>
@@ -4404,18 +4431,18 @@
         <v>6</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>59</v>
+        <v>418</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>9</v>
@@ -4427,21 +4454,21 @@
         <v>6</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
-        <v>382</v>
+        <v>312</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>372</v>
+        <v>9</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>11</v>
@@ -4449,22 +4476,22 @@
       <c r="F92" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G92" s="5" t="s">
-        <v>370</v>
+      <c r="G92" s="2" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
-        <v>299</v>
+        <v>55</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>343</v>
+        <v>53</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>342</v>
+        <v>54</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -4473,21 +4500,21 @@
         <v>6</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.15">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>60</v>
+        <v>412</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>413</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -4495,22 +4522,22 @@
       <c r="F94" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G94" s="2" t="s">
-        <v>64</v>
+      <c r="G94" s="5" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -4519,21 +4546,21 @@
         <v>6</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>212</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
-        <v>227</v>
+        <v>118</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -4542,21 +4569,21 @@
         <v>6</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>223</v>
+        <v>127</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
-        <v>526</v>
+        <v>382</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>63</v>
+        <v>372</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -4565,21 +4592,21 @@
         <v>6</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
-        <v>91</v>
+        <v>299</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>92</v>
+        <v>343</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>93</v>
+        <v>342</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -4587,22 +4614,22 @@
       <c r="F98" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G98" s="5" t="s">
-        <v>95</v>
+      <c r="G98" s="2" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
-        <v>421</v>
+        <v>61</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>460</v>
+        <v>62</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>459</v>
+        <v>60</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>419</v>
+        <v>63</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -4611,21 +4638,21 @@
         <v>6</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -4633,45 +4660,45 @@
       <c r="F100" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G100" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G100" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
-        <v>576</v>
+        <v>227</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>570</v>
+        <v>62</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>567</v>
+        <v>60</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G101" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G101" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
-        <v>224</v>
+        <v>526</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>230</v>
+        <v>62</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>234</v>
+        <v>60</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -4679,22 +4706,22 @@
       <c r="F102" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G102" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G102" s="5" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
-        <v>501</v>
+        <v>91</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>230</v>
+        <v>92</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>234</v>
+        <v>93</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>257</v>
+        <v>94</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -4702,22 +4729,22 @@
       <c r="F103" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>418</v>
+      <c r="G103" s="5" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
-        <v>551</v>
+        <v>421</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>230</v>
+        <v>460</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>234</v>
+        <v>459</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>257</v>
+        <v>419</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -4731,16 +4758,16 @@
     </row>
     <row r="105" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
-        <v>422</v>
+        <v>65</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>552</v>
+        <v>66</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>464</v>
+        <v>67</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -4749,90 +4776,90 @@
         <v>6</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.15">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>464</v>
+        <v>567</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>257</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G106" s="2" t="s">
+      <c r="G106" s="5" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A107" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A108" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>418</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="17" x14ac:dyDescent="0.15">
-      <c r="A107" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G107" s="10" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="14" x14ac:dyDescent="0.15">
-      <c r="A108" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
-        <v>176</v>
+        <v>551</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>177</v>
+        <v>230</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>178</v>
+        <v>234</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -4841,18 +4868,18 @@
         <v>6</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>180</v>
+        <v>418</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
-        <v>397</v>
+        <v>422</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>402</v>
+        <v>552</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>403</v>
+        <v>464</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>257</v>
@@ -4864,21 +4891,21 @@
         <v>6</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>386</v>
+        <v>553</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
-        <v>431</v>
+        <v>577</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>486</v>
+        <v>552</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>9</v>
+        <v>257</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -4890,41 +4917,41 @@
         <v>418</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:7" ht="17" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
-        <v>432</v>
+        <v>575</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>487</v>
+        <v>552</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>9</v>
+        <v>257</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G112" s="2" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G112" s="10" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="14" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
-        <v>433</v>
+        <v>171</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="C113" s="2" t="s">
-        <v>468</v>
+        <v>172</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>9</v>
+        <v>175</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -4933,21 +4960,21 @@
         <v>6</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>418</v>
+        <v>174</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
-        <v>434</v>
+        <v>176</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>489</v>
+        <v>177</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>456</v>
+        <v>178</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -4956,21 +4983,21 @@
         <v>6</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>418</v>
+        <v>180</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
-        <v>100</v>
+        <v>397</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>101</v>
+        <v>402</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>9</v>
+        <v>257</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -4979,18 +5006,18 @@
         <v>6</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>103</v>
+        <v>386</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
-        <v>371</v>
+        <v>431</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>368</v>
+        <v>486</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>369</v>
+        <v>463</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>9</v>
@@ -5001,22 +5028,22 @@
       <c r="F116" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G116" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="16" x14ac:dyDescent="0.15">
+      <c r="G116" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>400</v>
+        <v>487</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>399</v>
+        <v>475</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -5024,19 +5051,19 @@
       <c r="F117" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G117" s="5" t="s">
-        <v>386</v>
+      <c r="G117" s="2" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
-        <v>133</v>
+        <v>433</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>139</v>
+        <v>488</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>136</v>
+        <v>468</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>9</v>
@@ -5048,18 +5075,18 @@
         <v>6</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>141</v>
+        <v>418</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
-        <v>313</v>
+        <v>434</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>139</v>
+        <v>489</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>136</v>
+        <v>456</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>9</v>
@@ -5071,21 +5098,21 @@
         <v>6</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>302</v>
+        <v>418</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
-        <v>321</v>
+        <v>100</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>323</v>
+        <v>101</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>324</v>
+        <v>102</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -5093,22 +5120,22 @@
       <c r="F120" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G120" s="2" t="s">
-        <v>322</v>
+      <c r="G120" s="5" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="121" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
-        <v>273</v>
+        <v>371</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -5116,19 +5143,19 @@
       <c r="F121" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G121" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="G121" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="16" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
-        <v>301</v>
+        <v>396</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>274</v>
+        <v>400</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>276</v>
+        <v>399</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>257</v>
@@ -5139,22 +5166,22 @@
       <c r="F122" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G122" s="2" t="s">
-        <v>302</v>
+      <c r="G122" s="5" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
-        <v>469</v>
+        <v>133</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>274</v>
+        <v>139</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>276</v>
+        <v>136</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>257</v>
+        <v>9</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -5163,21 +5190,21 @@
         <v>6</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>418</v>
+        <v>141</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
-        <v>529</v>
+        <v>313</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>274</v>
+        <v>139</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>276</v>
